--- a/output/zone_monthly_3_03/installed_capacity_3_03.xlsx
+++ b/output/zone_monthly_3_03/installed_capacity_3_03.xlsx
@@ -13444,7 +13444,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>部分區塊可能沒有此欄</t>
+          <t>3-02 / 3-03 使用</t>
         </is>
       </c>
     </row>
@@ -13476,7 +13476,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>部分區塊可能沒有此欄</t>
+          <t>3-02 / 3-03 使用</t>
         </is>
       </c>
     </row>
@@ -14076,7 +14076,7 @@
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>例如：全國、台電、民營電廠、自用發電設備</t>
+          <t>例如：全國、台電、民營電廠、自用發電設備、再生能源</t>
         </is>
       </c>
     </row>
@@ -14286,7 +14286,11 @@
           <t>依 source_section 而異</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>3-02 / 3-03 使用</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -14314,7 +14318,11 @@
           <t>依 source_section 而異</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>3-02 / 3-03 使用</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/zone_monthly_3_03/installed_capacity_3_03.xlsx
+++ b/output/zone_monthly_3_03/installed_capacity_3_03.xlsx
@@ -13942,7 +13942,11 @@
           <t>依 source_section 而異</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>3-02 / 3-03 使用</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -13970,7 +13974,11 @@
           <t>依 source_section 而異</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>3-02 / 3-03 使用</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">

--- a/output/zone_monthly_3_03/installed_capacity_3_03.xlsx
+++ b/output/zone_monthly_3_03/installed_capacity_3_03.xlsx
@@ -14084,7 +14084,7 @@
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>例如：全國、台電、民營電廠、自用發電設備、再生能源</t>
+          <t>例如：全國、台電、民營電廠、自用發電設備、再生能源、直轉供及躉售</t>
         </is>
       </c>
     </row>

--- a/output/zone_monthly_3_03/installed_capacity_3_03.xlsx
+++ b/output/zone_monthly_3_03/installed_capacity_3_03.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE61"/>
+  <dimension ref="A1:AE65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -592,85 +592,85 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>66882.534961</v>
+        <v>66882.534481</v>
       </c>
       <c r="E2" t="n">
         <v>2602</v>
       </c>
       <c r="F2" t="n">
-        <v>3.890402780811548</v>
+        <v>3.890402808732041</v>
       </c>
       <c r="G2" t="n">
         <v>42121.0046</v>
       </c>
       <c r="H2" t="n">
-        <v>62.97758394558648</v>
+        <v>62.97758439756157</v>
       </c>
       <c r="I2" t="n">
         <v>19871.684</v>
       </c>
       <c r="J2" t="n">
-        <v>29.71132002037216</v>
+        <v>29.71132023360321</v>
       </c>
       <c r="K2" t="n">
         <v>2152.9006</v>
       </c>
       <c r="L2" t="n">
-        <v>3.218927932763586</v>
+        <v>3.218927955865064</v>
       </c>
       <c r="M2" t="n">
         <v>20096.42</v>
       </c>
       <c r="N2" t="n">
-        <v>30.04733599245074</v>
+        <v>30.0473362080933</v>
       </c>
       <c r="O2" t="n">
         <v>951</v>
       </c>
       <c r="P2" t="n">
-        <v>1.421895866468786</v>
+        <v>1.421895876673394</v>
       </c>
       <c r="Q2" t="n">
-        <v>21208.530361</v>
+        <v>21208.529881</v>
       </c>
       <c r="R2" t="n">
-        <v>31.71011740713319</v>
+        <v>31.71011691703297</v>
       </c>
       <c r="S2" t="n">
         <v>2122.6235</v>
       </c>
       <c r="T2" t="n">
-        <v>3.173658865109893</v>
+        <v>3.173658887886486</v>
       </c>
       <c r="U2" t="n">
         <v>7.489</v>
       </c>
       <c r="V2" t="n">
-        <v>0.011197243053612</v>
+        <v>0.011197243133972</v>
       </c>
       <c r="W2" t="n">
-        <v>14364.508161</v>
+        <v>14364.507681</v>
       </c>
       <c r="X2" t="n">
-        <v>21.47721848368354</v>
+        <v>21.47721792014427</v>
       </c>
       <c r="Y2" t="n">
         <v>3963.4467</v>
       </c>
       <c r="Z2" t="n">
-        <v>5.925981576970928</v>
+        <v>5.925981619500283</v>
       </c>
       <c r="AA2" t="n">
         <v>83.998</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.125590335427597</v>
+        <v>0.125590336328929</v>
       </c>
       <c r="AC2" t="n">
         <v>666.465</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.996470902887613</v>
+        <v>0.996470910039047</v>
       </c>
       <c r="AE2" t="inlineStr"/>
     </row>
@@ -691,85 +691,85 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>66932.785166</v>
+        <v>66932.784856</v>
       </c>
       <c r="E3" t="n">
         <v>2602</v>
       </c>
       <c r="F3" t="n">
-        <v>3.887482036713069</v>
+        <v>3.887482054717989</v>
       </c>
       <c r="G3" t="n">
         <v>42078.8206</v>
       </c>
       <c r="H3" t="n">
-        <v>62.86727871197996</v>
+        <v>62.86727900315052</v>
       </c>
       <c r="I3" t="n">
         <v>19831.684</v>
       </c>
       <c r="J3" t="n">
-        <v>29.62925261636049</v>
+        <v>29.62925275358873</v>
       </c>
       <c r="K3" t="n">
         <v>2150.7166</v>
       </c>
       <c r="L3" t="n">
-        <v>3.213248327655883</v>
+        <v>3.213248342538081</v>
       </c>
       <c r="M3" t="n">
         <v>20096.42</v>
       </c>
       <c r="N3" t="n">
-        <v>30.0247777679636</v>
+        <v>30.02477790702372</v>
       </c>
       <c r="O3" t="n">
         <v>951</v>
       </c>
       <c r="P3" t="n">
-        <v>1.420828369298282</v>
+        <v>1.420828375878865</v>
       </c>
       <c r="Q3" t="n">
-        <v>21300.964566</v>
+        <v>21300.964256</v>
       </c>
       <c r="R3" t="n">
-        <v>31.82441088200869</v>
+        <v>31.82441056625262</v>
       </c>
       <c r="S3" t="n">
         <v>2122.6835</v>
       </c>
       <c r="T3" t="n">
-        <v>3.171365863134983</v>
+        <v>3.171365877823203</v>
       </c>
       <c r="U3" t="n">
         <v>7.489</v>
       </c>
       <c r="V3" t="n">
-        <v>0.011188836653706</v>
+        <v>0.011188836705528</v>
       </c>
       <c r="W3" t="n">
-        <v>14440.882366</v>
+        <v>14440.882056</v>
       </c>
       <c r="X3" t="n">
-        <v>21.5752001506962</v>
+        <v>21.5751997874708</v>
       </c>
       <c r="Y3" t="n">
         <v>3979.4467</v>
       </c>
       <c r="Z3" t="n">
-        <v>5.945437187666066</v>
+        <v>5.945437215202431</v>
       </c>
       <c r="AA3" t="n">
         <v>83.998</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.1254960477017</v>
+        <v>0.125496048282937</v>
       </c>
       <c r="AC3" t="n">
         <v>666.465</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.995722796156025</v>
+        <v>0.995722800767727</v>
       </c>
       <c r="AE3" t="inlineStr"/>
     </row>
@@ -790,85 +790,85 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>67044.961021</v>
+        <v>67044.96071100001</v>
       </c>
       <c r="E4" t="n">
         <v>2602</v>
       </c>
       <c r="F4" t="n">
-        <v>3.880977720585138</v>
+        <v>3.880977738529859</v>
       </c>
       <c r="G4" t="n">
         <v>42121.3266</v>
       </c>
       <c r="H4" t="n">
-        <v>62.82549196621451</v>
+        <v>62.82549225670468</v>
       </c>
       <c r="I4" t="n">
         <v>19831.684</v>
       </c>
       <c r="J4" t="n">
-        <v>29.57967861863365</v>
+        <v>29.57967875540307</v>
       </c>
       <c r="K4" t="n">
         <v>2193.2226</v>
       </c>
       <c r="L4" t="n">
-        <v>3.271271347764723</v>
+        <v>3.271271362890306</v>
       </c>
       <c r="M4" t="n">
         <v>20096.42</v>
       </c>
       <c r="N4" t="n">
-        <v>29.97454199981614</v>
+        <v>29.97454213841131</v>
       </c>
       <c r="O4" t="n">
         <v>951</v>
       </c>
       <c r="P4" t="n">
-        <v>1.418451119245375</v>
+        <v>1.418451125803957</v>
       </c>
       <c r="Q4" t="n">
-        <v>21370.634421</v>
+        <v>21370.634111</v>
       </c>
       <c r="R4" t="n">
-        <v>31.87507919395498</v>
+        <v>31.8750788789615</v>
       </c>
       <c r="S4" t="n">
         <v>2122.2035</v>
       </c>
       <c r="T4" t="n">
-        <v>3.165343774806995</v>
+        <v>3.165343789442795</v>
       </c>
       <c r="U4" t="n">
         <v>7.489</v>
       </c>
       <c r="V4" t="n">
-        <v>0.011170116122007</v>
+        <v>0.011170116173655</v>
       </c>
       <c r="W4" t="n">
-        <v>14510.871121</v>
+        <v>14510.870811</v>
       </c>
       <c r="X4" t="n">
-        <v>21.64349251609658</v>
+        <v>21.64349215379467</v>
       </c>
       <c r="Y4" t="n">
         <v>3979.4128</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.935439053732253</v>
+        <v>5.935439081176316</v>
       </c>
       <c r="AA4" t="n">
         <v>84.193</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.125576924377104</v>
+        <v>0.125576924957742</v>
       </c>
       <c r="AC4" t="n">
         <v>666.465</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.994056808820052</v>
+        <v>0.994056813416335</v>
       </c>
       <c r="AE4" t="inlineStr"/>
     </row>
@@ -889,85 +889,85 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>66386.140176</v>
+        <v>66384.484866</v>
       </c>
       <c r="E5" t="n">
         <v>2602</v>
       </c>
       <c r="F5" t="n">
-        <v>3.919492823504564</v>
+        <v>3.919590556817985</v>
       </c>
       <c r="G5" t="n">
         <v>41349.3266</v>
       </c>
       <c r="H5" t="n">
-        <v>62.286083345675</v>
+        <v>62.28763646123855</v>
       </c>
       <c r="I5" t="n">
         <v>19831.684</v>
       </c>
       <c r="J5" t="n">
-        <v>29.8732294834782</v>
+        <v>29.87397437824686</v>
       </c>
       <c r="K5" t="n">
         <v>2193.2226</v>
       </c>
       <c r="L5" t="n">
-        <v>3.30373568064874</v>
+        <v>3.303818059938427</v>
       </c>
       <c r="M5" t="n">
         <v>19324.42</v>
       </c>
       <c r="N5" t="n">
-        <v>29.10911818154806</v>
+        <v>29.10984402305326</v>
       </c>
       <c r="O5" t="n">
         <v>951</v>
       </c>
       <c r="P5" t="n">
-        <v>1.432527930496864</v>
+        <v>1.432563650858533</v>
       </c>
       <c r="Q5" t="n">
-        <v>21483.813576</v>
+        <v>21482.158266</v>
       </c>
       <c r="R5" t="n">
-        <v>32.36189590032357</v>
+        <v>32.36020933108494</v>
       </c>
       <c r="S5" t="n">
-        <v>2123.8595</v>
+        <v>2122.2035</v>
       </c>
       <c r="T5" t="n">
-        <v>3.199251371399689</v>
+        <v>3.196836586566516</v>
       </c>
       <c r="U5" t="n">
         <v>7.489</v>
       </c>
       <c r="V5" t="n">
-        <v>0.011280969160348</v>
+        <v>0.011281250453501</v>
       </c>
       <c r="W5" t="n">
-        <v>14622.394276</v>
+        <v>14622.394966</v>
       </c>
       <c r="X5" t="n">
-        <v>22.02627572145896</v>
+        <v>22.02682599031377</v>
       </c>
       <c r="Y5" t="n">
         <v>3979.4128</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.994342779155342</v>
+        <v>5.994492249254656</v>
       </c>
       <c r="AA5" t="n">
         <v>84.193</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.12682315883525</v>
+        <v>0.126826321195302</v>
       </c>
       <c r="AC5" t="n">
         <v>666.465</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.003921900313977</v>
+        <v>1.003946933301191</v>
       </c>
       <c r="AE5" t="inlineStr"/>
     </row>
@@ -988,85 +988,85 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>67587.766506</v>
+        <v>67621.771866</v>
       </c>
       <c r="E6" t="n">
         <v>2602</v>
       </c>
       <c r="F6" t="n">
-        <v>3.849809121550143</v>
+        <v>3.8478731452884</v>
       </c>
       <c r="G6" t="n">
         <v>42479.7336</v>
       </c>
       <c r="H6" t="n">
-        <v>62.85121671571871</v>
+        <v>62.81961035297667</v>
       </c>
       <c r="I6" t="n">
         <v>19831.684</v>
       </c>
       <c r="J6" t="n">
-        <v>29.34212066060724</v>
+        <v>29.327365215006</v>
       </c>
       <c r="K6" t="n">
         <v>2224.6816</v>
       </c>
       <c r="L6" t="n">
-        <v>3.291544779486843</v>
+        <v>3.289889540913616</v>
       </c>
       <c r="M6" t="n">
         <v>20423.368</v>
       </c>
       <c r="N6" t="n">
-        <v>30.21755127562463</v>
+        <v>30.20235559705705</v>
       </c>
       <c r="O6" t="n">
         <v>951</v>
       </c>
       <c r="P6" t="n">
-        <v>1.407059367638042</v>
+        <v>1.406351791379426</v>
       </c>
       <c r="Q6" t="n">
-        <v>21555.032906</v>
+        <v>21589.038266</v>
       </c>
       <c r="R6" t="n">
-        <v>31.89191479509311</v>
+        <v>31.92616471035551</v>
       </c>
       <c r="S6" t="n">
         <v>2123.8595</v>
       </c>
       <c r="T6" t="n">
-        <v>3.142372665638326</v>
+        <v>3.140792442127459</v>
       </c>
       <c r="U6" t="n">
         <v>7.489</v>
       </c>
       <c r="V6" t="n">
-        <v>0.011080407575438</v>
+        <v>0.011074835505405</v>
       </c>
       <c r="W6" t="n">
-        <v>14693.632606</v>
+        <v>14727.637966</v>
       </c>
       <c r="X6" t="n">
-        <v>21.74007718496748</v>
+        <v>21.7794322147968</v>
       </c>
       <c r="Y6" t="n">
         <v>3979.4128</v>
       </c>
       <c r="Z6" t="n">
-        <v>5.887770828537045</v>
+        <v>5.884810010429253</v>
       </c>
       <c r="AA6" t="n">
         <v>84.17400000000001</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.124540289391761</v>
+        <v>0.124477661080517</v>
       </c>
       <c r="AC6" t="n">
         <v>666.465</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.986073418983058</v>
+        <v>0.985577546416077</v>
       </c>
       <c r="AE6" t="inlineStr"/>
     </row>
@@ -1087,37 +1087,37 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>66784.56986600001</v>
+        <v>66785.974386</v>
       </c>
       <c r="E7" t="n">
         <v>2602</v>
       </c>
       <c r="F7" t="n">
-        <v>3.89610954329838</v>
+        <v>3.896027607475386</v>
       </c>
       <c r="G7" t="n">
         <v>42479.7336</v>
       </c>
       <c r="H7" t="n">
-        <v>63.60710817668443</v>
+        <v>63.6057705087624</v>
       </c>
       <c r="I7" t="n">
         <v>19831.684</v>
       </c>
       <c r="J7" t="n">
-        <v>29.69500895160561</v>
+        <v>29.69438446069481</v>
       </c>
       <c r="K7" t="n">
         <v>2224.6816</v>
       </c>
       <c r="L7" t="n">
-        <v>3.331131134727252</v>
+        <v>3.331061080492895</v>
       </c>
       <c r="M7" t="n">
         <v>20423.368</v>
       </c>
       <c r="N7" t="n">
-        <v>30.58096809035156</v>
+        <v>30.5803249675747</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1126,46 +1126,46 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>21702.836266</v>
+        <v>21704.240786</v>
       </c>
       <c r="R7" t="n">
-        <v>32.49678228001721</v>
+        <v>32.49820188376221</v>
       </c>
       <c r="S7" t="n">
         <v>2123.8595</v>
       </c>
       <c r="T7" t="n">
-        <v>3.180164975624492</v>
+        <v>3.180098096233232</v>
       </c>
       <c r="U7" t="n">
         <v>7.489</v>
       </c>
       <c r="V7" t="n">
-        <v>0.011213668089839</v>
+        <v>0.011213432264559</v>
       </c>
       <c r="W7" t="n">
-        <v>14842.945566</v>
+        <v>14844.350086</v>
       </c>
       <c r="X7" t="n">
-        <v>22.2251121715415</v>
+        <v>22.22674779019432</v>
       </c>
       <c r="Y7" t="n">
         <v>3977.9032</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.956320760890532</v>
+        <v>5.956195498487579</v>
       </c>
       <c r="AA7" t="n">
         <v>84.17400000000001</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.1260380955794</v>
+        <v>0.126035444977568</v>
       </c>
       <c r="AC7" t="n">
         <v>666.465</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.997932608291451</v>
+        <v>0.9979116216049509</v>
       </c>
       <c r="AE7" t="inlineStr"/>
     </row>
@@ -1186,37 +1186,37 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>68092.072751</v>
+        <v>68093.97343100001</v>
       </c>
       <c r="E8" t="n">
         <v>2602</v>
       </c>
       <c r="F8" t="n">
-        <v>3.821296510557152</v>
+        <v>3.821189848227349</v>
       </c>
       <c r="G8" t="n">
         <v>43605.3626</v>
       </c>
       <c r="H8" t="n">
-        <v>64.03882396039943</v>
+        <v>64.0370364701739</v>
       </c>
       <c r="I8" t="n">
         <v>19831.684</v>
       </c>
       <c r="J8" t="n">
-        <v>29.12480586766798</v>
+        <v>29.12399291854448</v>
       </c>
       <c r="K8" t="n">
         <v>2226.6816</v>
       </c>
       <c r="L8" t="n">
-        <v>3.270104007763956</v>
+        <v>3.270012730651279</v>
       </c>
       <c r="M8" t="n">
         <v>21546.997</v>
       </c>
       <c r="N8" t="n">
-        <v>31.64391408496749</v>
+        <v>31.64303082097814</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1225,46 +1225,46 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>21884.710151</v>
+        <v>21886.610831</v>
       </c>
       <c r="R8" t="n">
-        <v>32.13987952904342</v>
+        <v>32.14177368159874</v>
       </c>
       <c r="S8" t="n">
         <v>2123.8595</v>
       </c>
       <c r="T8" t="n">
-        <v>3.119099498948369</v>
+        <v>3.119012436764494</v>
       </c>
       <c r="U8" t="n">
         <v>7.489</v>
       </c>
       <c r="V8" t="n">
-        <v>0.010998343415666</v>
+        <v>0.01099803642328</v>
       </c>
       <c r="W8" t="n">
-        <v>14940.724451</v>
+        <v>14942.625131</v>
       </c>
       <c r="X8" t="n">
-        <v>21.94194396994705</v>
+        <v>21.944122773422</v>
       </c>
       <c r="Y8" t="n">
         <v>4061.9482</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.965376050239778</v>
+        <v>5.965209541070466</v>
       </c>
       <c r="AA8" t="n">
         <v>84.224</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.123691344083461</v>
+        <v>0.123687891536165</v>
       </c>
       <c r="AC8" t="n">
         <v>666.465</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.978770322409098</v>
+        <v>0.978743002382337</v>
       </c>
       <c r="AE8" t="inlineStr"/>
     </row>
@@ -1285,37 +1285,37 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>68241.673771</v>
+        <v>68241.08889100001</v>
       </c>
       <c r="E9" t="n">
         <v>2602</v>
       </c>
       <c r="F9" t="n">
-        <v>3.812919373477834</v>
+        <v>3.812952053206708</v>
       </c>
       <c r="G9" t="n">
         <v>43608.1506</v>
       </c>
       <c r="H9" t="n">
-        <v>63.90252200779361</v>
+        <v>63.90306970285064</v>
       </c>
       <c r="I9" t="n">
         <v>19831.684</v>
       </c>
       <c r="J9" t="n">
-        <v>29.06095777566886</v>
+        <v>29.06120685101716</v>
       </c>
       <c r="K9" t="n">
         <v>2229.4696</v>
       </c>
       <c r="L9" t="n">
-        <v>3.267020688093726</v>
+        <v>3.267048689039946</v>
       </c>
       <c r="M9" t="n">
         <v>21546.997</v>
       </c>
       <c r="N9" t="n">
-        <v>31.57454354403103</v>
+        <v>31.57481416279354</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1324,46 +1324,46 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>22031.523171</v>
+        <v>22030.938291</v>
       </c>
       <c r="R9" t="n">
-        <v>32.28455861872855</v>
+        <v>32.28397824394264</v>
       </c>
       <c r="S9" t="n">
         <v>2123.8595</v>
       </c>
       <c r="T9" t="n">
-        <v>3.112261734855859</v>
+        <v>3.112288409395686</v>
       </c>
       <c r="U9" t="n">
         <v>7.489</v>
       </c>
       <c r="V9" t="n">
-        <v>0.010974232585694</v>
+        <v>0.01097432664353</v>
       </c>
       <c r="W9" t="n">
-        <v>15019.677471</v>
+        <v>15019.092591</v>
       </c>
       <c r="X9" t="n">
-        <v>22.00953851366812</v>
+        <v>22.008870073849</v>
       </c>
       <c r="Y9" t="n">
         <v>4129.5482</v>
       </c>
       <c r="Z9" t="n">
-        <v>6.051358314946393</v>
+        <v>6.051410179863977</v>
       </c>
       <c r="AA9" t="n">
         <v>84.48399999999999</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.123801183838932</v>
+        <v>0.123802244912804</v>
       </c>
       <c r="AC9" t="n">
         <v>666.465</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.976624638833553</v>
+        <v>0.976633009277636</v>
       </c>
       <c r="AE9" t="inlineStr"/>
     </row>
@@ -1384,37 +1384,37 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>68401.257791</v>
+        <v>68401.25735099999</v>
       </c>
       <c r="E10" t="n">
         <v>2602</v>
       </c>
       <c r="F10" t="n">
-        <v>3.804023615984386</v>
+        <v>3.804023640454263</v>
       </c>
       <c r="G10" t="n">
         <v>43607.1506</v>
       </c>
       <c r="H10" t="n">
-        <v>63.75197183250872</v>
+        <v>63.75197224260158</v>
       </c>
       <c r="I10" t="n">
         <v>19831.684</v>
       </c>
       <c r="J10" t="n">
-        <v>28.99315691035346</v>
+        <v>28.99315709685572</v>
       </c>
       <c r="K10" t="n">
         <v>2228.4696</v>
       </c>
       <c r="L10" t="n">
-        <v>3.257936581822936</v>
+        <v>3.257936602780037</v>
       </c>
       <c r="M10" t="n">
         <v>21546.997</v>
       </c>
       <c r="N10" t="n">
-        <v>31.50087834033233</v>
+        <v>31.50087854296583</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1423,46 +1423,46 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>22192.107191</v>
+        <v>22192.106751</v>
       </c>
       <c r="R10" t="n">
-        <v>32.44400455150689</v>
+        <v>32.44400411694414</v>
       </c>
       <c r="S10" t="n">
         <v>2123.8595</v>
       </c>
       <c r="T10" t="n">
-        <v>3.105000651434585</v>
+        <v>3.105000671407906</v>
       </c>
       <c r="U10" t="n">
         <v>7.489</v>
       </c>
       <c r="V10" t="n">
-        <v>0.010948629077674</v>
+        <v>0.010948629148102</v>
       </c>
       <c r="W10" t="n">
-        <v>15098.769491</v>
+        <v>15098.769051</v>
       </c>
       <c r="X10" t="n">
-        <v>22.07381849195563</v>
+        <v>22.07381799068531</v>
       </c>
       <c r="Y10" t="n">
         <v>4213.0602</v>
       </c>
       <c r="Z10" t="n">
-        <v>6.159331474390431</v>
+        <v>6.159331514011133</v>
       </c>
       <c r="AA10" t="n">
         <v>84.434</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.123439250573415</v>
+        <v>0.123439251367454</v>
       </c>
       <c r="AC10" t="n">
         <v>664.495</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.971466054075152</v>
+        <v>0.971466060324234</v>
       </c>
       <c r="AE10" t="inlineStr"/>
     </row>
@@ -1483,37 +1483,37 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>68580.986661</v>
+        <v>68580.986341</v>
       </c>
       <c r="E11" t="n">
         <v>2602</v>
       </c>
       <c r="F11" t="n">
-        <v>3.794054484607876</v>
+        <v>3.794054502310996</v>
       </c>
       <c r="G11" t="n">
         <v>43634.4736</v>
       </c>
       <c r="H11" t="n">
-        <v>63.62473875695003</v>
+        <v>63.62473905382409</v>
       </c>
       <c r="I11" t="n">
         <v>19859.007</v>
       </c>
       <c r="J11" t="n">
-        <v>28.95701559116419</v>
+        <v>28.95701572627809</v>
       </c>
       <c r="K11" t="n">
         <v>2228.4696</v>
       </c>
       <c r="L11" t="n">
-        <v>3.249398570212268</v>
+        <v>3.249398585374014</v>
       </c>
       <c r="M11" t="n">
         <v>21546.997</v>
       </c>
       <c r="N11" t="n">
-        <v>31.41832459557357</v>
+        <v>31.41832474217199</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1522,46 +1522,46 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>22344.513061</v>
+        <v>22344.512741</v>
       </c>
       <c r="R11" t="n">
-        <v>32.58120675844209</v>
+        <v>32.58120644386489</v>
       </c>
       <c r="S11" t="n">
         <v>2123.8595</v>
       </c>
       <c r="T11" t="n">
-        <v>3.096863436069193</v>
+        <v>3.096863450519209</v>
       </c>
       <c r="U11" t="n">
         <v>7.489</v>
       </c>
       <c r="V11" t="n">
-        <v>0.01091993621646</v>
+        <v>0.010919936267412</v>
       </c>
       <c r="W11" t="n">
-        <v>15183.575361</v>
+        <v>15183.575041</v>
       </c>
       <c r="X11" t="n">
-        <v>22.13962805180004</v>
+        <v>22.13962768850227</v>
       </c>
       <c r="Y11" t="n">
         <v>4280.6602</v>
       </c>
       <c r="Z11" t="n">
-        <v>6.241759426937913</v>
+        <v>6.241759456062064</v>
       </c>
       <c r="AA11" t="n">
         <v>84.434</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.123115755708448</v>
+        <v>0.123115756282908</v>
       </c>
       <c r="AC11" t="n">
         <v>664.495</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.968920151710035</v>
+        <v>0.968920156231032</v>
       </c>
       <c r="AE11" t="inlineStr"/>
     </row>
@@ -1582,37 +1582,37 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>68703.26694099999</v>
+        <v>68703.266621</v>
       </c>
       <c r="E12" t="n">
         <v>2602</v>
       </c>
       <c r="F12" t="n">
-        <v>3.7873017046402</v>
+        <v>3.787301722280359</v>
       </c>
       <c r="G12" t="n">
         <v>43634.4736</v>
       </c>
       <c r="H12" t="n">
-        <v>63.51149740444189</v>
+        <v>63.51149770026013</v>
       </c>
       <c r="I12" t="n">
         <v>19859.007</v>
       </c>
       <c r="J12" t="n">
-        <v>28.90547696524277</v>
+        <v>28.90547709987614</v>
       </c>
       <c r="K12" t="n">
         <v>2228.4696</v>
       </c>
       <c r="L12" t="n">
-        <v>3.243615186325467</v>
+        <v>3.243615201433291</v>
       </c>
       <c r="M12" t="n">
         <v>21546.997</v>
       </c>
       <c r="N12" t="n">
-        <v>31.36240525287366</v>
+        <v>31.3624053989507</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1621,46 +1621,46 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>22466.793341</v>
+        <v>22466.793021</v>
       </c>
       <c r="R12" t="n">
-        <v>32.70120089091791</v>
+        <v>32.70120057745951</v>
       </c>
       <c r="S12" t="n">
         <v>2124.4215</v>
       </c>
       <c r="T12" t="n">
-        <v>3.09216954970188</v>
+        <v>3.092169564104313</v>
       </c>
       <c r="U12" t="n">
         <v>7.489</v>
       </c>
       <c r="V12" t="n">
-        <v>0.010900500563432</v>
+        <v>0.010900500614204</v>
       </c>
       <c r="W12" t="n">
-        <v>15263.537641</v>
+        <v>15263.537321</v>
       </c>
       <c r="X12" t="n">
-        <v>22.21661111706348</v>
+        <v>22.21661075477088</v>
       </c>
       <c r="Y12" t="n">
         <v>4322.4162</v>
       </c>
       <c r="Z12" t="n">
-        <v>6.29142745673498</v>
+        <v>6.291427486038633</v>
       </c>
       <c r="AA12" t="n">
         <v>84.434</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.122896630334201</v>
+        <v>0.122896630906618</v>
       </c>
       <c r="AC12" t="n">
         <v>664.495</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.967195636519942</v>
+        <v>0.967195641024861</v>
       </c>
       <c r="AE12" t="inlineStr"/>
     </row>
@@ -1681,37 +1681,37 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>69858.48459599999</v>
+        <v>69858.484276</v>
       </c>
       <c r="E13" t="n">
         <v>2602</v>
       </c>
       <c r="F13" t="n">
-        <v>3.724672836875404</v>
+        <v>3.724672853936972</v>
       </c>
       <c r="G13" t="n">
         <v>44384.4736</v>
       </c>
       <c r="H13" t="n">
-        <v>63.53483597115042</v>
+        <v>63.53483626218377</v>
       </c>
       <c r="I13" t="n">
         <v>19309.007</v>
       </c>
       <c r="J13" t="n">
-        <v>27.64017443502576</v>
+        <v>27.6401745616368</v>
       </c>
       <c r="K13" t="n">
         <v>2228.4696</v>
       </c>
       <c r="L13" t="n">
-        <v>3.189977012652803</v>
+        <v>3.189977027265096</v>
       </c>
       <c r="M13" t="n">
         <v>22846.997</v>
       </c>
       <c r="N13" t="n">
-        <v>32.70468452347188</v>
+        <v>32.70468467328188</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -1720,46 +1720,46 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>22872.010996</v>
+        <v>22872.010676</v>
       </c>
       <c r="R13" t="n">
-        <v>32.74049119197414</v>
+        <v>32.74049088387925</v>
       </c>
       <c r="S13" t="n">
         <v>2124.4215</v>
       </c>
       <c r="T13" t="n">
-        <v>3.041035762922405</v>
+        <v>3.041035776852445</v>
       </c>
       <c r="U13" t="n">
         <v>7.489</v>
       </c>
       <c r="V13" t="n">
-        <v>0.010720243995142</v>
+        <v>0.010720244044248</v>
       </c>
       <c r="W13" t="n">
-        <v>15474.020296</v>
+        <v>15474.019976</v>
       </c>
       <c r="X13" t="n">
-        <v>22.15052385617597</v>
+        <v>22.15052349957173</v>
       </c>
       <c r="Y13" t="n">
         <v>4517.1962</v>
       </c>
       <c r="Z13" t="n">
-        <v>6.466209832811988</v>
+        <v>6.466209862431685</v>
       </c>
       <c r="AA13" t="n">
         <v>84.389</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.120799929297109</v>
+        <v>0.120799929850456</v>
       </c>
       <c r="AC13" t="n">
         <v>664.495</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.95120156677153</v>
+        <v>0.951201571128689</v>
       </c>
       <c r="AE13" t="inlineStr"/>
     </row>
@@ -2063,95 +2063,101 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>台電</t>
+          <t>全國</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>01月</t>
+          <t>04月</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2025/01</t>
+          <t>2026/04</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>32516.151965</v>
+        <v>71003.480256</v>
       </c>
       <c r="E17" t="n">
         <v>2602</v>
       </c>
       <c r="F17" t="n">
-        <v>3.890402780811548</v>
+        <v>3.66460910172093</v>
       </c>
       <c r="G17" t="n">
-        <v>26145.89</v>
+        <v>44668.3656</v>
       </c>
       <c r="H17" t="n">
-        <v>39.09225332928242</v>
+        <v>62.91010727777022</v>
       </c>
       <c r="I17" t="n">
-        <v>10600</v>
+        <v>19276.757</v>
       </c>
       <c r="J17" t="n">
-        <v>15.84868158209163</v>
+        <v>27.14903118903254</v>
       </c>
       <c r="K17" t="n">
-        <v>1592.488</v>
+        <v>2231.4696</v>
       </c>
       <c r="L17" t="n">
-        <v>2.381022192009616</v>
+        <v>3.142760878698526</v>
       </c>
       <c r="M17" t="n">
-        <v>13953.402</v>
+        <v>23160.139</v>
       </c>
       <c r="N17" t="n">
-        <v>20.86254955518118</v>
+        <v>32.61831521003916</v>
       </c>
       <c r="O17" t="n">
-        <v>951</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.421895866468786</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>2817.261965</v>
+        <v>23733.114656</v>
       </c>
       <c r="R17" t="n">
-        <v>4.212253567605922</v>
+        <v>33.42528362050884</v>
       </c>
       <c r="S17" t="n">
-        <v>2076.328</v>
+        <v>2124.7865</v>
       </c>
       <c r="T17" t="n">
-        <v>3.104439748300108</v>
+        <v>2.992510356308132</v>
       </c>
       <c r="U17" t="n">
-        <v>0.84</v>
+        <v>12.937</v>
       </c>
       <c r="V17" t="n">
-        <v>0.001255933257449</v>
+        <v>0.018220233646796</v>
       </c>
       <c r="W17" t="n">
-        <v>291.653965</v>
+        <v>15836.692956</v>
       </c>
       <c r="X17" t="n">
-        <v>0.4360689456075</v>
+        <v>22.30410805062158</v>
       </c>
       <c r="Y17" t="n">
-        <v>448.44</v>
+        <v>5014.4722</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.670488940440865</v>
-      </c>
-      <c r="AA17" t="inlineStr"/>
-      <c r="AB17" t="inlineStr"/>
-      <c r="AC17" t="inlineStr"/>
-      <c r="AD17" t="inlineStr"/>
-      <c r="AE17" t="n">
-        <v>48.61680554416868</v>
-      </c>
+        <v>7.062290724230045</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>79.73099999999999</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.112291678819874</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>664.495</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.935862576882417</v>
+      </c>
+      <c r="AE17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2161,89 +2167,89 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>02月</t>
+          <t>01月</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2025/02</t>
+          <t>2025/01</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>32513.967795</v>
+        <v>32516.151795</v>
       </c>
       <c r="E18" t="n">
         <v>2602</v>
       </c>
       <c r="F18" t="n">
-        <v>3.887482036713069</v>
+        <v>3.890402808732041</v>
       </c>
       <c r="G18" t="n">
-        <v>26143.706</v>
+        <v>26145.89</v>
       </c>
       <c r="H18" t="n">
-        <v>39.05964160188612</v>
+        <v>39.0922536098382</v>
       </c>
       <c r="I18" t="n">
         <v>10600</v>
       </c>
       <c r="J18" t="n">
-        <v>15.83678308576423</v>
+        <v>15.84868169583383</v>
       </c>
       <c r="K18" t="n">
-        <v>1590.304</v>
+        <v>1592.488</v>
       </c>
       <c r="L18" t="n">
-        <v>2.375971649851246</v>
+        <v>2.381022209097644</v>
       </c>
       <c r="M18" t="n">
         <v>13953.402</v>
       </c>
       <c r="N18" t="n">
-        <v>20.84688686627064</v>
+        <v>20.86254970490672</v>
       </c>
       <c r="O18" t="n">
         <v>951</v>
       </c>
       <c r="P18" t="n">
-        <v>1.420828369298282</v>
+        <v>1.421895876673394</v>
       </c>
       <c r="Q18" t="n">
         <v>2817.261795</v>
       </c>
       <c r="R18" t="n">
-        <v>4.209090938040168</v>
+        <v>4.212253343659289</v>
       </c>
       <c r="S18" t="n">
         <v>2076.328</v>
       </c>
       <c r="T18" t="n">
-        <v>3.102109070839498</v>
+        <v>3.104439770579931</v>
       </c>
       <c r="U18" t="n">
         <v>0.84</v>
       </c>
       <c r="V18" t="n">
-        <v>0.00125499035774</v>
+        <v>0.001255933266462</v>
       </c>
       <c r="W18" t="n">
         <v>291.653795</v>
       </c>
       <c r="X18" t="n">
-        <v>0.435741310146693</v>
+        <v>0.436068694560092</v>
       </c>
       <c r="Y18" t="n">
         <v>448.44</v>
       </c>
       <c r="Z18" t="n">
-        <v>0.669985566696237</v>
+        <v>0.670488945252804</v>
       </c>
       <c r="AA18" t="inlineStr"/>
       <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr"/>
       <c r="AE18" t="n">
-        <v>48.57704294593764</v>
+        <v>48.61680563890292</v>
       </c>
     </row>
     <row r="19">
@@ -2254,89 +2260,89 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>03月</t>
+          <t>02月</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2025/03</t>
+          <t>2025/02</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>32515.613795</v>
+        <v>32513.967795</v>
       </c>
       <c r="E19" t="n">
         <v>2602</v>
       </c>
       <c r="F19" t="n">
-        <v>3.880977720585138</v>
+        <v>3.887482054717989</v>
       </c>
       <c r="G19" t="n">
-        <v>26145.352</v>
+        <v>26143.706</v>
       </c>
       <c r="H19" t="n">
-        <v>38.99674427703923</v>
+        <v>39.05964178279133</v>
       </c>
       <c r="I19" t="n">
         <v>10600</v>
       </c>
       <c r="J19" t="n">
-        <v>15.81028587171501</v>
+        <v>15.83678315911249</v>
       </c>
       <c r="K19" t="n">
-        <v>1591.95</v>
+        <v>1590.304</v>
       </c>
       <c r="L19" t="n">
-        <v>2.374451376743086</v>
+        <v>2.375971660855587</v>
       </c>
       <c r="M19" t="n">
         <v>13953.402</v>
       </c>
       <c r="N19" t="n">
-        <v>20.81200702858113</v>
+        <v>20.84688696282325</v>
       </c>
       <c r="O19" t="n">
         <v>951</v>
       </c>
       <c r="P19" t="n">
-        <v>1.418451119245375</v>
+        <v>1.420828375878865</v>
       </c>
       <c r="Q19" t="n">
         <v>2817.261795</v>
       </c>
       <c r="R19" t="n">
-        <v>4.202048524001036</v>
+        <v>4.209090957534624</v>
       </c>
       <c r="S19" t="n">
         <v>2076.328</v>
       </c>
       <c r="T19" t="n">
-        <v>3.096918796551537</v>
+        <v>3.102109085206954</v>
       </c>
       <c r="U19" t="n">
         <v>0.84</v>
       </c>
       <c r="V19" t="n">
-        <v>0.001252890578513</v>
+        <v>0.001254990363552</v>
       </c>
       <c r="W19" t="n">
         <v>291.653795</v>
       </c>
       <c r="X19" t="n">
-        <v>0.435012252313261</v>
+        <v>0.435741312164834</v>
       </c>
       <c r="Y19" t="n">
         <v>448.44</v>
       </c>
       <c r="Z19" t="n">
-        <v>0.668864584557724</v>
+        <v>0.669985569799283</v>
       </c>
       <c r="AA19" t="inlineStr"/>
       <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr"/>
       <c r="AE19" t="n">
-        <v>48.49822164087078</v>
+        <v>48.57704317092281</v>
       </c>
     </row>
     <row r="20">
@@ -2347,89 +2353,89 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>04月</t>
+          <t>03月</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2025/04</t>
+          <t>2025/03</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>31743.613795</v>
+        <v>32515.613795</v>
       </c>
       <c r="E20" t="n">
         <v>2602</v>
       </c>
       <c r="F20" t="n">
-        <v>3.919492823504564</v>
+        <v>3.880977738529859</v>
       </c>
       <c r="G20" t="n">
-        <v>25373.352</v>
+        <v>26145.352</v>
       </c>
       <c r="H20" t="n">
-        <v>38.22085744514034</v>
+        <v>38.99674445735093</v>
       </c>
       <c r="I20" t="n">
         <v>10600</v>
       </c>
       <c r="J20" t="n">
-        <v>15.9671882894498</v>
+        <v>15.81028594481803</v>
       </c>
       <c r="K20" t="n">
         <v>1591.95</v>
       </c>
       <c r="L20" t="n">
-        <v>2.398015603527321</v>
+        <v>2.374451387721986</v>
       </c>
       <c r="M20" t="n">
-        <v>13181.402</v>
+        <v>13953.402</v>
       </c>
       <c r="N20" t="n">
-        <v>19.85565355216322</v>
+        <v>20.81200712481092</v>
       </c>
       <c r="O20" t="n">
         <v>951</v>
       </c>
       <c r="P20" t="n">
-        <v>1.432527930496864</v>
+        <v>1.418451125803957</v>
       </c>
       <c r="Q20" t="n">
         <v>2817.261795</v>
       </c>
       <c r="R20" t="n">
-        <v>4.243749956739464</v>
+        <v>4.202048543430312</v>
       </c>
       <c r="S20" t="n">
         <v>2076.328</v>
       </c>
       <c r="T20" t="n">
-        <v>3.127652842137427</v>
+        <v>3.096918810870955</v>
       </c>
       <c r="U20" t="n">
         <v>0.84</v>
       </c>
       <c r="V20" t="n">
-        <v>0.001265324355013</v>
+        <v>0.001252890584306</v>
       </c>
       <c r="W20" t="n">
         <v>291.653795</v>
       </c>
       <c r="X20" t="n">
-        <v>0.439329345292226</v>
+        <v>0.435012254324655</v>
       </c>
       <c r="Y20" t="n">
         <v>448.44</v>
       </c>
       <c r="Z20" t="n">
-        <v>0.6755024449547991</v>
+        <v>0.668864587650396</v>
       </c>
       <c r="AA20" t="inlineStr"/>
       <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr"/>
       <c r="AE20" t="n">
-        <v>47.81662815588124</v>
+        <v>48.49822186511506</v>
       </c>
     </row>
     <row r="21">
@@ -2440,12 +2446,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>05月</t>
+          <t>04月</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2025/05</t>
+          <t>2025/04</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -2455,74 +2461,74 @@
         <v>2602</v>
       </c>
       <c r="F21" t="n">
-        <v>3.849809121550143</v>
+        <v>3.919590556817985</v>
       </c>
       <c r="G21" t="n">
         <v>25373.352</v>
       </c>
       <c r="H21" t="n">
-        <v>37.54133819135379</v>
+        <v>38.22181048963056</v>
       </c>
       <c r="I21" t="n">
         <v>10600</v>
       </c>
       <c r="J21" t="n">
-        <v>15.6833115635786</v>
+        <v>15.96758643438533</v>
       </c>
       <c r="K21" t="n">
         <v>1591.95</v>
       </c>
       <c r="L21" t="n">
-        <v>2.35538187204141</v>
+        <v>2.398075398511295</v>
       </c>
       <c r="M21" t="n">
         <v>13181.402</v>
       </c>
       <c r="N21" t="n">
-        <v>19.50264475573378</v>
+        <v>19.85614865673393</v>
       </c>
       <c r="O21" t="n">
         <v>951</v>
       </c>
       <c r="P21" t="n">
-        <v>1.407059367638042</v>
+        <v>1.432563650858533</v>
       </c>
       <c r="Q21" t="n">
         <v>2817.261795</v>
       </c>
       <c r="R21" t="n">
-        <v>4.168301366712424</v>
+        <v>4.243855775467365</v>
       </c>
       <c r="S21" t="n">
         <v>2076.328</v>
       </c>
       <c r="T21" t="n">
-        <v>3.072047069073775</v>
+        <v>3.127730830767399</v>
       </c>
       <c r="U21" t="n">
         <v>0.84</v>
       </c>
       <c r="V21" t="n">
-        <v>0.001242828463529</v>
+        <v>0.001265355906121</v>
       </c>
       <c r="W21" t="n">
         <v>291.653795</v>
       </c>
       <c r="X21" t="n">
-        <v>0.431518616574064</v>
+        <v>0.439340300054623</v>
       </c>
       <c r="Y21" t="n">
         <v>448.44</v>
       </c>
       <c r="Z21" t="n">
-        <v>0.6634928526010549</v>
+        <v>0.675519288739222</v>
       </c>
       <c r="AA21" t="inlineStr"/>
       <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr"/>
       <c r="AE21" t="n">
-        <v>46.96650804725439</v>
+        <v>47.81782047277444</v>
       </c>
     </row>
     <row r="22">
@@ -2533,89 +2539,89 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>06月</t>
+          <t>05月</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2025/06</t>
+          <t>2025/05</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>30791.113795</v>
+        <v>31743.613795</v>
       </c>
       <c r="E22" t="n">
         <v>2602</v>
       </c>
       <c r="F22" t="n">
-        <v>3.89610954329838</v>
+        <v>3.8478731452884</v>
       </c>
       <c r="G22" t="n">
         <v>25373.352</v>
       </c>
       <c r="H22" t="n">
-        <v>37.99283584652922</v>
+        <v>37.52245955678313</v>
       </c>
       <c r="I22" t="n">
         <v>10600</v>
       </c>
       <c r="J22" t="n">
-        <v>15.87192973057757</v>
+        <v>15.67542480401885</v>
       </c>
       <c r="K22" t="n">
         <v>1591.95</v>
       </c>
       <c r="L22" t="n">
-        <v>2.383709295716317</v>
+        <v>2.354197407241302</v>
       </c>
       <c r="M22" t="n">
         <v>13181.402</v>
       </c>
       <c r="N22" t="n">
-        <v>19.73719682023534</v>
+        <v>19.49283734552298</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>951</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1.406351791379426</v>
       </c>
       <c r="Q22" t="n">
-        <v>2815.761795</v>
+        <v>2817.261795</v>
       </c>
       <c r="R22" t="n">
-        <v>4.216186164932543</v>
+        <v>4.166205228373363</v>
       </c>
       <c r="S22" t="n">
         <v>2076.328</v>
       </c>
       <c r="T22" t="n">
-        <v>3.108993595625534</v>
+        <v>3.070502210611212</v>
       </c>
       <c r="U22" t="n">
         <v>0.84</v>
       </c>
       <c r="V22" t="n">
-        <v>0.001257775563555</v>
+        <v>0.001242203475035</v>
       </c>
       <c r="W22" t="n">
         <v>291.653795</v>
       </c>
       <c r="X22" t="n">
-        <v>0.436708352820403</v>
+        <v>0.431301616257474</v>
       </c>
       <c r="Y22" t="n">
-        <v>446.94</v>
+        <v>448.44</v>
       </c>
       <c r="Z22" t="n">
-        <v>0.6692264409230509</v>
+        <v>0.663159198029642</v>
       </c>
       <c r="AA22" t="inlineStr"/>
       <c r="AB22" t="inlineStr"/>
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr"/>
       <c r="AE22" t="n">
-        <v>46.10513155476015</v>
+        <v>46.94288972182432</v>
       </c>
     </row>
     <row r="23">
@@ -2626,46 +2632,46 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>07月</t>
+          <t>06月</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2025/07</t>
+          <t>2025/06</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>31916.742795</v>
+        <v>30791.113795</v>
       </c>
       <c r="E23" t="n">
         <v>2602</v>
       </c>
       <c r="F23" t="n">
-        <v>3.821296510557152</v>
+        <v>3.896027607475386</v>
       </c>
       <c r="G23" t="n">
-        <v>26498.981</v>
+        <v>25373.352</v>
       </c>
       <c r="H23" t="n">
-        <v>38.91639647525759</v>
+        <v>37.99203685095726</v>
       </c>
       <c r="I23" t="n">
         <v>10600</v>
       </c>
       <c r="J23" t="n">
-        <v>15.56715719135504</v>
+        <v>15.87159594129096</v>
       </c>
       <c r="K23" t="n">
-        <v>1593.95</v>
+        <v>1591.95</v>
       </c>
       <c r="L23" t="n">
-        <v>2.340874547656637</v>
+        <v>2.383659165918693</v>
       </c>
       <c r="M23" t="n">
-        <v>14305.031</v>
+        <v>13181.402</v>
       </c>
       <c r="N23" t="n">
-        <v>21.00836473624592</v>
+        <v>19.73678174374761</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -2677,38 +2683,38 @@
         <v>2815.761795</v>
       </c>
       <c r="R23" t="n">
-        <v>4.135227026054435</v>
+        <v>4.216097497845676</v>
       </c>
       <c r="S23" t="n">
         <v>2076.328</v>
       </c>
       <c r="T23" t="n">
-        <v>3.049294750642625</v>
+        <v>3.108928212980074</v>
       </c>
       <c r="U23" t="n">
         <v>0.84</v>
       </c>
       <c r="V23" t="n">
-        <v>0.001233623777428</v>
+        <v>0.001257749112329</v>
       </c>
       <c r="W23" t="n">
         <v>291.653795</v>
       </c>
       <c r="X23" t="n">
-        <v>0.428322686058513</v>
+        <v>0.436699168772086</v>
       </c>
       <c r="Y23" t="n">
         <v>446.94</v>
       </c>
       <c r="Z23" t="n">
-        <v>0.65637596557587</v>
+        <v>0.669212366981187</v>
       </c>
       <c r="AA23" t="inlineStr"/>
       <c r="AB23" t="inlineStr"/>
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr"/>
       <c r="AE23" t="n">
-        <v>46.87292001186918</v>
+        <v>46.10416195627833</v>
       </c>
     </row>
     <row r="24">
@@ -2719,46 +2725,46 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>08月</t>
+          <t>07月</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2025/08</t>
+          <t>2025/07</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>31914.927995</v>
+        <v>31916.742795</v>
       </c>
       <c r="E24" t="n">
         <v>2602</v>
       </c>
       <c r="F24" t="n">
-        <v>3.812919373477834</v>
+        <v>3.821189848227349</v>
       </c>
       <c r="G24" t="n">
         <v>26498.981</v>
       </c>
       <c r="H24" t="n">
-        <v>38.83108302548847</v>
+        <v>38.91531021735948</v>
       </c>
       <c r="I24" t="n">
         <v>10600</v>
       </c>
       <c r="J24" t="n">
-        <v>15.53303049917949</v>
+        <v>15.56672267148728</v>
       </c>
       <c r="K24" t="n">
         <v>1593.95</v>
       </c>
       <c r="L24" t="n">
-        <v>2.335742826808221</v>
+        <v>2.340809207756334</v>
       </c>
       <c r="M24" t="n">
         <v>14305.031</v>
       </c>
       <c r="N24" t="n">
-        <v>20.96230969950076</v>
+        <v>21.00777833811588</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -2767,41 +2773,41 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>2813.946995</v>
+        <v>2815.761795</v>
       </c>
       <c r="R24" t="n">
-        <v>4.123502310982025</v>
+        <v>4.135111601107001</v>
       </c>
       <c r="S24" t="n">
         <v>2076.328</v>
       </c>
       <c r="T24" t="n">
-        <v>3.042610014179278</v>
+        <v>3.049209636890927</v>
       </c>
       <c r="U24" t="n">
         <v>0.84</v>
       </c>
       <c r="V24" t="n">
-        <v>0.001230919398048</v>
+        <v>0.001233589343778</v>
       </c>
       <c r="W24" t="n">
-        <v>292.238995</v>
+        <v>291.653795</v>
       </c>
       <c r="X24" t="n">
-        <v>0.42824124739477</v>
+        <v>0.428310730457717</v>
       </c>
       <c r="Y24" t="n">
-        <v>444.54</v>
+        <v>446.94</v>
       </c>
       <c r="Z24" t="n">
-        <v>0.651420130009929</v>
+        <v>0.656357644414578</v>
       </c>
       <c r="AA24" t="inlineStr"/>
       <c r="AB24" t="inlineStr"/>
       <c r="AC24" t="inlineStr"/>
       <c r="AD24" t="inlineStr"/>
       <c r="AE24" t="n">
-        <v>46.76750470994833</v>
+        <v>46.87161166669384</v>
       </c>
     </row>
     <row r="25">
@@ -2812,46 +2818,46 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>09月</t>
+          <t>08月</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2025/09</t>
+          <t>2025/08</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>31913.927995</v>
+        <v>31914.927995</v>
       </c>
       <c r="E25" t="n">
         <v>2602</v>
       </c>
       <c r="F25" t="n">
-        <v>3.804023615984386</v>
+        <v>3.812952053206708</v>
       </c>
       <c r="G25" t="n">
-        <v>26497.981</v>
+        <v>26498.981</v>
       </c>
       <c r="H25" t="n">
-        <v>38.7390259415471</v>
+        <v>38.8314158385225</v>
       </c>
       <c r="I25" t="n">
         <v>10600</v>
       </c>
       <c r="J25" t="n">
-        <v>15.49679105666199</v>
+        <v>15.53316362951234</v>
       </c>
       <c r="K25" t="n">
-        <v>1592.95</v>
+        <v>1593.95</v>
       </c>
       <c r="L25" t="n">
-        <v>2.328831444689596</v>
+        <v>2.335762845968037</v>
       </c>
       <c r="M25" t="n">
         <v>14305.031</v>
       </c>
       <c r="N25" t="n">
-        <v>20.91340344019552</v>
+        <v>20.96248936304213</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -2863,38 +2869,38 @@
         <v>2813.946995</v>
       </c>
       <c r="R25" t="n">
-        <v>4.113881945852536</v>
+        <v>4.123537652651843</v>
       </c>
       <c r="S25" t="n">
         <v>2076.328</v>
       </c>
       <c r="T25" t="n">
-        <v>3.03551143217895</v>
+        <v>3.042636091748878</v>
       </c>
       <c r="U25" t="n">
         <v>0.84</v>
       </c>
       <c r="V25" t="n">
-        <v>0.001228047593169</v>
+        <v>0.001230929947999</v>
       </c>
       <c r="W25" t="n">
         <v>292.238995</v>
       </c>
       <c r="X25" t="n">
-        <v>0.427242136238103</v>
+        <v>0.428244917760306</v>
       </c>
       <c r="Y25" t="n">
         <v>444.54</v>
       </c>
       <c r="Z25" t="n">
-        <v>0.6499003298423131</v>
+        <v>0.651425713194662</v>
       </c>
       <c r="AA25" t="inlineStr"/>
       <c r="AB25" t="inlineStr"/>
       <c r="AC25" t="inlineStr"/>
       <c r="AD25" t="inlineStr"/>
       <c r="AE25" t="n">
-        <v>46.65693150338402</v>
+        <v>46.76790554438106</v>
       </c>
     </row>
     <row r="26">
@@ -2905,46 +2911,46 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>10月</t>
+          <t>09月</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2025/10</t>
+          <t>2025/09</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>31911.527995</v>
+        <v>31913.927995</v>
       </c>
       <c r="E26" t="n">
         <v>2602</v>
       </c>
       <c r="F26" t="n">
-        <v>3.794054484607876</v>
+        <v>3.804023640454263</v>
       </c>
       <c r="G26" t="n">
         <v>26497.981</v>
       </c>
       <c r="H26" t="n">
-        <v>38.63750332286867</v>
+        <v>38.73902619074092</v>
       </c>
       <c r="I26" t="n">
         <v>10600</v>
       </c>
       <c r="J26" t="n">
-        <v>15.45617891500518</v>
+        <v>15.49679115634711</v>
       </c>
       <c r="K26" t="n">
         <v>1592.95</v>
       </c>
       <c r="L26" t="n">
-        <v>2.322728321005425</v>
+        <v>2.328831459670107</v>
       </c>
       <c r="M26" t="n">
         <v>14305.031</v>
       </c>
       <c r="N26" t="n">
-        <v>20.85859608685807</v>
+        <v>20.91340357472371</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -2953,41 +2959,41 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>2811.546995</v>
+        <v>2813.946995</v>
       </c>
       <c r="R26" t="n">
-        <v>4.099601262515584</v>
+        <v>4.113881972315617</v>
       </c>
       <c r="S26" t="n">
         <v>2076.328</v>
       </c>
       <c r="T26" t="n">
-        <v>3.027556325871215</v>
+        <v>3.035511451705273</v>
       </c>
       <c r="U26" t="n">
         <v>0.84</v>
       </c>
       <c r="V26" t="n">
-        <v>0.00122482927251</v>
+        <v>0.001228047601069</v>
       </c>
       <c r="W26" t="n">
         <v>292.238995</v>
       </c>
       <c r="X26" t="n">
-        <v>0.426122471005784</v>
+        <v>0.427242138986393</v>
       </c>
       <c r="Y26" t="n">
-        <v>442.14</v>
+        <v>444.54</v>
       </c>
       <c r="Z26" t="n">
-        <v>0.644697636366075</v>
+        <v>0.6499003340228821</v>
       </c>
       <c r="AA26" t="inlineStr"/>
       <c r="AB26" t="inlineStr"/>
       <c r="AC26" t="inlineStr"/>
       <c r="AD26" t="inlineStr"/>
       <c r="AE26" t="n">
-        <v>46.53115906999214</v>
+        <v>46.65693180351081</v>
       </c>
     </row>
     <row r="27">
@@ -2998,12 +3004,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>11月</t>
+          <t>10月</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2025/11</t>
+          <t>2025/10</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -3013,31 +3019,31 @@
         <v>2602</v>
       </c>
       <c r="F27" t="n">
-        <v>3.7873017046402</v>
+        <v>3.794054502310996</v>
       </c>
       <c r="G27" t="n">
         <v>26497.981</v>
       </c>
       <c r="H27" t="n">
-        <v>38.5687350541213</v>
+        <v>38.63750350315189</v>
       </c>
       <c r="I27" t="n">
         <v>10600</v>
       </c>
       <c r="J27" t="n">
-        <v>15.42866951160112</v>
+        <v>15.45617898712396</v>
       </c>
       <c r="K27" t="n">
         <v>1592.95</v>
       </c>
       <c r="L27" t="n">
-        <v>2.318594254575944</v>
+        <v>2.322728331843313</v>
       </c>
       <c r="M27" t="n">
         <v>14305.031</v>
       </c>
       <c r="N27" t="n">
-        <v>20.82147128794423</v>
+        <v>20.85859618418461</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3049,38 +3055,38 @@
         <v>2811.546995</v>
       </c>
       <c r="R27" t="n">
-        <v>4.092304660583987</v>
+        <v>4.09960128164439</v>
       </c>
       <c r="S27" t="n">
         <v>2076.328</v>
       </c>
       <c r="T27" t="n">
-        <v>3.022167783932428</v>
+        <v>3.027556339997842</v>
       </c>
       <c r="U27" t="n">
         <v>0.84</v>
       </c>
       <c r="V27" t="n">
-        <v>0.001222649282051</v>
+        <v>0.001224829278225</v>
       </c>
       <c r="W27" t="n">
         <v>292.238995</v>
       </c>
       <c r="X27" t="n">
-        <v>0.42536404455259</v>
+        <v>0.426122472994078</v>
       </c>
       <c r="Y27" t="n">
         <v>442.14</v>
       </c>
       <c r="Z27" t="n">
-        <v>0.643550182816917</v>
+        <v>0.644697639374244</v>
       </c>
       <c r="AA27" t="inlineStr"/>
       <c r="AB27" t="inlineStr"/>
       <c r="AC27" t="inlineStr"/>
       <c r="AD27" t="inlineStr"/>
       <c r="AE27" t="n">
-        <v>46.4483414193455</v>
+        <v>46.53115928710728</v>
       </c>
     </row>
     <row r="28">
@@ -3091,46 +3097,46 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>12月</t>
+          <t>11月</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2025/12</t>
+          <t>2025/11</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>32661.527995</v>
+        <v>31911.527995</v>
       </c>
       <c r="E28" t="n">
         <v>2602</v>
       </c>
       <c r="F28" t="n">
-        <v>3.724672836875404</v>
+        <v>3.787301722280359</v>
       </c>
       <c r="G28" t="n">
-        <v>27247.981</v>
+        <v>26497.981</v>
       </c>
       <c r="H28" t="n">
-        <v>39.00454061890741</v>
+        <v>38.56873523376334</v>
       </c>
       <c r="I28" t="n">
-        <v>10050</v>
+        <v>10600</v>
       </c>
       <c r="J28" t="n">
-        <v>14.38622675272782</v>
+        <v>15.42866958346342</v>
       </c>
       <c r="K28" t="n">
         <v>1592.95</v>
       </c>
       <c r="L28" t="n">
-        <v>2.280252726941074</v>
+        <v>2.318594265375287</v>
       </c>
       <c r="M28" t="n">
-        <v>15605.031</v>
+        <v>14305.031</v>
       </c>
       <c r="N28" t="n">
-        <v>22.33806113923851</v>
+        <v>20.82147138492464</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3142,38 +3148,38 @@
         <v>2811.546995</v>
       </c>
       <c r="R28" t="n">
-        <v>4.02463209910652</v>
+        <v>4.09230467964476</v>
       </c>
       <c r="S28" t="n">
         <v>2076.328</v>
       </c>
       <c r="T28" t="n">
-        <v>2.972191584182872</v>
+        <v>3.022167798008813</v>
       </c>
       <c r="U28" t="n">
         <v>0.84</v>
       </c>
       <c r="V28" t="n">
-        <v>0.001202430892765</v>
+        <v>0.001222649287746</v>
       </c>
       <c r="W28" t="n">
         <v>292.238995</v>
       </c>
       <c r="X28" t="n">
-        <v>0.41832999483177</v>
+        <v>0.425364046533813</v>
       </c>
       <c r="Y28" t="n">
         <v>442.14</v>
       </c>
       <c r="Z28" t="n">
-        <v>0.632908089199113</v>
+        <v>0.6435501858143881</v>
       </c>
       <c r="AA28" t="inlineStr"/>
       <c r="AB28" t="inlineStr"/>
       <c r="AC28" t="inlineStr"/>
       <c r="AD28" t="inlineStr"/>
       <c r="AE28" t="n">
-        <v>46.75384555488934</v>
+        <v>46.44834163568846</v>
       </c>
     </row>
     <row r="29">
@@ -3184,46 +3190,46 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>01月</t>
+          <t>12月</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026/01</t>
+          <t>2025/12</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>32977.669995</v>
+        <v>32661.527995</v>
       </c>
       <c r="E29" t="n">
         <v>2602</v>
       </c>
       <c r="F29" t="n">
-        <v>3.701131377042136</v>
+        <v>3.724672853936972</v>
       </c>
       <c r="G29" t="n">
-        <v>27564.123</v>
+        <v>27247.981</v>
       </c>
       <c r="H29" t="n">
-        <v>39.2077019661602</v>
+        <v>39.00454079757509</v>
       </c>
       <c r="I29" t="n">
         <v>10050</v>
       </c>
       <c r="J29" t="n">
-        <v>14.29529989979764</v>
+        <v>14.38622681862666</v>
       </c>
       <c r="K29" t="n">
-        <v>1595.95</v>
+        <v>1592.95</v>
       </c>
       <c r="L29" t="n">
-        <v>2.270107848266871</v>
+        <v>2.280252737386203</v>
       </c>
       <c r="M29" t="n">
-        <v>15918.173</v>
+        <v>15605.031</v>
       </c>
       <c r="N29" t="n">
-        <v>22.64229421809568</v>
+        <v>22.33806124156223</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3235,38 +3241,38 @@
         <v>2811.546995</v>
       </c>
       <c r="R29" t="n">
-        <v>3.999194773721381</v>
+        <v>4.024632117542109</v>
       </c>
       <c r="S29" t="n">
         <v>2076.328</v>
       </c>
       <c r="T29" t="n">
-        <v>2.953406114462392</v>
+        <v>2.972191597797557</v>
       </c>
       <c r="U29" t="n">
         <v>0.84</v>
       </c>
       <c r="V29" t="n">
-        <v>0.001194831036401</v>
+        <v>0.001202430898273</v>
       </c>
       <c r="W29" t="n">
         <v>292.238995</v>
       </c>
       <c r="X29" t="n">
-        <v>0.415685977705519</v>
+        <v>0.41832999674801</v>
       </c>
       <c r="Y29" t="n">
         <v>442.14</v>
       </c>
       <c r="Z29" t="n">
-        <v>0.628907850517068</v>
+        <v>0.632908092098268</v>
       </c>
       <c r="AA29" t="inlineStr"/>
       <c r="AB29" t="inlineStr"/>
       <c r="AC29" t="inlineStr"/>
       <c r="AD29" t="inlineStr"/>
       <c r="AE29" t="n">
-        <v>46.90802811692372</v>
+        <v>46.75384576905417</v>
       </c>
     </row>
     <row r="30">
@@ -3277,46 +3283,46 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>02月</t>
+          <t>01月</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026/02</t>
+          <t>2026/01</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>32993.752995</v>
+        <v>32977.669995</v>
       </c>
       <c r="E30" t="n">
         <v>2602</v>
       </c>
       <c r="F30" t="n">
-        <v>3.693554303106413</v>
+        <v>3.701131377042136</v>
       </c>
       <c r="G30" t="n">
         <v>27564.123</v>
       </c>
       <c r="H30" t="n">
-        <v>39.12743471099326</v>
+        <v>39.2077019661602</v>
       </c>
       <c r="I30" t="n">
         <v>10050</v>
       </c>
       <c r="J30" t="n">
-        <v>14.26603410692523</v>
+        <v>14.29529989979764</v>
       </c>
       <c r="K30" t="n">
         <v>1595.95</v>
       </c>
       <c r="L30" t="n">
-        <v>2.26546041123854</v>
+        <v>2.270107848266871</v>
       </c>
       <c r="M30" t="n">
         <v>15918.173</v>
       </c>
       <c r="N30" t="n">
-        <v>22.59594019282949</v>
+        <v>22.64229421809568</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -3325,41 +3331,41 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>2827.629995</v>
+        <v>2811.546995</v>
       </c>
       <c r="R30" t="n">
-        <v>4.013837408003464</v>
+        <v>3.999194773721381</v>
       </c>
       <c r="S30" t="n">
         <v>2076.328</v>
       </c>
       <c r="T30" t="n">
-        <v>2.94735980747899</v>
+        <v>2.953406114462392</v>
       </c>
       <c r="U30" t="n">
         <v>0.84</v>
       </c>
       <c r="V30" t="n">
-        <v>0.00119238494028</v>
+        <v>0.001194831036401</v>
       </c>
       <c r="W30" t="n">
-        <v>308.321995</v>
+        <v>292.238995</v>
       </c>
       <c r="X30" t="n">
-        <v>0.437664885232361</v>
+        <v>0.415685977705519</v>
       </c>
       <c r="Y30" t="n">
         <v>442.14</v>
       </c>
       <c r="Z30" t="n">
-        <v>0.627620330351833</v>
+        <v>0.628907850517068</v>
       </c>
       <c r="AA30" t="inlineStr"/>
       <c r="AB30" t="inlineStr"/>
       <c r="AC30" t="inlineStr"/>
       <c r="AD30" t="inlineStr"/>
       <c r="AE30" t="n">
-        <v>46.83482642210313</v>
+        <v>46.90802811692372</v>
       </c>
     </row>
     <row r="31">
@@ -3370,12 +3376,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>03月</t>
+          <t>02月</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026/03</t>
+          <t>2026/02</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -3385,31 +3391,31 @@
         <v>2602</v>
       </c>
       <c r="F31" t="n">
-        <v>3.676246830763415</v>
+        <v>3.693554303106413</v>
       </c>
       <c r="G31" t="n">
         <v>27564.123</v>
       </c>
       <c r="H31" t="n">
-        <v>38.94408909359069</v>
+        <v>39.12743471099326</v>
       </c>
       <c r="I31" t="n">
         <v>10050</v>
       </c>
       <c r="J31" t="n">
-        <v>14.19918549161119</v>
+        <v>14.26603410692523</v>
       </c>
       <c r="K31" t="n">
         <v>1595.95</v>
       </c>
       <c r="L31" t="n">
-        <v>2.254844784610635</v>
+        <v>2.26546041123854</v>
       </c>
       <c r="M31" t="n">
         <v>15918.173</v>
       </c>
       <c r="N31" t="n">
-        <v>22.49005881736885</v>
+        <v>22.59594019282949</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -3421,200 +3427,224 @@
         <v>2827.629995</v>
       </c>
       <c r="R31" t="n">
-        <v>3.995029134392898</v>
+        <v>4.013837408003464</v>
       </c>
       <c r="S31" t="n">
         <v>2076.328</v>
       </c>
       <c r="T31" t="n">
-        <v>2.933548896858317</v>
+        <v>2.94735980747899</v>
       </c>
       <c r="U31" t="n">
         <v>0.84</v>
       </c>
       <c r="V31" t="n">
-        <v>0.001186797593329</v>
+        <v>0.00119238494028</v>
       </c>
       <c r="W31" t="n">
         <v>308.321995</v>
       </c>
       <c r="X31" t="n">
-        <v>0.435614049567027</v>
+        <v>0.437664885232361</v>
       </c>
       <c r="Y31" t="n">
         <v>442.14</v>
       </c>
       <c r="Z31" t="n">
-        <v>0.624679390374226</v>
+        <v>0.627620330351833</v>
       </c>
       <c r="AA31" t="inlineStr"/>
       <c r="AB31" t="inlineStr"/>
       <c r="AC31" t="inlineStr"/>
       <c r="AD31" t="inlineStr"/>
       <c r="AE31" t="n">
-        <v>46.615365058747</v>
+        <v>46.83482642210313</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>民營電廠</t>
+          <t>台電</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>01月</t>
+          <t>03月</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2025/01</t>
+          <t>2026/03</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>15498.082196</v>
-      </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
+        <v>32993.752995</v>
+      </c>
+      <c r="E32" t="n">
+        <v>2602</v>
+      </c>
+      <c r="F32" t="n">
+        <v>3.676246830763415</v>
+      </c>
       <c r="G32" t="n">
-        <v>8763.280000000001</v>
+        <v>27564.123</v>
       </c>
       <c r="H32" t="n">
-        <v>13.1024938051615</v>
+        <v>38.94408909359069</v>
       </c>
       <c r="I32" t="n">
-        <v>3120.3</v>
+        <v>10050</v>
       </c>
       <c r="J32" t="n">
-        <v>4.665343503830236</v>
-      </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
+        <v>14.19918549161119</v>
+      </c>
+      <c r="K32" t="n">
+        <v>1595.95</v>
+      </c>
+      <c r="L32" t="n">
+        <v>2.254844784610635</v>
+      </c>
       <c r="M32" t="n">
-        <v>5642.98</v>
+        <v>15918.173</v>
       </c>
       <c r="N32" t="n">
-        <v>8.437150301331265</v>
-      </c>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr"/>
+        <v>22.49005881736885</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
       <c r="Q32" t="n">
-        <v>6734.802196</v>
+        <v>2827.629995</v>
       </c>
       <c r="R32" t="n">
-        <v>10.06959769082787</v>
+        <v>3.995029134392898</v>
       </c>
       <c r="S32" t="n">
-        <v>42.335</v>
+        <v>2076.328</v>
       </c>
       <c r="T32" t="n">
-        <v>0.06329754101677799</v>
+        <v>2.933548896858317</v>
       </c>
       <c r="U32" t="n">
-        <v>4.2</v>
+        <v>0.84</v>
       </c>
       <c r="V32" t="n">
-        <v>0.006279666287244</v>
+        <v>0.001186797593329</v>
       </c>
       <c r="W32" t="n">
-        <v>3179.474196</v>
+        <v>308.321995</v>
       </c>
       <c r="X32" t="n">
-        <v>4.753818314234037</v>
+        <v>0.435614049567027</v>
       </c>
       <c r="Y32" t="n">
-        <v>3508.793</v>
+        <v>442.14</v>
       </c>
       <c r="Z32" t="n">
-        <v>5.246202169289814</v>
+        <v>0.624679390374226</v>
       </c>
       <c r="AA32" t="inlineStr"/>
       <c r="AB32" t="inlineStr"/>
       <c r="AC32" t="inlineStr"/>
       <c r="AD32" t="inlineStr"/>
       <c r="AE32" t="n">
-        <v>23.17209149598937</v>
+        <v>46.615365058747</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>民營電廠</t>
+          <t>台電</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>02月</t>
+          <t>04月</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2025/02</t>
+          <t>2026/04</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>15543.443571</v>
-      </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
+        <v>32993.752995</v>
+      </c>
+      <c r="E33" t="n">
+        <v>2602</v>
+      </c>
+      <c r="F33" t="n">
+        <v>3.66460910172093</v>
+      </c>
       <c r="G33" t="n">
-        <v>8763.280000000001</v>
+        <v>27564.123</v>
       </c>
       <c r="H33" t="n">
-        <v>13.09265702639773</v>
+        <v>38.82080554448702</v>
       </c>
       <c r="I33" t="n">
-        <v>3120.3</v>
+        <v>10050</v>
       </c>
       <c r="J33" t="n">
-        <v>4.661840968161333</v>
-      </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
+        <v>14.15423576952166</v>
+      </c>
+      <c r="K33" t="n">
+        <v>1595.95</v>
+      </c>
+      <c r="L33" t="n">
+        <v>2.247706724016725</v>
+      </c>
       <c r="M33" t="n">
-        <v>5642.98</v>
+        <v>15918.173</v>
       </c>
       <c r="N33" t="n">
-        <v>8.430816058236402</v>
-      </c>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
+        <v>22.41886305094864</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
       <c r="Q33" t="n">
-        <v>6780.163571</v>
+        <v>2827.629995</v>
       </c>
       <c r="R33" t="n">
-        <v>10.12980941131393</v>
+        <v>3.982382250567297</v>
       </c>
       <c r="S33" t="n">
-        <v>42.335</v>
+        <v>2076.328</v>
       </c>
       <c r="T33" t="n">
-        <v>0.063250019993946</v>
+        <v>2.924262293219837</v>
       </c>
       <c r="U33" t="n">
-        <v>4.2</v>
+        <v>0.84</v>
       </c>
       <c r="V33" t="n">
-        <v>0.006274951788699</v>
+        <v>0.001183040601632</v>
       </c>
       <c r="W33" t="n">
-        <v>3208.835571</v>
+        <v>308.321995</v>
       </c>
       <c r="X33" t="n">
-        <v>4.794116310925605</v>
+        <v>0.434235045786993</v>
       </c>
       <c r="Y33" t="n">
-        <v>3524.793</v>
+        <v>442.14</v>
       </c>
       <c r="Z33" t="n">
-        <v>5.266168128605676</v>
+        <v>0.622701870958836</v>
       </c>
       <c r="AA33" t="inlineStr"/>
       <c r="AB33" t="inlineStr"/>
       <c r="AC33" t="inlineStr"/>
       <c r="AD33" t="inlineStr"/>
       <c r="AE33" t="n">
-        <v>23.22246643771166</v>
+        <v>46.46779689677525</v>
       </c>
     </row>
     <row r="34">
@@ -3625,16 +3655,16 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>03月</t>
+          <t>01月</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2025/03</t>
+          <t>2025/01</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>15548.261326</v>
+        <v>15498.083886</v>
       </c>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
@@ -3642,13 +3672,13 @@
         <v>8763.280000000001</v>
       </c>
       <c r="H34" t="n">
-        <v>13.07075112961158</v>
+        <v>13.10249389919497</v>
       </c>
       <c r="I34" t="n">
         <v>3120.3</v>
       </c>
       <c r="J34" t="n">
-        <v>4.654041038255882</v>
+        <v>4.665343537312293</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
@@ -3656,46 +3686,46 @@
         <v>5642.98</v>
       </c>
       <c r="N34" t="n">
-        <v>8.416710091355698</v>
+        <v>8.437150361882679</v>
       </c>
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="n">
-        <v>6784.981326</v>
+        <v>6734.803886</v>
       </c>
       <c r="R34" t="n">
-        <v>10.12004664134981</v>
+        <v>10.06960028991309</v>
       </c>
       <c r="S34" t="n">
         <v>42.335</v>
       </c>
       <c r="T34" t="n">
-        <v>0.06314419362066601</v>
+        <v>0.06329754147105</v>
       </c>
       <c r="U34" t="n">
         <v>4.2</v>
       </c>
       <c r="V34" t="n">
-        <v>0.006264452892566</v>
+        <v>0.006279666332312</v>
       </c>
       <c r="W34" t="n">
-        <v>3213.653326</v>
+        <v>3179.475886</v>
       </c>
       <c r="X34" t="n">
-        <v>4.79328092232526</v>
+        <v>4.753820875169175</v>
       </c>
       <c r="Y34" t="n">
-        <v>3524.793</v>
+        <v>3508.793</v>
       </c>
       <c r="Z34" t="n">
-        <v>5.257357072511318</v>
+        <v>5.246202206940555</v>
       </c>
       <c r="AA34" t="inlineStr"/>
       <c r="AB34" t="inlineStr"/>
       <c r="AC34" t="inlineStr"/>
       <c r="AD34" t="inlineStr"/>
       <c r="AE34" t="n">
-        <v>23.1907977709614</v>
+        <v>23.17209418910807</v>
       </c>
     </row>
     <row r="35">
@@ -3706,16 +3736,16 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>04月</t>
+          <t>02月</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2025/04</t>
+          <t>2025/02</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>15563.181481</v>
+        <v>15543.445261</v>
       </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
@@ -3723,13 +3753,13 @@
         <v>8763.280000000001</v>
       </c>
       <c r="H35" t="n">
-        <v>13.2004662069028</v>
+        <v>13.09265708703653</v>
       </c>
       <c r="I35" t="n">
         <v>3120.3</v>
       </c>
       <c r="J35" t="n">
-        <v>4.700228077317943</v>
+        <v>4.661840989752706</v>
       </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
@@ -3737,46 +3767,46 @@
         <v>5642.98</v>
       </c>
       <c r="N35" t="n">
-        <v>8.500238129584853</v>
+        <v>8.430816097283827</v>
       </c>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="n">
-        <v>6799.901481</v>
+        <v>6780.165261</v>
       </c>
       <c r="R35" t="n">
-        <v>10.24295351856939</v>
+        <v>10.12981198315135</v>
       </c>
       <c r="S35" t="n">
-        <v>43.991</v>
+        <v>42.335</v>
       </c>
       <c r="T35" t="n">
-        <v>0.066265337739735</v>
+        <v>0.063250020286889</v>
       </c>
       <c r="U35" t="n">
         <v>4.2</v>
       </c>
       <c r="V35" t="n">
-        <v>0.006326621775065</v>
+        <v>0.006274951817762</v>
       </c>
       <c r="W35" t="n">
-        <v>3226.917481</v>
+        <v>3208.837261</v>
       </c>
       <c r="X35" t="n">
-        <v>4.860830095626796</v>
+        <v>4.794118858050701</v>
       </c>
       <c r="Y35" t="n">
         <v>3524.793</v>
       </c>
       <c r="Z35" t="n">
-        <v>5.309531463427794</v>
+        <v>5.266168152995998</v>
       </c>
       <c r="AA35" t="inlineStr"/>
       <c r="AB35" t="inlineStr"/>
       <c r="AC35" t="inlineStr"/>
       <c r="AD35" t="inlineStr"/>
       <c r="AE35" t="n">
-        <v>23.44341972547219</v>
+        <v>23.22246907018788</v>
       </c>
     </row>
     <row r="36">
@@ -3787,77 +3817,77 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>05月</t>
+          <t>03月</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2025/05</t>
+          <t>2025/03</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>16639.047811</v>
+        <v>15548.263016</v>
       </c>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="n">
-        <v>9868.977999999999</v>
+        <v>8763.280000000001</v>
       </c>
       <c r="H36" t="n">
-        <v>14.60172233850026</v>
+        <v>13.07075119004763</v>
       </c>
       <c r="I36" t="n">
         <v>3120.3</v>
       </c>
       <c r="J36" t="n">
-        <v>4.616663874701348</v>
+        <v>4.654041059775064</v>
       </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="n">
-        <v>6748.678</v>
+        <v>5642.98</v>
       </c>
       <c r="N36" t="n">
-        <v>9.985058463798913</v>
+        <v>8.41671013027257</v>
       </c>
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr"/>
       <c r="Q36" t="n">
-        <v>6770.069811</v>
+        <v>6784.983016</v>
       </c>
       <c r="R36" t="n">
-        <v>10.01670888236704</v>
+        <v>10.12004920883904</v>
       </c>
       <c r="S36" t="n">
-        <v>43.991</v>
+        <v>42.335</v>
       </c>
       <c r="T36" t="n">
-        <v>0.065087222546546</v>
+        <v>0.063144193912629</v>
       </c>
       <c r="U36" t="n">
         <v>4.2</v>
       </c>
       <c r="V36" t="n">
-        <v>0.006214142317644</v>
+        <v>0.006264452921532</v>
       </c>
       <c r="W36" t="n">
-        <v>3197.085811</v>
+        <v>3213.655016</v>
       </c>
       <c r="X36" t="n">
-        <v>4.73027291220843</v>
+        <v>4.793283465184788</v>
       </c>
       <c r="Y36" t="n">
         <v>3524.793</v>
       </c>
       <c r="Z36" t="n">
-        <v>5.215134605294424</v>
+        <v>5.257357096820091</v>
       </c>
       <c r="AA36" t="inlineStr"/>
       <c r="AB36" t="inlineStr"/>
       <c r="AC36" t="inlineStr"/>
       <c r="AD36" t="inlineStr"/>
       <c r="AE36" t="n">
-        <v>24.61843122086731</v>
+        <v>23.19080039888668</v>
       </c>
     </row>
     <row r="37">
@@ -3868,77 +3898,77 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>06月</t>
+          <t>04月</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2025/06</t>
+          <t>2025/04</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>16681.159771</v>
+        <v>15561.527171</v>
       </c>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="n">
-        <v>9868.977999999999</v>
+        <v>8763.280000000001</v>
       </c>
       <c r="H37" t="n">
-        <v>14.77733257817132</v>
+        <v>13.20079536308682</v>
       </c>
       <c r="I37" t="n">
         <v>3120.3</v>
       </c>
       <c r="J37" t="n">
-        <v>4.672187013049168</v>
+        <v>4.700345278416278</v>
       </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="n">
-        <v>6748.678</v>
+        <v>5642.98</v>
       </c>
       <c r="N37" t="n">
-        <v>10.10514556512215</v>
+        <v>8.500450084670542</v>
       </c>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr"/>
       <c r="Q37" t="n">
-        <v>6812.181771</v>
+        <v>6798.247171</v>
       </c>
       <c r="R37" t="n">
-        <v>10.20023305483334</v>
+        <v>10.24071691559038</v>
       </c>
       <c r="S37" t="n">
-        <v>43.991</v>
+        <v>42.335</v>
       </c>
       <c r="T37" t="n">
-        <v>0.06587000573375799</v>
+        <v>0.06377243129242501</v>
       </c>
       <c r="U37" t="n">
         <v>4.2</v>
       </c>
       <c r="V37" t="n">
-        <v>0.006288877817776</v>
+        <v>0.006326779530606</v>
       </c>
       <c r="W37" t="n">
-        <v>3239.197771</v>
+        <v>3226.919171</v>
       </c>
       <c r="X37" t="n">
-        <v>4.850218811769386</v>
+        <v>4.860953847143167</v>
       </c>
       <c r="Y37" t="n">
         <v>3524.793</v>
       </c>
       <c r="Z37" t="n">
-        <v>5.277855359512424</v>
+        <v>5.309663857624186</v>
       </c>
       <c r="AA37" t="inlineStr"/>
       <c r="AB37" t="inlineStr"/>
       <c r="AC37" t="inlineStr"/>
       <c r="AD37" t="inlineStr"/>
       <c r="AE37" t="n">
-        <v>24.97756563300466</v>
+        <v>23.44151227867721</v>
       </c>
     </row>
     <row r="38">
@@ -3949,16 +3979,16 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>07月</t>
+          <t>05月</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2025/07</t>
+          <t>2025/05</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>17006.322656</v>
+        <v>16668.881171</v>
       </c>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr"/>
@@ -3966,13 +3996,13 @@
         <v>9868.977999999999</v>
       </c>
       <c r="H38" t="n">
-        <v>14.49357847585138</v>
+        <v>14.59437948410531</v>
       </c>
       <c r="I38" t="n">
         <v>3120.3</v>
       </c>
       <c r="J38" t="n">
-        <v>4.582471753225011</v>
+        <v>4.61434226565849</v>
       </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
@@ -3980,46 +4010,46 @@
         <v>6748.678</v>
       </c>
       <c r="N38" t="n">
-        <v>9.911106722626371</v>
+        <v>9.980037218446821</v>
       </c>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr"/>
       <c r="Q38" t="n">
-        <v>7137.344656</v>
+        <v>6799.903171</v>
       </c>
       <c r="R38" t="n">
-        <v>10.48190247064432</v>
+        <v>10.05578970109621</v>
       </c>
       <c r="S38" t="n">
         <v>43.991</v>
       </c>
       <c r="T38" t="n">
-        <v>0.064605170943858</v>
+        <v>0.06505449175033901</v>
       </c>
       <c r="U38" t="n">
         <v>4.2</v>
       </c>
       <c r="V38" t="n">
-        <v>0.006168118887141</v>
+        <v>0.006211017375177</v>
       </c>
       <c r="W38" t="n">
-        <v>3480.315656</v>
+        <v>3226.919171</v>
       </c>
       <c r="X38" t="n">
-        <v>5.111190650234521</v>
+        <v>4.772012152231824</v>
       </c>
       <c r="Y38" t="n">
-        <v>3608.838</v>
+        <v>3524.793</v>
       </c>
       <c r="Z38" t="n">
-        <v>5.299938530578805</v>
+        <v>5.212512039738867</v>
       </c>
       <c r="AA38" t="inlineStr"/>
       <c r="AB38" t="inlineStr"/>
       <c r="AC38" t="inlineStr"/>
       <c r="AD38" t="inlineStr"/>
       <c r="AE38" t="n">
-        <v>24.97548094649571</v>
+        <v>24.65016918520152</v>
       </c>
     </row>
     <row r="39">
@@ -4030,16 +4060,16 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>08月</t>
+          <t>06月</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2025/08</t>
+          <t>2025/06</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>17085.074476</v>
+        <v>16679.366291</v>
       </c>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr"/>
@@ -4047,13 +4077,13 @@
         <v>9868.977999999999</v>
       </c>
       <c r="H39" t="n">
-        <v>14.46180530846523</v>
+        <v>14.77702180844244</v>
       </c>
       <c r="I39" t="n">
         <v>3120.3</v>
       </c>
       <c r="J39" t="n">
-        <v>4.572425949678279</v>
+        <v>4.672088756189641</v>
       </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
@@ -4061,46 +4091,46 @@
         <v>6748.678</v>
       </c>
       <c r="N39" t="n">
-        <v>9.889379358786949</v>
+        <v>10.1049330522528</v>
       </c>
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr"/>
       <c r="Q39" t="n">
-        <v>7216.096476</v>
+        <v>6810.388291</v>
       </c>
       <c r="R39" t="n">
-        <v>10.57432515535185</v>
+        <v>10.19733312811803</v>
       </c>
       <c r="S39" t="n">
         <v>43.991</v>
       </c>
       <c r="T39" t="n">
-        <v>0.064463541951831</v>
+        <v>0.06586862047672901</v>
       </c>
       <c r="U39" t="n">
         <v>4.2</v>
       </c>
       <c r="V39" t="n">
-        <v>0.006154596990241</v>
+        <v>0.006288745561644</v>
       </c>
       <c r="W39" t="n">
-        <v>3489.067476</v>
+        <v>3237.404291</v>
       </c>
       <c r="X39" t="n">
-        <v>5.112810520604075</v>
+        <v>4.847431396731468</v>
       </c>
       <c r="Y39" t="n">
-        <v>3678.838</v>
+        <v>3524.793</v>
       </c>
       <c r="Z39" t="n">
-        <v>5.390896495805705</v>
+        <v>5.277744365348189</v>
       </c>
       <c r="AA39" t="inlineStr"/>
       <c r="AB39" t="inlineStr"/>
       <c r="AC39" t="inlineStr"/>
       <c r="AD39" t="inlineStr"/>
       <c r="AE39" t="n">
-        <v>25.03613046381708</v>
+        <v>24.97435493656047</v>
       </c>
     </row>
     <row r="40">
@@ -4111,16 +4141,16 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>09月</t>
+          <t>07月</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2025/09</t>
+          <t>2025/07</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>17178.671496</v>
+        <v>17006.324336</v>
       </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
@@ -4128,13 +4158,13 @@
         <v>9868.977999999999</v>
       </c>
       <c r="H40" t="n">
-        <v>14.42806509516924</v>
+        <v>14.49317392235936</v>
       </c>
       <c r="I40" t="n">
         <v>3120.3</v>
       </c>
       <c r="J40" t="n">
-        <v>4.56175822019834</v>
+        <v>4.582343844513372</v>
       </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
@@ -4142,46 +4172,46 @@
         <v>6748.678</v>
       </c>
       <c r="N40" t="n">
-        <v>9.866306874970901</v>
+        <v>9.910830077845983</v>
       </c>
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr"/>
       <c r="Q40" t="n">
-        <v>7309.693496</v>
+        <v>7137.346336</v>
       </c>
       <c r="R40" t="n">
-        <v>10.6864898863918</v>
+        <v>10.48161236064791</v>
       </c>
       <c r="S40" t="n">
         <v>43.991</v>
       </c>
       <c r="T40" t="n">
-        <v>0.064313144846568</v>
+        <v>0.06460336764541499</v>
       </c>
       <c r="U40" t="n">
         <v>4.2</v>
       </c>
       <c r="V40" t="n">
-        <v>0.006140237965847</v>
+        <v>0.006167946718891</v>
       </c>
       <c r="W40" t="n">
-        <v>3499.152496</v>
+        <v>3480.317336</v>
       </c>
       <c r="X40" t="n">
-        <v>5.115625953387668</v>
+        <v>5.111050450781263</v>
       </c>
       <c r="Y40" t="n">
-        <v>3762.35</v>
+        <v>3608.838</v>
       </c>
       <c r="Z40" t="n">
-        <v>5.500410550191721</v>
+        <v>5.29979059550234</v>
       </c>
       <c r="AA40" t="inlineStr"/>
       <c r="AB40" t="inlineStr"/>
       <c r="AC40" t="inlineStr"/>
       <c r="AD40" t="inlineStr"/>
       <c r="AE40" t="n">
-        <v>25.11455498156104</v>
+        <v>24.97478628300726</v>
       </c>
     </row>
     <row r="41">
@@ -4192,16 +4222,16 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>10月</t>
+          <t>08月</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2025/10</t>
+          <t>2025/08</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>17269.222366</v>
+        <v>17079.284596</v>
       </c>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
@@ -4209,13 +4239,13 @@
         <v>9868.977999999999</v>
       </c>
       <c r="H41" t="n">
-        <v>14.39025374304246</v>
+        <v>14.46192925755259</v>
       </c>
       <c r="I41" t="n">
         <v>3120.3</v>
       </c>
       <c r="J41" t="n">
-        <v>4.549803308348177</v>
+        <v>4.572465138978053</v>
       </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
@@ -4223,46 +4253,46 @@
         <v>6748.678</v>
       </c>
       <c r="N41" t="n">
-        <v>9.840450434694279</v>
+        <v>9.889464118574539</v>
       </c>
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr"/>
       <c r="Q41" t="n">
-        <v>7400.244366</v>
+        <v>7210.306596</v>
       </c>
       <c r="R41" t="n">
-        <v>10.79051895619388</v>
+        <v>10.56593133722832</v>
       </c>
       <c r="S41" t="n">
         <v>43.991</v>
       </c>
       <c r="T41" t="n">
-        <v>0.06414460062735799</v>
+        <v>0.064464094455271</v>
       </c>
       <c r="U41" t="n">
         <v>4.2</v>
       </c>
       <c r="V41" t="n">
-        <v>0.006124146362549</v>
+        <v>0.006154649739995</v>
       </c>
       <c r="W41" t="n">
-        <v>3519.703366</v>
+        <v>3483.277596</v>
       </c>
       <c r="X41" t="n">
-        <v>5.132185372890752</v>
+        <v>5.104369892988904</v>
       </c>
       <c r="Y41" t="n">
-        <v>3832.35</v>
+        <v>3678.838</v>
       </c>
       <c r="Z41" t="n">
-        <v>5.588064836313219</v>
+        <v>5.390942700044143</v>
       </c>
       <c r="AA41" t="inlineStr"/>
       <c r="AB41" t="inlineStr"/>
       <c r="AC41" t="inlineStr"/>
       <c r="AD41" t="inlineStr"/>
       <c r="AE41" t="n">
-        <v>25.18077269923633</v>
+        <v>25.0278605947809</v>
       </c>
     </row>
     <row r="42">
@@ -4273,16 +4303,16 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>11月</t>
+          <t>09月</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2025/11</t>
+          <t>2025/09</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>17354.429646</v>
+        <v>17177.101056</v>
       </c>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr"/>
@@ -4290,13 +4320,13 @@
         <v>9868.977999999999</v>
       </c>
       <c r="H42" t="n">
-        <v>14.36464150747757</v>
+        <v>14.42806518797965</v>
       </c>
       <c r="I42" t="n">
         <v>3120.3</v>
       </c>
       <c r="J42" t="n">
-        <v>4.541705422363111</v>
+        <v>4.561758249542443</v>
       </c>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
@@ -4304,46 +4334,46 @@
         <v>6748.678</v>
       </c>
       <c r="N42" t="n">
-        <v>9.822936085114458</v>
+        <v>9.866306938437203</v>
       </c>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr"/>
       <c r="Q42" t="n">
-        <v>7485.451646</v>
+        <v>7308.123056</v>
       </c>
       <c r="R42" t="n">
-        <v>10.89533581049101</v>
+        <v>10.68419403242616</v>
       </c>
       <c r="S42" t="n">
         <v>43.991</v>
       </c>
       <c r="T42" t="n">
-        <v>0.064030434008004</v>
+        <v>0.06431314526027</v>
       </c>
       <c r="U42" t="n">
         <v>4.2</v>
       </c>
       <c r="V42" t="n">
-        <v>0.006113246410257</v>
+        <v>0.006140238005345</v>
       </c>
       <c r="W42" t="n">
-        <v>3563.154646</v>
+        <v>3497.582056</v>
       </c>
       <c r="X42" t="n">
-        <v>5.186295797345292</v>
+        <v>5.113330063586713</v>
       </c>
       <c r="Y42" t="n">
-        <v>3874.106</v>
+        <v>3762.35</v>
       </c>
       <c r="Z42" t="n">
-        <v>5.638896332727452</v>
+        <v>5.500410585573827</v>
       </c>
       <c r="AA42" t="inlineStr"/>
       <c r="AB42" t="inlineStr"/>
       <c r="AC42" t="inlineStr"/>
       <c r="AD42" t="inlineStr"/>
       <c r="AE42" t="n">
-        <v>25.25997731796857</v>
+        <v>25.1122592204058</v>
       </c>
     </row>
     <row r="43">
@@ -4354,16 +4384,16 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>12月</t>
+          <t>10月</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2025/12</t>
+          <t>2025/10</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>17620.551301</v>
+        <v>17269.224046</v>
       </c>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr"/>
@@ -4371,13 +4401,13 @@
         <v>9868.977999999999</v>
       </c>
       <c r="H43" t="n">
-        <v>14.1271000324062</v>
+        <v>14.39025381018761</v>
       </c>
       <c r="I43" t="n">
         <v>3120.3</v>
       </c>
       <c r="J43" t="n">
-        <v>4.466601327018569</v>
+        <v>4.549803329577632</v>
       </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
@@ -4385,46 +4415,46 @@
         <v>6748.678</v>
       </c>
       <c r="N43" t="n">
-        <v>9.660498705387633</v>
+        <v>9.840450480609981</v>
       </c>
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr"/>
       <c r="Q43" t="n">
-        <v>7751.573301</v>
+        <v>7400.246046</v>
       </c>
       <c r="R43" t="n">
-        <v>11.09610857697283</v>
+        <v>10.79052145620117</v>
       </c>
       <c r="S43" t="n">
         <v>43.991</v>
       </c>
       <c r="T43" t="n">
-        <v>0.062971592147189</v>
+        <v>0.064144600926658</v>
       </c>
       <c r="U43" t="n">
         <v>4.2</v>
       </c>
       <c r="V43" t="n">
-        <v>0.006012154463827</v>
+        <v>0.006124146391125</v>
       </c>
       <c r="W43" t="n">
-        <v>3634.496301</v>
+        <v>3519.705046</v>
       </c>
       <c r="X43" t="n">
-        <v>5.20265551424244</v>
+        <v>5.132187846496169</v>
       </c>
       <c r="Y43" t="n">
-        <v>4068.886</v>
+        <v>3832.35</v>
       </c>
       <c r="Z43" t="n">
-        <v>5.824469316119373</v>
+        <v>5.588064862387221</v>
       </c>
       <c r="AA43" t="inlineStr"/>
       <c r="AB43" t="inlineStr"/>
       <c r="AC43" t="inlineStr"/>
       <c r="AD43" t="inlineStr"/>
       <c r="AE43" t="n">
-        <v>25.22320860937903</v>
+        <v>25.18077526638878</v>
       </c>
     </row>
     <row r="44">
@@ -4435,16 +4465,16 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>01月</t>
+          <t>11月</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026/01</t>
+          <t>2025/11</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>17728.083001</v>
+        <v>17354.431326</v>
       </c>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr"/>
@@ -4452,13 +4482,13 @@
         <v>9868.977999999999</v>
       </c>
       <c r="H44" t="n">
-        <v>14.03781096661743</v>
+        <v>14.36464157438393</v>
       </c>
       <c r="I44" t="n">
         <v>3120.3</v>
       </c>
       <c r="J44" t="n">
-        <v>4.438370574859561</v>
+        <v>4.541705443517065</v>
       </c>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
@@ -4466,46 +4496,46 @@
         <v>6748.678</v>
       </c>
       <c r="N44" t="n">
-        <v>9.599440391757868</v>
+        <v>9.822936130866861</v>
       </c>
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr"/>
       <c r="Q44" t="n">
-        <v>7859.105001</v>
+        <v>7485.453326</v>
       </c>
       <c r="R44" t="n">
-        <v>11.17893163515368</v>
+        <v>10.89533830653691</v>
       </c>
       <c r="S44" t="n">
         <v>43.991</v>
       </c>
       <c r="T44" t="n">
-        <v>0.0625735858599</v>
+        <v>0.06403043430624</v>
       </c>
       <c r="U44" t="n">
         <v>4.2</v>
       </c>
       <c r="V44" t="n">
-        <v>0.005974155182005</v>
+        <v>0.006113246438731</v>
       </c>
       <c r="W44" t="n">
-        <v>3686.516001</v>
+        <v>3563.156326</v>
       </c>
       <c r="X44" t="n">
-        <v>5.243766350218678</v>
+        <v>5.186298266800137</v>
       </c>
       <c r="Y44" t="n">
-        <v>4124.398</v>
+        <v>3874.106</v>
       </c>
       <c r="Z44" t="n">
-        <v>5.866617543893096</v>
+        <v>5.638896358991804</v>
       </c>
       <c r="AA44" t="inlineStr"/>
       <c r="AB44" t="inlineStr"/>
       <c r="AC44" t="inlineStr"/>
       <c r="AD44" t="inlineStr"/>
       <c r="AE44" t="n">
-        <v>25.21674260177111</v>
+        <v>25.25997988092083</v>
       </c>
     </row>
     <row r="45">
@@ -4516,16 +4546,16 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>02月</t>
+          <t>12月</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026/02</t>
+          <t>2025/12</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>17771.432441</v>
+        <v>17620.552981</v>
       </c>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr"/>
@@ -4533,13 +4563,13 @@
         <v>9868.977999999999</v>
       </c>
       <c r="H45" t="n">
-        <v>14.00907231328306</v>
+        <v>14.12710009711806</v>
       </c>
       <c r="I45" t="n">
         <v>3120.3</v>
       </c>
       <c r="J45" t="n">
-        <v>4.429284201376995</v>
+        <v>4.466601347478683</v>
       </c>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
@@ -4547,46 +4577,46 @@
         <v>6748.678</v>
       </c>
       <c r="N45" t="n">
-        <v>9.579788111906067</v>
+        <v>9.660498749639377</v>
       </c>
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr"/>
       <c r="Q45" t="n">
-        <v>7902.454441</v>
+        <v>7751.574981</v>
       </c>
       <c r="R45" t="n">
-        <v>11.2175805555949</v>
+        <v>11.09611103266245</v>
       </c>
       <c r="S45" t="n">
         <v>43.991</v>
       </c>
       <c r="T45" t="n">
-        <v>0.062445483223657</v>
+        <v>0.062971592435642</v>
       </c>
       <c r="U45" t="n">
         <v>4.2</v>
       </c>
       <c r="V45" t="n">
-        <v>0.005961924701402</v>
+        <v>0.006012154491366</v>
       </c>
       <c r="W45" t="n">
-        <v>3688.231441</v>
+        <v>3634.497981</v>
       </c>
       <c r="X45" t="n">
-        <v>5.23546622204378</v>
+        <v>5.202657942935985</v>
       </c>
       <c r="Y45" t="n">
-        <v>4166.032</v>
+        <v>4068.886</v>
       </c>
       <c r="Z45" t="n">
-        <v>5.913706925626064</v>
+        <v>5.824469342799457</v>
       </c>
       <c r="AA45" t="inlineStr"/>
       <c r="AB45" t="inlineStr"/>
       <c r="AC45" t="inlineStr"/>
       <c r="AD45" t="inlineStr"/>
       <c r="AE45" t="n">
-        <v>25.22665286887796</v>
+        <v>25.22321112978051</v>
       </c>
     </row>
     <row r="46">
@@ -4597,16 +4627,16 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>03月</t>
+          <t>01月</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026/03</t>
+          <t>2026/01</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>18008.212441</v>
+        <v>17728.083001</v>
       </c>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr"/>
@@ -4614,13 +4644,13 @@
         <v>9868.977999999999</v>
       </c>
       <c r="H46" t="n">
-        <v>13.9434277845403</v>
+        <v>14.03781096661743</v>
       </c>
       <c r="I46" t="n">
         <v>3120.3</v>
       </c>
       <c r="J46" t="n">
-        <v>4.408529202932776</v>
+        <v>4.438370574859561</v>
       </c>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
@@ -4628,325 +4658,289 @@
         <v>6748.678</v>
       </c>
       <c r="N46" t="n">
-        <v>9.534898581607528</v>
+        <v>9.599440391757868</v>
       </c>
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr"/>
       <c r="Q46" t="n">
-        <v>8139.234441</v>
+        <v>7859.105001</v>
       </c>
       <c r="R46" t="n">
-        <v>11.49955219775814</v>
+        <v>11.17893163515368</v>
       </c>
       <c r="S46" t="n">
         <v>43.991</v>
       </c>
       <c r="T46" t="n">
-        <v>0.062152872533479</v>
+        <v>0.0625735858599</v>
       </c>
       <c r="U46" t="n">
         <v>4.2</v>
       </c>
       <c r="V46" t="n">
-        <v>0.005933987966643</v>
+        <v>0.005974155182005</v>
       </c>
       <c r="W46" t="n">
-        <v>3688.231441</v>
+        <v>3686.516001</v>
       </c>
       <c r="X46" t="n">
-        <v>5.210933568830989</v>
+        <v>5.243766350218678</v>
       </c>
       <c r="Y46" t="n">
-        <v>4402.812</v>
+        <v>4124.398</v>
       </c>
       <c r="Z46" t="n">
-        <v>6.22053176842703</v>
+        <v>5.866617543893096</v>
       </c>
       <c r="AA46" t="inlineStr"/>
       <c r="AB46" t="inlineStr"/>
       <c r="AC46" t="inlineStr"/>
       <c r="AD46" t="inlineStr"/>
       <c r="AE46" t="n">
-        <v>25.44297998229845</v>
+        <v>25.21674260177111</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>自用發電設備</t>
+          <t>民營電廠</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>01月</t>
+          <t>02月</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2025/01</t>
+          <t>2026/02</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>18868.3008</v>
+        <v>17771.432441</v>
       </c>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="n">
-        <v>7211.8346</v>
+        <v>9868.977999999999</v>
       </c>
       <c r="H47" t="n">
-        <v>10.78283681114256</v>
+        <v>14.00907231328306</v>
       </c>
       <c r="I47" t="n">
-        <v>6151.384</v>
+        <v>3120.3</v>
       </c>
       <c r="J47" t="n">
-        <v>9.197294934450296</v>
-      </c>
-      <c r="K47" t="n">
-        <v>560.4126</v>
-      </c>
-      <c r="L47" t="n">
-        <v>0.83790574075397</v>
-      </c>
+        <v>4.429284201376995</v>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
       <c r="M47" t="n">
-        <v>500.038</v>
+        <v>6748.678</v>
       </c>
       <c r="N47" t="n">
-        <v>0.747636135938295</v>
+        <v>9.579788111906067</v>
       </c>
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr"/>
       <c r="Q47" t="n">
-        <v>11656.4662</v>
+        <v>7902.454441</v>
       </c>
       <c r="R47" t="n">
-        <v>17.42826614869939</v>
+        <v>11.2175805555949</v>
       </c>
       <c r="S47" t="n">
-        <v>3.9605</v>
+        <v>43.991</v>
       </c>
       <c r="T47" t="n">
-        <v>0.005921575793007</v>
+        <v>0.062445483223657</v>
       </c>
       <c r="U47" t="n">
-        <v>2.449</v>
+        <v>4.2</v>
       </c>
       <c r="V47" t="n">
-        <v>0.003661643508919</v>
+        <v>0.005961924701402</v>
       </c>
       <c r="W47" t="n">
-        <v>10893.38</v>
+        <v>3688.231441</v>
       </c>
       <c r="X47" t="n">
-        <v>16.28733122384201</v>
+        <v>5.23546622204378</v>
       </c>
       <c r="Y47" t="n">
-        <v>6.2137</v>
+        <v>4166.032</v>
       </c>
       <c r="Z47" t="n">
-        <v>0.009290467240249</v>
-      </c>
-      <c r="AA47" t="n">
-        <v>83.998</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>0.125590335427597</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>666.465</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>0.996470902887613</v>
-      </c>
+        <v>5.913706925626064</v>
+      </c>
+      <c r="AA47" t="inlineStr"/>
+      <c r="AB47" t="inlineStr"/>
+      <c r="AC47" t="inlineStr"/>
+      <c r="AD47" t="inlineStr"/>
       <c r="AE47" t="n">
-        <v>28.21110295984196</v>
+        <v>25.22665286887796</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>自用發電設備</t>
+          <t>民營電廠</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>02月</t>
+          <t>03月</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2025/02</t>
+          <t>2026/03</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>18875.3738</v>
+        <v>18008.212441</v>
       </c>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="n">
-        <v>7171.8346</v>
+        <v>9868.977999999999</v>
       </c>
       <c r="H48" t="n">
-        <v>10.7149800836961</v>
+        <v>13.9434277845403</v>
       </c>
       <c r="I48" t="n">
-        <v>6111.384</v>
+        <v>3120.3</v>
       </c>
       <c r="J48" t="n">
-        <v>9.130628562434921</v>
-      </c>
-      <c r="K48" t="n">
-        <v>560.4126</v>
-      </c>
-      <c r="L48" t="n">
-        <v>0.837276677804637</v>
-      </c>
+        <v>4.408529202932776</v>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
       <c r="M48" t="n">
-        <v>500.038</v>
+        <v>6748.678</v>
       </c>
       <c r="N48" t="n">
-        <v>0.747074843456545</v>
+        <v>9.534898581607528</v>
       </c>
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr"/>
       <c r="Q48" t="n">
-        <v>11703.5392</v>
+        <v>8139.234441</v>
       </c>
       <c r="R48" t="n">
-        <v>17.48551053265459</v>
+        <v>11.49955219775814</v>
       </c>
       <c r="S48" t="n">
-        <v>4.0205</v>
+        <v>43.991</v>
       </c>
       <c r="T48" t="n">
-        <v>0.006006772301539</v>
+        <v>0.062152872533479</v>
       </c>
       <c r="U48" t="n">
-        <v>2.449</v>
+        <v>4.2</v>
       </c>
       <c r="V48" t="n">
-        <v>0.003658894507268</v>
+        <v>0.005933987966643</v>
       </c>
       <c r="W48" t="n">
-        <v>10940.393</v>
+        <v>3688.231441</v>
       </c>
       <c r="X48" t="n">
-        <v>16.34534252962391</v>
+        <v>5.210933568830989</v>
       </c>
       <c r="Y48" t="n">
-        <v>6.2137</v>
+        <v>4402.812</v>
       </c>
       <c r="Z48" t="n">
-        <v>0.009283492364151999</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>83.998</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>0.1254960477017</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>666.465</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>0.995722796156025</v>
-      </c>
+        <v>6.22053176842703</v>
+      </c>
+      <c r="AA48" t="inlineStr"/>
+      <c r="AB48" t="inlineStr"/>
+      <c r="AC48" t="inlineStr"/>
+      <c r="AD48" t="inlineStr"/>
       <c r="AE48" t="n">
-        <v>28.20049061635069</v>
+        <v>25.44297998229845</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>自用發電設備</t>
+          <t>民營電廠</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>03月</t>
+          <t>04月</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2025/03</t>
+          <t>2026/04</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>18981.0859</v>
+        <v>18176.879961</v>
       </c>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="n">
-        <v>7212.6946</v>
+        <v>9868.977999999999</v>
       </c>
       <c r="H49" t="n">
-        <v>10.7579965595637</v>
+        <v>13.8992877031067</v>
       </c>
       <c r="I49" t="n">
-        <v>6111.384</v>
+        <v>3120.3</v>
       </c>
       <c r="J49" t="n">
-        <v>9.115351708662754</v>
-      </c>
-      <c r="K49" t="n">
-        <v>601.2726</v>
-      </c>
-      <c r="L49" t="n">
-        <v>0.896819971021637</v>
-      </c>
+        <v>4.394573320561037</v>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
       <c r="M49" t="n">
-        <v>500.038</v>
+        <v>6748.678</v>
       </c>
       <c r="N49" t="n">
-        <v>0.745824879879305</v>
+        <v>9.504714382545659</v>
       </c>
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr"/>
       <c r="Q49" t="n">
-        <v>11768.3913</v>
+        <v>8307.901961</v>
       </c>
       <c r="R49" t="n">
-        <v>17.55298402860414</v>
+        <v>11.70069682647416</v>
       </c>
       <c r="S49" t="n">
-        <v>3.5405</v>
+        <v>43.991</v>
       </c>
       <c r="T49" t="n">
-        <v>0.005280784634793</v>
+        <v>0.061956117983784</v>
       </c>
       <c r="U49" t="n">
-        <v>2.449</v>
+        <v>4.2</v>
       </c>
       <c r="V49" t="n">
-        <v>0.003652772650927</v>
+        <v>0.005915203008158</v>
       </c>
       <c r="W49" t="n">
-        <v>11005.564</v>
+        <v>3703.508961</v>
       </c>
       <c r="X49" t="n">
-        <v>16.41519934145805</v>
+        <v>5.215954130202009</v>
       </c>
       <c r="Y49" t="n">
-        <v>6.1798</v>
+        <v>4556.202</v>
       </c>
       <c r="Z49" t="n">
-        <v>0.00921739666321</v>
-      </c>
-      <c r="AA49" t="n">
-        <v>84.193</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>0.125576924377104</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>666.465</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>0.994056808820052</v>
-      </c>
+        <v>6.41687137528021</v>
+      </c>
+      <c r="AA49" t="inlineStr"/>
+      <c r="AB49" t="inlineStr"/>
+      <c r="AC49" t="inlineStr"/>
+      <c r="AD49" t="inlineStr"/>
       <c r="AE49" t="n">
-        <v>28.31098058816784</v>
+        <v>25.59998452958085</v>
       </c>
     </row>
     <row r="50">
@@ -4957,89 +4951,89 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>04月</t>
+          <t>01月</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2025/04</t>
+          <t>2025/01</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>19079.3449</v>
+        <v>18868.2988</v>
       </c>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="n">
-        <v>7212.6946</v>
+        <v>7211.8346</v>
       </c>
       <c r="H50" t="n">
-        <v>10.86475969363187</v>
+        <v>10.78283688852841</v>
       </c>
       <c r="I50" t="n">
-        <v>6111.384</v>
+        <v>6151.384</v>
       </c>
       <c r="J50" t="n">
-        <v>9.205813116710461</v>
+        <v>9.197295000457087</v>
       </c>
       <c r="K50" t="n">
-        <v>601.2726</v>
+        <v>560.4126</v>
       </c>
       <c r="L50" t="n">
-        <v>0.905720077121418</v>
+        <v>0.837905746767419</v>
       </c>
       <c r="M50" t="n">
         <v>500.038</v>
       </c>
       <c r="N50" t="n">
-        <v>0.75322649979999</v>
+        <v>0.747636141303902</v>
       </c>
       <c r="O50" t="inlineStr"/>
       <c r="P50" t="inlineStr"/>
       <c r="Q50" t="n">
-        <v>11866.6503</v>
+        <v>11656.4642</v>
       </c>
       <c r="R50" t="n">
-        <v>17.87519242501471</v>
+        <v>17.4282632834606</v>
       </c>
       <c r="S50" t="n">
-        <v>3.5405</v>
+        <v>3.9605</v>
       </c>
       <c r="T50" t="n">
-        <v>0.005333191522528</v>
+        <v>0.005921575835505</v>
       </c>
       <c r="U50" t="n">
         <v>2.449</v>
       </c>
       <c r="V50" t="n">
-        <v>0.00368902303027</v>
+        <v>0.003661643535198</v>
       </c>
       <c r="W50" t="n">
-        <v>11103.823</v>
+        <v>10893.378</v>
       </c>
       <c r="X50" t="n">
-        <v>16.72611628053994</v>
+        <v>16.287328350415</v>
       </c>
       <c r="Y50" t="n">
-        <v>6.1798</v>
+        <v>6.2137</v>
       </c>
       <c r="Z50" t="n">
-        <v>0.009308870772749001</v>
+        <v>0.009290467306924999</v>
       </c>
       <c r="AA50" t="n">
-        <v>84.193</v>
+        <v>83.998</v>
       </c>
       <c r="AB50" t="n">
-        <v>0.12682315883525</v>
+        <v>0.125590336328929</v>
       </c>
       <c r="AC50" t="n">
         <v>666.465</v>
       </c>
       <c r="AD50" t="n">
-        <v>1.003921900313977</v>
+        <v>0.996470910039047</v>
       </c>
       <c r="AE50" t="n">
-        <v>28.73995211864658</v>
+        <v>28.21110017198901</v>
       </c>
     </row>
     <row r="51">
@@ -5050,89 +5044,89 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>05月</t>
+          <t>02月</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2025/05</t>
+          <t>2025/02</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>19205.1049</v>
+        <v>18875.3718</v>
       </c>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="n">
-        <v>7237.4036</v>
+        <v>7171.8346</v>
       </c>
       <c r="H51" t="n">
-        <v>10.70815618586466</v>
+        <v>10.71498013332266</v>
       </c>
       <c r="I51" t="n">
         <v>6111.384</v>
       </c>
       <c r="J51" t="n">
-        <v>9.042145222327285</v>
+        <v>9.130628604723539</v>
       </c>
       <c r="K51" t="n">
-        <v>632.7316</v>
+        <v>560.4126</v>
       </c>
       <c r="L51" t="n">
-        <v>0.936162907445433</v>
+        <v>0.837276681682494</v>
       </c>
       <c r="M51" t="n">
-        <v>493.288</v>
+        <v>500.038</v>
       </c>
       <c r="N51" t="n">
-        <v>0.72984805609194</v>
+        <v>0.747074846916631</v>
       </c>
       <c r="O51" t="inlineStr"/>
       <c r="P51" t="inlineStr"/>
       <c r="Q51" t="n">
-        <v>11967.7013</v>
+        <v>11703.5372</v>
       </c>
       <c r="R51" t="n">
-        <v>17.70690454601364</v>
+        <v>17.48550762556665</v>
       </c>
       <c r="S51" t="n">
-        <v>3.5405</v>
+        <v>4.0205</v>
       </c>
       <c r="T51" t="n">
-        <v>0.005238374018005</v>
+        <v>0.00600677232936</v>
       </c>
       <c r="U51" t="n">
         <v>2.449</v>
       </c>
       <c r="V51" t="n">
-        <v>0.003623436794265</v>
+        <v>0.003658894524214</v>
       </c>
       <c r="W51" t="n">
-        <v>11204.893</v>
+        <v>10940.391</v>
       </c>
       <c r="X51" t="n">
-        <v>16.57828565618499</v>
+        <v>16.34533961725527</v>
       </c>
       <c r="Y51" t="n">
-        <v>6.1798</v>
+        <v>6.2137</v>
       </c>
       <c r="Z51" t="n">
-        <v>0.009143370641566</v>
+        <v>0.009283492407148999</v>
       </c>
       <c r="AA51" t="n">
-        <v>84.17400000000001</v>
+        <v>83.998</v>
       </c>
       <c r="AB51" t="n">
-        <v>0.124540289391761</v>
+        <v>0.125496048282937</v>
       </c>
       <c r="AC51" t="n">
         <v>666.465</v>
       </c>
       <c r="AD51" t="n">
-        <v>0.986073418983058</v>
+        <v>0.995722800767727</v>
       </c>
       <c r="AE51" t="n">
-        <v>28.4150607318783</v>
+        <v>28.20048775888931</v>
       </c>
     </row>
     <row r="52">
@@ -5143,89 +5137,89 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>06月</t>
+          <t>03月</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2025/06</t>
+          <t>2025/03</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>19312.2963</v>
+        <v>18981.0839</v>
       </c>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="n">
-        <v>7237.4036</v>
+        <v>7212.6946</v>
       </c>
       <c r="H52" t="n">
-        <v>10.83693975198388</v>
+        <v>10.75799660930612</v>
       </c>
       <c r="I52" t="n">
         <v>6111.384</v>
       </c>
       <c r="J52" t="n">
-        <v>9.150892207978874</v>
+        <v>9.115351750809978</v>
       </c>
       <c r="K52" t="n">
-        <v>632.7316</v>
+        <v>601.2726</v>
       </c>
       <c r="L52" t="n">
-        <v>0.947421839010935</v>
+        <v>0.89681997516832</v>
       </c>
       <c r="M52" t="n">
-        <v>493.288</v>
+        <v>500.038</v>
       </c>
       <c r="N52" t="n">
-        <v>0.738625704994071</v>
+        <v>0.745824883327822</v>
       </c>
       <c r="O52" t="inlineStr"/>
       <c r="P52" t="inlineStr"/>
       <c r="Q52" t="n">
-        <v>12074.8927</v>
+        <v>11768.3893</v>
       </c>
       <c r="R52" t="n">
-        <v>18.08036306025132</v>
+        <v>17.55298112669216</v>
       </c>
       <c r="S52" t="n">
         <v>3.5405</v>
       </c>
       <c r="T52" t="n">
-        <v>0.005301374265199</v>
+        <v>0.00528078465921</v>
       </c>
       <c r="U52" t="n">
         <v>2.449</v>
       </c>
       <c r="V52" t="n">
-        <v>0.003667014708508</v>
+        <v>0.003652772667817</v>
       </c>
       <c r="W52" t="n">
-        <v>11312.094</v>
+        <v>11005.562</v>
       </c>
       <c r="X52" t="n">
-        <v>16.93818500695171</v>
+        <v>16.41519643428522</v>
       </c>
       <c r="Y52" t="n">
-        <v>6.1702</v>
+        <v>6.1798</v>
       </c>
       <c r="Z52" t="n">
-        <v>0.009238960455057999</v>
+        <v>0.009217396705829</v>
       </c>
       <c r="AA52" t="n">
-        <v>84.17400000000001</v>
+        <v>84.193</v>
       </c>
       <c r="AB52" t="n">
-        <v>0.1260380955794</v>
+        <v>0.125576924957742</v>
       </c>
       <c r="AC52" t="n">
         <v>666.465</v>
       </c>
       <c r="AD52" t="n">
-        <v>0.997932608291451</v>
+        <v>0.994056813416335</v>
       </c>
       <c r="AE52" t="n">
-        <v>28.91730281223521</v>
+        <v>28.31097773599827</v>
       </c>
     </row>
     <row r="53">
@@ -5236,89 +5230,89 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>07月</t>
+          <t>04月</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2025/07</t>
+          <t>2025/04</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>19169.0073</v>
+        <v>19079.3439</v>
       </c>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="n">
-        <v>7237.4036</v>
+        <v>7212.6946</v>
       </c>
       <c r="H53" t="n">
-        <v>10.62884900929046</v>
+        <v>10.86503060852116</v>
       </c>
       <c r="I53" t="n">
         <v>6111.384</v>
       </c>
       <c r="J53" t="n">
-        <v>8.975176923087934</v>
+        <v>9.206042665445244</v>
       </c>
       <c r="K53" t="n">
-        <v>632.7316</v>
+        <v>601.2726</v>
       </c>
       <c r="L53" t="n">
-        <v>0.929229460107319</v>
+        <v>0.905742661427132</v>
       </c>
       <c r="M53" t="n">
-        <v>493.288</v>
+        <v>500.038</v>
       </c>
       <c r="N53" t="n">
-        <v>0.724442626095202</v>
+        <v>0.75324528164879</v>
       </c>
       <c r="O53" t="inlineStr"/>
       <c r="P53" t="inlineStr"/>
       <c r="Q53" t="n">
-        <v>11931.6037</v>
+        <v>11866.6493</v>
       </c>
       <c r="R53" t="n">
-        <v>17.52275003234465</v>
+        <v>17.87563664002719</v>
       </c>
       <c r="S53" t="n">
         <v>3.5405</v>
       </c>
       <c r="T53" t="n">
-        <v>0.005199577361886</v>
+        <v>0.005333324506693</v>
       </c>
       <c r="U53" t="n">
         <v>2.449</v>
       </c>
       <c r="V53" t="n">
-        <v>0.003596600751097</v>
+        <v>0.003689115016774</v>
       </c>
       <c r="W53" t="n">
-        <v>11168.755</v>
+        <v>11103.822</v>
       </c>
       <c r="X53" t="n">
-        <v>16.40243063365401</v>
+        <v>16.72653184311598</v>
       </c>
       <c r="Y53" t="n">
-        <v>6.1702</v>
+        <v>6.1798</v>
       </c>
       <c r="Z53" t="n">
-        <v>0.009061554085104</v>
+        <v>0.009309102891246999</v>
       </c>
       <c r="AA53" t="n">
-        <v>84.224</v>
+        <v>84.193</v>
       </c>
       <c r="AB53" t="n">
-        <v>0.123691344083461</v>
+        <v>0.126826321195302</v>
       </c>
       <c r="AC53" t="n">
         <v>666.465</v>
       </c>
       <c r="AD53" t="n">
-        <v>0.978770322409098</v>
+        <v>1.003946933301191</v>
       </c>
       <c r="AE53" t="n">
-        <v>28.15159904163512</v>
+        <v>28.74066724854835</v>
       </c>
     </row>
     <row r="54">
@@ -5329,89 +5323,89 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>08月</t>
+          <t>05月</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2025/08</t>
+          <t>2025/05</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>19241.6713</v>
+        <v>19209.2769</v>
       </c>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="n">
-        <v>7240.1916</v>
+        <v>7237.4036</v>
       </c>
       <c r="H54" t="n">
-        <v>10.60963367383992</v>
+        <v>10.70277131208823</v>
       </c>
       <c r="I54" t="n">
         <v>6111.384</v>
       </c>
       <c r="J54" t="n">
-        <v>8.955501326811088</v>
+        <v>9.037598145328669</v>
       </c>
       <c r="K54" t="n">
-        <v>635.5196</v>
+        <v>632.7316</v>
       </c>
       <c r="L54" t="n">
-        <v>0.931277861285505</v>
+        <v>0.935692133672314</v>
       </c>
       <c r="M54" t="n">
         <v>493.288</v>
       </c>
       <c r="N54" t="n">
-        <v>0.722854485743326</v>
+        <v>0.72948103308725</v>
       </c>
       <c r="O54" t="inlineStr"/>
       <c r="P54" t="inlineStr"/>
       <c r="Q54" t="n">
-        <v>12001.4797</v>
+        <v>11971.8733</v>
       </c>
       <c r="R54" t="n">
-        <v>17.58673115239467</v>
+        <v>17.70416978088594</v>
       </c>
       <c r="S54" t="n">
         <v>3.5405</v>
       </c>
       <c r="T54" t="n">
-        <v>0.00518817872475</v>
+        <v>0.005235739765908</v>
       </c>
       <c r="U54" t="n">
         <v>2.449</v>
       </c>
       <c r="V54" t="n">
-        <v>0.003588716197405</v>
+        <v>0.003621614655193</v>
       </c>
       <c r="W54" t="n">
-        <v>11238.371</v>
+        <v>11209.065</v>
       </c>
       <c r="X54" t="n">
-        <v>16.46848674566927</v>
+        <v>16.5761184463075</v>
       </c>
       <c r="Y54" t="n">
-        <v>6.1702</v>
+        <v>6.1798</v>
       </c>
       <c r="Z54" t="n">
-        <v>0.009041689130758</v>
+        <v>0.009138772660743</v>
       </c>
       <c r="AA54" t="n">
-        <v>84.48399999999999</v>
+        <v>84.17400000000001</v>
       </c>
       <c r="AB54" t="n">
-        <v>0.123801183838932</v>
+        <v>0.124477661080517</v>
       </c>
       <c r="AC54" t="n">
         <v>666.465</v>
       </c>
       <c r="AD54" t="n">
-        <v>0.976624638833553</v>
+        <v>0.985577546416077</v>
       </c>
       <c r="AE54" t="n">
-        <v>28.19636482623459</v>
+        <v>28.40694109297418</v>
       </c>
     </row>
     <row r="55">
@@ -5422,89 +5416,89 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>09月</t>
+          <t>06月</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2025/09</t>
+          <t>2025/06</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>19308.6583</v>
+        <v>19315.4943</v>
       </c>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="n">
-        <v>7240.1916</v>
+        <v>7237.4036</v>
       </c>
       <c r="H55" t="n">
-        <v>10.58488079579238</v>
+        <v>10.8367118493627</v>
       </c>
       <c r="I55" t="n">
         <v>6111.384</v>
       </c>
       <c r="J55" t="n">
-        <v>8.93460763349313</v>
+        <v>9.150699763214202</v>
       </c>
       <c r="K55" t="n">
-        <v>635.5196</v>
+        <v>632.7316</v>
       </c>
       <c r="L55" t="n">
-        <v>0.92910513713334</v>
+        <v>0.947401914574202</v>
       </c>
       <c r="M55" t="n">
         <v>493.288</v>
       </c>
       <c r="N55" t="n">
-        <v>0.7211680251659131</v>
+        <v>0.738610171574296</v>
       </c>
       <c r="O55" t="inlineStr"/>
       <c r="P55" t="inlineStr"/>
       <c r="Q55" t="n">
-        <v>12068.4667</v>
+        <v>12078.0907</v>
       </c>
       <c r="R55" t="n">
-        <v>17.64363271926255</v>
+        <v>18.08477125779851</v>
       </c>
       <c r="S55" t="n">
         <v>3.5405</v>
       </c>
       <c r="T55" t="n">
-        <v>0.005176074409067</v>
+        <v>0.005301262776428</v>
       </c>
       <c r="U55" t="n">
         <v>2.449</v>
       </c>
       <c r="V55" t="n">
-        <v>0.003580343518657</v>
+        <v>0.003666937590587</v>
       </c>
       <c r="W55" t="n">
-        <v>11307.378</v>
+        <v>11315.292</v>
       </c>
       <c r="X55" t="n">
-        <v>16.53095040232986</v>
+        <v>16.94261722469077</v>
       </c>
       <c r="Y55" t="n">
         <v>6.1702</v>
       </c>
       <c r="Z55" t="n">
-        <v>0.009020594356397999</v>
+        <v>0.009238766158203</v>
       </c>
       <c r="AA55" t="n">
-        <v>84.434</v>
+        <v>84.17400000000001</v>
       </c>
       <c r="AB55" t="n">
-        <v>0.123439250573415</v>
+        <v>0.126035444977568</v>
       </c>
       <c r="AC55" t="n">
-        <v>664.495</v>
+        <v>666.465</v>
       </c>
       <c r="AD55" t="n">
-        <v>0.971466054075152</v>
+        <v>0.9979116216049509</v>
       </c>
       <c r="AE55" t="n">
-        <v>28.22851351505493</v>
+        <v>28.9214831071612</v>
       </c>
     </row>
     <row r="56">
@@ -5515,89 +5509,89 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>10月</t>
+          <t>07月</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2025/10</t>
+          <t>2025/07</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>19400.2363</v>
+        <v>19170.9063</v>
       </c>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="n">
-        <v>7267.5146</v>
+        <v>7237.4036</v>
       </c>
       <c r="H56" t="n">
-        <v>10.5969816910389</v>
+        <v>10.62855233045506</v>
       </c>
       <c r="I56" t="n">
-        <v>6138.707</v>
+        <v>6111.384</v>
       </c>
       <c r="J56" t="n">
-        <v>8.951033367810822</v>
+        <v>8.974926402543829</v>
       </c>
       <c r="K56" t="n">
-        <v>635.5196</v>
+        <v>632.7316</v>
       </c>
       <c r="L56" t="n">
-        <v>0.926670249206842</v>
+        <v>0.929203522894945</v>
       </c>
       <c r="M56" t="n">
         <v>493.288</v>
       </c>
       <c r="N56" t="n">
-        <v>0.719278074021234</v>
+        <v>0.724422405016285</v>
       </c>
       <c r="O56" t="inlineStr"/>
       <c r="P56" t="inlineStr"/>
       <c r="Q56" t="n">
-        <v>12132.7217</v>
+        <v>11933.5027</v>
       </c>
       <c r="R56" t="n">
-        <v>17.69108653973263</v>
+        <v>17.52504971984383</v>
       </c>
       <c r="S56" t="n">
         <v>3.5405</v>
       </c>
       <c r="T56" t="n">
-        <v>0.00516250957062</v>
+        <v>0.005199432228151</v>
       </c>
       <c r="U56" t="n">
         <v>2.449</v>
       </c>
       <c r="V56" t="n">
-        <v>0.003570960581401</v>
+        <v>0.003596500360611</v>
       </c>
       <c r="W56" t="n">
-        <v>11371.633</v>
+        <v>11170.654</v>
       </c>
       <c r="X56" t="n">
-        <v>16.5813202079035</v>
+        <v>16.40476159218302</v>
       </c>
       <c r="Y56" t="n">
         <v>6.1702</v>
       </c>
       <c r="Z56" t="n">
-        <v>0.008996954258618999</v>
+        <v>0.009061301153548</v>
       </c>
       <c r="AA56" t="n">
-        <v>84.434</v>
+        <v>84.224</v>
       </c>
       <c r="AB56" t="n">
-        <v>0.123115755708448</v>
+        <v>0.123687891536165</v>
       </c>
       <c r="AC56" t="n">
-        <v>664.495</v>
+        <v>666.465</v>
       </c>
       <c r="AD56" t="n">
-        <v>0.968920151710035</v>
+        <v>0.978743002382337</v>
       </c>
       <c r="AE56" t="n">
-        <v>28.28806823077153</v>
+        <v>28.15360205029889</v>
       </c>
     </row>
     <row r="57">
@@ -5608,89 +5602,89 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>11月</t>
+          <t>08月</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2025/11</t>
+          <t>2025/08</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>19437.3093</v>
+        <v>19246.8763</v>
       </c>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="n">
-        <v>7267.5146</v>
+        <v>7240.1916</v>
       </c>
       <c r="H57" t="n">
-        <v>10.57812084284302</v>
+        <v>10.60972460677555</v>
       </c>
       <c r="I57" t="n">
-        <v>6138.707</v>
+        <v>6111.384</v>
       </c>
       <c r="J57" t="n">
-        <v>8.935102031278527</v>
+        <v>8.95557808252676</v>
       </c>
       <c r="K57" t="n">
         <v>635.5196</v>
       </c>
       <c r="L57" t="n">
-        <v>0.925020931749523</v>
+        <v>0.931285843071909</v>
       </c>
       <c r="M57" t="n">
         <v>493.288</v>
       </c>
       <c r="N57" t="n">
-        <v>0.717997879814971</v>
+        <v>0.722860681176876</v>
       </c>
       <c r="O57" t="inlineStr"/>
       <c r="P57" t="inlineStr"/>
       <c r="Q57" t="n">
-        <v>12169.7947</v>
+        <v>12006.6847</v>
       </c>
       <c r="R57" t="n">
-        <v>17.71356041984292</v>
+        <v>17.59450925406248</v>
       </c>
       <c r="S57" t="n">
-        <v>4.1025</v>
+        <v>3.5405</v>
       </c>
       <c r="T57" t="n">
-        <v>0.005971331761448</v>
+        <v>0.005188223191537</v>
       </c>
       <c r="U57" t="n">
         <v>2.449</v>
       </c>
       <c r="V57" t="n">
-        <v>0.003564604871124</v>
+        <v>0.003588746955535</v>
       </c>
       <c r="W57" t="n">
-        <v>11408.144</v>
+        <v>11243.576</v>
       </c>
       <c r="X57" t="n">
-        <v>16.60495127516559</v>
+        <v>16.4762552630998</v>
       </c>
       <c r="Y57" t="n">
         <v>6.1702</v>
       </c>
       <c r="Z57" t="n">
-        <v>0.008980941190611</v>
+        <v>0.009041766625171</v>
       </c>
       <c r="AA57" t="n">
-        <v>84.434</v>
+        <v>84.48399999999999</v>
       </c>
       <c r="AB57" t="n">
-        <v>0.122896630334201</v>
+        <v>0.123802244912804</v>
       </c>
       <c r="AC57" t="n">
-        <v>664.495</v>
+        <v>666.465</v>
       </c>
       <c r="AD57" t="n">
-        <v>0.967195636519942</v>
+        <v>0.976633009277636</v>
       </c>
       <c r="AE57" t="n">
-        <v>28.29168126268594</v>
+        <v>28.20423386083803</v>
       </c>
     </row>
     <row r="58">
@@ -5701,89 +5695,89 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>12月</t>
+          <t>09月</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2025/12</t>
+          <t>2025/09</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>19576.4053</v>
+        <v>19310.2283</v>
       </c>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="n">
-        <v>7267.5146</v>
+        <v>7240.1916</v>
       </c>
       <c r="H58" t="n">
-        <v>10.40319531983682</v>
+        <v>10.58488086388101</v>
       </c>
       <c r="I58" t="n">
-        <v>6138.707</v>
+        <v>6111.384</v>
       </c>
       <c r="J58" t="n">
-        <v>8.787346355279359</v>
+        <v>8.934607690966155</v>
       </c>
       <c r="K58" t="n">
         <v>635.5196</v>
       </c>
       <c r="L58" t="n">
-        <v>0.90972428571173</v>
+        <v>0.92910514310993</v>
       </c>
       <c r="M58" t="n">
         <v>493.288</v>
       </c>
       <c r="N58" t="n">
-        <v>0.706124678845732</v>
+        <v>0.72116802980492</v>
       </c>
       <c r="O58" t="inlineStr"/>
       <c r="P58" t="inlineStr"/>
       <c r="Q58" t="n">
-        <v>12308.8907</v>
+        <v>12070.0367</v>
       </c>
       <c r="R58" t="n">
-        <v>17.6197505158948</v>
+        <v>17.64592811220237</v>
       </c>
       <c r="S58" t="n">
-        <v>4.1025</v>
+        <v>3.5405</v>
       </c>
       <c r="T58" t="n">
-        <v>0.005872586592345</v>
+        <v>0.005176074442363</v>
       </c>
       <c r="U58" t="n">
         <v>2.449</v>
       </c>
       <c r="V58" t="n">
-        <v>0.00350565863855</v>
+        <v>0.003580343541688</v>
       </c>
       <c r="W58" t="n">
-        <v>11547.285</v>
+        <v>11308.948</v>
       </c>
       <c r="X58" t="n">
-        <v>16.52953834710176</v>
+        <v>16.53324578811221</v>
       </c>
       <c r="Y58" t="n">
         <v>6.1702</v>
       </c>
       <c r="Z58" t="n">
-        <v>0.008832427493501001</v>
+        <v>0.009020594414424</v>
       </c>
       <c r="AA58" t="n">
-        <v>84.389</v>
+        <v>84.434</v>
       </c>
       <c r="AB58" t="n">
-        <v>0.120799929297109</v>
+        <v>0.123439251367454</v>
       </c>
       <c r="AC58" t="n">
         <v>664.495</v>
       </c>
       <c r="AD58" t="n">
-        <v>0.95120156677153</v>
+        <v>0.971466060324234</v>
       </c>
       <c r="AE58" t="n">
-        <v>28.02294583573162</v>
+        <v>28.23080897608337</v>
       </c>
     </row>
     <row r="59">
@@ -5794,89 +5788,89 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>01月</t>
+          <t>10月</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2026/01</t>
+          <t>2025/10</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>19597.0743</v>
+        <v>19400.2343</v>
       </c>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="n">
-        <v>7229.1146</v>
+        <v>7267.5146</v>
       </c>
       <c r="H59" t="n">
-        <v>10.28282201164236</v>
+        <v>10.59698174048459</v>
       </c>
       <c r="I59" t="n">
-        <v>6100.307</v>
+        <v>6138.707</v>
       </c>
       <c r="J59" t="n">
-        <v>8.677185875207451</v>
+        <v>8.951033409576489</v>
       </c>
       <c r="K59" t="n">
         <v>635.5196</v>
       </c>
       <c r="L59" t="n">
-        <v>0.903974455144223</v>
+        <v>0.926670253530701</v>
       </c>
       <c r="M59" t="n">
         <v>493.288</v>
       </c>
       <c r="N59" t="n">
-        <v>0.701661681290685</v>
+        <v>0.719278077377397</v>
       </c>
       <c r="O59" t="inlineStr"/>
       <c r="P59" t="inlineStr"/>
       <c r="Q59" t="n">
-        <v>12367.9597</v>
+        <v>12132.7197</v>
       </c>
       <c r="R59" t="n">
-        <v>17.59240726966282</v>
+        <v>17.69108370601933</v>
       </c>
       <c r="S59" t="n">
-        <v>4.1025</v>
+        <v>3.5405</v>
       </c>
       <c r="T59" t="n">
-        <v>0.005835469436708</v>
+        <v>0.005162509594709</v>
       </c>
       <c r="U59" t="n">
-        <v>7.897</v>
+        <v>2.449</v>
       </c>
       <c r="V59" t="n">
-        <v>0.01123283416007</v>
+        <v>0.003570960598063</v>
       </c>
       <c r="W59" t="n">
-        <v>11600.906</v>
+        <v>11371.631</v>
       </c>
       <c r="X59" t="n">
-        <v>16.50133635615541</v>
+        <v>16.58131736901203</v>
       </c>
       <c r="Y59" t="n">
         <v>6.1702</v>
       </c>
       <c r="Z59" t="n">
-        <v>0.008776602929525999</v>
+        <v>0.008996954300599</v>
       </c>
       <c r="AA59" t="n">
-        <v>84.389</v>
+        <v>84.434</v>
       </c>
       <c r="AB59" t="n">
-        <v>0.120036424203385</v>
+        <v>0.123115756282908</v>
       </c>
       <c r="AC59" t="n">
         <v>664.495</v>
       </c>
       <c r="AD59" t="n">
-        <v>0.945189582777715</v>
+        <v>0.968920156231032</v>
       </c>
       <c r="AE59" t="n">
-        <v>27.87522928130518</v>
+        <v>28.28806544650392</v>
       </c>
     </row>
     <row r="60">
@@ -5887,89 +5881,89 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>02月</t>
+          <t>11月</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2026/02</t>
+          <t>2025/11</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>19681.8633</v>
+        <v>19437.3073</v>
       </c>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="n">
-        <v>7229.1146</v>
+        <v>7267.5146</v>
       </c>
       <c r="H60" t="n">
-        <v>10.26177069119116</v>
+        <v>10.57812089211286</v>
       </c>
       <c r="I60" t="n">
-        <v>6100.307</v>
+        <v>6138.707</v>
       </c>
       <c r="J60" t="n">
-        <v>8.65942166415072</v>
+        <v>8.935102072895655</v>
       </c>
       <c r="K60" t="n">
         <v>635.5196</v>
       </c>
       <c r="L60" t="n">
-        <v>0.902123809872585</v>
+        <v>0.925020936058003</v>
       </c>
       <c r="M60" t="n">
         <v>493.288</v>
       </c>
       <c r="N60" t="n">
-        <v>0.700225217167854</v>
+        <v>0.717997883159198</v>
       </c>
       <c r="O60" t="inlineStr"/>
       <c r="P60" t="inlineStr"/>
       <c r="Q60" t="n">
-        <v>12452.7487</v>
+        <v>12169.7927</v>
       </c>
       <c r="R60" t="n">
-        <v>17.67675001782774</v>
+        <v>17.71355759127784</v>
       </c>
       <c r="S60" t="n">
         <v>4.1025</v>
       </c>
       <c r="T60" t="n">
-        <v>0.005823522877976</v>
+        <v>0.00597133178926</v>
       </c>
       <c r="U60" t="n">
-        <v>7.897</v>
+        <v>2.449</v>
       </c>
       <c r="V60" t="n">
-        <v>0.011209837944516</v>
+        <v>0.003564604887727</v>
       </c>
       <c r="W60" t="n">
-        <v>11679.818</v>
+        <v>11408.142</v>
       </c>
       <c r="X60" t="n">
-        <v>16.57957034335117</v>
+        <v>16.60494844143693</v>
       </c>
       <c r="Y60" t="n">
-        <v>16.1302</v>
+        <v>6.1702</v>
       </c>
       <c r="Z60" t="n">
-        <v>0.022896913766321</v>
+        <v>0.008980941232442001</v>
       </c>
       <c r="AA60" t="n">
-        <v>80.306</v>
+        <v>84.434</v>
       </c>
       <c r="AB60" t="n">
-        <v>0.113994839302561</v>
+        <v>0.122896630906618</v>
       </c>
       <c r="AC60" t="n">
         <v>664.495</v>
       </c>
       <c r="AD60" t="n">
-        <v>0.943254560585202</v>
+        <v>0.967195641024861</v>
       </c>
       <c r="AE60" t="n">
-        <v>27.9385207090189</v>
+        <v>28.29167848339069</v>
       </c>
     </row>
     <row r="61">
@@ -5980,89 +5974,461 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>03月</t>
+          <t>12月</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2026/03</t>
+          <t>2025/12</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>19776.7423</v>
+        <v>19576.4033</v>
       </c>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="n">
-        <v>7235.2646</v>
+        <v>7267.5146</v>
       </c>
       <c r="H61" t="n">
-        <v>10.22237454092418</v>
+        <v>10.40319536749063</v>
       </c>
       <c r="I61" t="n">
-        <v>6106.457</v>
+        <v>6138.707</v>
       </c>
       <c r="J61" t="n">
-        <v>8.627533894482349</v>
+        <v>8.787346395531461</v>
       </c>
       <c r="K61" t="n">
         <v>635.5196</v>
       </c>
       <c r="L61" t="n">
-        <v>0.897896585468114</v>
+        <v>0.909724289878894</v>
       </c>
       <c r="M61" t="n">
         <v>493.288</v>
       </c>
       <c r="N61" t="n">
-        <v>0.696944060973722</v>
+        <v>0.706124682080269</v>
       </c>
       <c r="O61" t="inlineStr"/>
       <c r="P61" t="inlineStr"/>
       <c r="Q61" t="n">
-        <v>12541.4777</v>
+        <v>12308.8887</v>
       </c>
       <c r="R61" t="n">
-        <v>17.71928041803038</v>
+        <v>17.61974773367469</v>
       </c>
       <c r="S61" t="n">
         <v>4.1025</v>
       </c>
       <c r="T61" t="n">
-        <v>0.005796234674561</v>
+        <v>0.005872586619245</v>
       </c>
       <c r="U61" t="n">
-        <v>7.897</v>
+        <v>2.449</v>
       </c>
       <c r="V61" t="n">
-        <v>0.011157310231568</v>
+        <v>0.003505658654609</v>
       </c>
       <c r="W61" t="n">
-        <v>11768.547</v>
+        <v>11547.283</v>
       </c>
       <c r="X61" t="n">
-        <v>16.62724197211388</v>
+        <v>16.52953555988773</v>
       </c>
       <c r="Y61" t="n">
-        <v>16.1302</v>
+        <v>6.1702</v>
       </c>
       <c r="Z61" t="n">
-        <v>0.022789622071322</v>
+        <v>0.008832427533959001</v>
       </c>
       <c r="AA61" t="n">
-        <v>80.306</v>
+        <v>84.389</v>
       </c>
       <c r="AB61" t="n">
-        <v>0.113460675630779</v>
+        <v>0.120799929850456</v>
       </c>
       <c r="AC61" t="n">
         <v>664.495</v>
       </c>
       <c r="AD61" t="n">
+        <v>0.951201571128689</v>
+      </c>
+      <c r="AE61" t="n">
+        <v>28.02294310116532</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>自用發電設備</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>01月</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>2026/01</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>19597.0743</v>
+      </c>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="n">
+        <v>7229.1146</v>
+      </c>
+      <c r="H62" t="n">
+        <v>10.28282201164236</v>
+      </c>
+      <c r="I62" t="n">
+        <v>6100.307</v>
+      </c>
+      <c r="J62" t="n">
+        <v>8.677185875207451</v>
+      </c>
+      <c r="K62" t="n">
+        <v>635.5196</v>
+      </c>
+      <c r="L62" t="n">
+        <v>0.903974455144223</v>
+      </c>
+      <c r="M62" t="n">
+        <v>493.288</v>
+      </c>
+      <c r="N62" t="n">
+        <v>0.701661681290685</v>
+      </c>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="n">
+        <v>12367.9597</v>
+      </c>
+      <c r="R62" t="n">
+        <v>17.59240726966282</v>
+      </c>
+      <c r="S62" t="n">
+        <v>4.1025</v>
+      </c>
+      <c r="T62" t="n">
+        <v>0.005835469436708</v>
+      </c>
+      <c r="U62" t="n">
+        <v>7.897</v>
+      </c>
+      <c r="V62" t="n">
+        <v>0.01123283416007</v>
+      </c>
+      <c r="W62" t="n">
+        <v>11600.906</v>
+      </c>
+      <c r="X62" t="n">
+        <v>16.50133635615541</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>6.1702</v>
+      </c>
+      <c r="Z62" t="n">
+        <v>0.008776602929525999</v>
+      </c>
+      <c r="AA62" t="n">
+        <v>84.389</v>
+      </c>
+      <c r="AB62" t="n">
+        <v>0.120036424203385</v>
+      </c>
+      <c r="AC62" t="n">
+        <v>664.495</v>
+      </c>
+      <c r="AD62" t="n">
+        <v>0.945189582777715</v>
+      </c>
+      <c r="AE62" t="n">
+        <v>27.87522928130518</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>自用發電設備</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>02月</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>2026/02</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>19681.8633</v>
+      </c>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="n">
+        <v>7229.1146</v>
+      </c>
+      <c r="H63" t="n">
+        <v>10.26177069119116</v>
+      </c>
+      <c r="I63" t="n">
+        <v>6100.307</v>
+      </c>
+      <c r="J63" t="n">
+        <v>8.65942166415072</v>
+      </c>
+      <c r="K63" t="n">
+        <v>635.5196</v>
+      </c>
+      <c r="L63" t="n">
+        <v>0.902123809872585</v>
+      </c>
+      <c r="M63" t="n">
+        <v>493.288</v>
+      </c>
+      <c r="N63" t="n">
+        <v>0.700225217167854</v>
+      </c>
+      <c r="O63" t="inlineStr"/>
+      <c r="P63" t="inlineStr"/>
+      <c r="Q63" t="n">
+        <v>12452.7487</v>
+      </c>
+      <c r="R63" t="n">
+        <v>17.67675001782774</v>
+      </c>
+      <c r="S63" t="n">
+        <v>4.1025</v>
+      </c>
+      <c r="T63" t="n">
+        <v>0.005823522877976</v>
+      </c>
+      <c r="U63" t="n">
+        <v>7.897</v>
+      </c>
+      <c r="V63" t="n">
+        <v>0.011209837944516</v>
+      </c>
+      <c r="W63" t="n">
+        <v>11679.818</v>
+      </c>
+      <c r="X63" t="n">
+        <v>16.57957034335117</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>16.1302</v>
+      </c>
+      <c r="Z63" t="n">
+        <v>0.022896913766321</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>80.306</v>
+      </c>
+      <c r="AB63" t="n">
+        <v>0.113994839302561</v>
+      </c>
+      <c r="AC63" t="n">
+        <v>664.495</v>
+      </c>
+      <c r="AD63" t="n">
+        <v>0.943254560585202</v>
+      </c>
+      <c r="AE63" t="n">
+        <v>27.9385207090189</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>自用發電設備</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>03月</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>2026/03</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>19776.7423</v>
+      </c>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="n">
+        <v>7235.2646</v>
+      </c>
+      <c r="H64" t="n">
+        <v>10.22237454092418</v>
+      </c>
+      <c r="I64" t="n">
+        <v>6106.457</v>
+      </c>
+      <c r="J64" t="n">
+        <v>8.627533894482349</v>
+      </c>
+      <c r="K64" t="n">
+        <v>635.5196</v>
+      </c>
+      <c r="L64" t="n">
+        <v>0.897896585468114</v>
+      </c>
+      <c r="M64" t="n">
+        <v>493.288</v>
+      </c>
+      <c r="N64" t="n">
+        <v>0.696944060973722</v>
+      </c>
+      <c r="O64" t="inlineStr"/>
+      <c r="P64" t="inlineStr"/>
+      <c r="Q64" t="n">
+        <v>12541.4777</v>
+      </c>
+      <c r="R64" t="n">
+        <v>17.71928041803038</v>
+      </c>
+      <c r="S64" t="n">
+        <v>4.1025</v>
+      </c>
+      <c r="T64" t="n">
+        <v>0.005796234674561</v>
+      </c>
+      <c r="U64" t="n">
+        <v>7.897</v>
+      </c>
+      <c r="V64" t="n">
+        <v>0.011157310231568</v>
+      </c>
+      <c r="W64" t="n">
+        <v>11768.547</v>
+      </c>
+      <c r="X64" t="n">
+        <v>16.62724197211388</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>16.1302</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>0.022789622071322</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>80.306</v>
+      </c>
+      <c r="AB64" t="n">
+        <v>0.113460675630779</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>664.495</v>
+      </c>
+      <c r="AD64" t="n">
         <v>0.938834603308276</v>
       </c>
-      <c r="AE61" t="n">
+      <c r="AE64" t="n">
         <v>27.94165495895456</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>自用發電設備</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>04月</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>2026/04</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>19832.8473</v>
+      </c>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="n">
+        <v>7235.2646</v>
+      </c>
+      <c r="H65" t="n">
+        <v>10.1900140301765</v>
+      </c>
+      <c r="I65" t="n">
+        <v>6106.457</v>
+      </c>
+      <c r="J65" t="n">
+        <v>8.600222098949843</v>
+      </c>
+      <c r="K65" t="n">
+        <v>635.5196</v>
+      </c>
+      <c r="L65" t="n">
+        <v>0.8950541546818001</v>
+      </c>
+      <c r="M65" t="n">
+        <v>493.288</v>
+      </c>
+      <c r="N65" t="n">
+        <v>0.694737776544856</v>
+      </c>
+      <c r="O65" t="inlineStr"/>
+      <c r="P65" t="inlineStr"/>
+      <c r="Q65" t="n">
+        <v>12597.5827</v>
+      </c>
+      <c r="R65" t="n">
+        <v>17.74220454346738</v>
+      </c>
+      <c r="S65" t="n">
+        <v>4.4675</v>
+      </c>
+      <c r="T65" t="n">
+        <v>0.006291945104511</v>
+      </c>
+      <c r="U65" t="n">
+        <v>7.897</v>
+      </c>
+      <c r="V65" t="n">
+        <v>0.011121990037006</v>
+      </c>
+      <c r="W65" t="n">
+        <v>11824.862</v>
+      </c>
+      <c r="X65" t="n">
+        <v>16.65391887463258</v>
+      </c>
+      <c r="Y65" t="n">
+        <v>16.1302</v>
+      </c>
+      <c r="Z65" t="n">
+        <v>0.022717477990999</v>
+      </c>
+      <c r="AA65" t="n">
+        <v>79.73099999999999</v>
+      </c>
+      <c r="AB65" t="n">
+        <v>0.112291678819874</v>
+      </c>
+      <c r="AC65" t="n">
+        <v>664.495</v>
+      </c>
+      <c r="AD65" t="n">
+        <v>0.935862576882417</v>
+      </c>
+      <c r="AE65" t="n">
+        <v>27.93221857364388</v>
       </c>
     </row>
   </sheetData>
@@ -8035,37 +8401,37 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>69858.48459599999</v>
+        <v>69858.484276</v>
       </c>
       <c r="E20" t="n">
         <v>2602</v>
       </c>
       <c r="F20" t="n">
-        <v>3.724672836875404</v>
+        <v>3.724672853936972</v>
       </c>
       <c r="G20" t="n">
         <v>44384.4736</v>
       </c>
       <c r="H20" t="n">
-        <v>63.53483597115042</v>
+        <v>63.53483626218377</v>
       </c>
       <c r="I20" t="n">
         <v>19309.007</v>
       </c>
       <c r="J20" t="n">
-        <v>27.64017443502576</v>
+        <v>27.6401745616368</v>
       </c>
       <c r="K20" t="n">
         <v>2228.4696</v>
       </c>
       <c r="L20" t="n">
-        <v>3.189977012652803</v>
+        <v>3.189977027265096</v>
       </c>
       <c r="M20" t="n">
         <v>22846.997</v>
       </c>
       <c r="N20" t="n">
-        <v>32.70468452347188</v>
+        <v>32.70468467328188</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -8074,46 +8440,46 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>22872.010996</v>
+        <v>22872.010676</v>
       </c>
       <c r="R20" t="n">
-        <v>32.74049119197414</v>
+        <v>32.74049088387925</v>
       </c>
       <c r="S20" t="n">
         <v>2124.4215</v>
       </c>
       <c r="T20" t="n">
-        <v>3.041035762922405</v>
+        <v>3.041035776852445</v>
       </c>
       <c r="U20" t="n">
         <v>7.489</v>
       </c>
       <c r="V20" t="n">
-        <v>0.010720243995142</v>
+        <v>0.010720244044248</v>
       </c>
       <c r="W20" t="n">
-        <v>15474.020296</v>
+        <v>15474.019976</v>
       </c>
       <c r="X20" t="n">
-        <v>22.15052385617597</v>
+        <v>22.15052349957173</v>
       </c>
       <c r="Y20" t="n">
         <v>4517.1962</v>
       </c>
       <c r="Z20" t="n">
-        <v>6.466209832811988</v>
+        <v>6.466209862431685</v>
       </c>
       <c r="AA20" t="n">
         <v>84.389</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.120799929297109</v>
+        <v>0.120799929850456</v>
       </c>
       <c r="AC20" t="n">
         <v>664.495</v>
       </c>
       <c r="AD20" t="n">
-        <v>0.95120156677153</v>
+        <v>0.951201571128689</v>
       </c>
       <c r="AE20" t="inlineStr"/>
     </row>
@@ -9859,31 +10225,31 @@
         <v>2602</v>
       </c>
       <c r="F40" t="n">
-        <v>3.724672836875404</v>
+        <v>3.724672853936972</v>
       </c>
       <c r="G40" t="n">
         <v>27247.981</v>
       </c>
       <c r="H40" t="n">
-        <v>39.00454061890741</v>
+        <v>39.00454079757509</v>
       </c>
       <c r="I40" t="n">
         <v>10050</v>
       </c>
       <c r="J40" t="n">
-        <v>14.38622675272782</v>
+        <v>14.38622681862666</v>
       </c>
       <c r="K40" t="n">
         <v>1592.95</v>
       </c>
       <c r="L40" t="n">
-        <v>2.280252726941074</v>
+        <v>2.280252737386203</v>
       </c>
       <c r="M40" t="n">
         <v>15605.031</v>
       </c>
       <c r="N40" t="n">
-        <v>22.33806113923851</v>
+        <v>22.33806124156223</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -9895,38 +10261,38 @@
         <v>2811.546995</v>
       </c>
       <c r="R40" t="n">
-        <v>4.02463209910652</v>
+        <v>4.024632117542109</v>
       </c>
       <c r="S40" t="n">
         <v>2076.328</v>
       </c>
       <c r="T40" t="n">
-        <v>2.972191584182872</v>
+        <v>2.972191597797557</v>
       </c>
       <c r="U40" t="n">
         <v>0.84</v>
       </c>
       <c r="V40" t="n">
-        <v>0.001202430892765</v>
+        <v>0.001202430898273</v>
       </c>
       <c r="W40" t="n">
         <v>292.238995</v>
       </c>
       <c r="X40" t="n">
-        <v>0.41832999483177</v>
+        <v>0.41832999674801</v>
       </c>
       <c r="Y40" t="n">
         <v>442.14</v>
       </c>
       <c r="Z40" t="n">
-        <v>0.632908089199113</v>
+        <v>0.632908092098268</v>
       </c>
       <c r="AA40" t="inlineStr"/>
       <c r="AB40" t="inlineStr"/>
       <c r="AC40" t="inlineStr"/>
       <c r="AD40" t="inlineStr"/>
       <c r="AE40" t="n">
-        <v>46.75384555488934</v>
+        <v>46.75384576905417</v>
       </c>
     </row>
     <row r="41">
@@ -11449,7 +11815,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>17620.551301</v>
+        <v>17620.552981</v>
       </c>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr"/>
@@ -11457,13 +11823,13 @@
         <v>9868.977999999999</v>
       </c>
       <c r="H60" t="n">
-        <v>14.1271000324062</v>
+        <v>14.12710009711806</v>
       </c>
       <c r="I60" t="n">
         <v>3120.3</v>
       </c>
       <c r="J60" t="n">
-        <v>4.466601327018569</v>
+        <v>4.466601347478683</v>
       </c>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
@@ -11471,46 +11837,46 @@
         <v>6748.678</v>
       </c>
       <c r="N60" t="n">
-        <v>9.660498705387633</v>
+        <v>9.660498749639377</v>
       </c>
       <c r="O60" t="inlineStr"/>
       <c r="P60" t="inlineStr"/>
       <c r="Q60" t="n">
-        <v>7751.573301</v>
+        <v>7751.574981</v>
       </c>
       <c r="R60" t="n">
-        <v>11.09610857697283</v>
+        <v>11.09611103266245</v>
       </c>
       <c r="S60" t="n">
         <v>43.991</v>
       </c>
       <c r="T60" t="n">
-        <v>0.062971592147189</v>
+        <v>0.062971592435642</v>
       </c>
       <c r="U60" t="n">
         <v>4.2</v>
       </c>
       <c r="V60" t="n">
-        <v>0.006012154463827</v>
+        <v>0.006012154491366</v>
       </c>
       <c r="W60" t="n">
-        <v>3634.496301</v>
+        <v>3634.497981</v>
       </c>
       <c r="X60" t="n">
-        <v>5.20265551424244</v>
+        <v>5.202657942935985</v>
       </c>
       <c r="Y60" t="n">
         <v>4068.886</v>
       </c>
       <c r="Z60" t="n">
-        <v>5.824469316119373</v>
+        <v>5.824469342799457</v>
       </c>
       <c r="AA60" t="inlineStr"/>
       <c r="AB60" t="inlineStr"/>
       <c r="AC60" t="inlineStr"/>
       <c r="AD60" t="inlineStr"/>
       <c r="AE60" t="n">
-        <v>25.22320860937903</v>
+        <v>25.22321112978051</v>
       </c>
     </row>
     <row r="61">
@@ -13249,7 +13615,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>19576.4053</v>
+        <v>19576.4033</v>
       </c>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr"/>
@@ -13257,72 +13623,72 @@
         <v>7267.5146</v>
       </c>
       <c r="H80" t="n">
-        <v>10.40319531983682</v>
+        <v>10.40319536749063</v>
       </c>
       <c r="I80" t="n">
         <v>6138.707</v>
       </c>
       <c r="J80" t="n">
-        <v>8.787346355279359</v>
+        <v>8.787346395531461</v>
       </c>
       <c r="K80" t="n">
         <v>635.5196</v>
       </c>
       <c r="L80" t="n">
-        <v>0.90972428571173</v>
+        <v>0.909724289878894</v>
       </c>
       <c r="M80" t="n">
         <v>493.288</v>
       </c>
       <c r="N80" t="n">
-        <v>0.706124678845732</v>
+        <v>0.706124682080269</v>
       </c>
       <c r="O80" t="inlineStr"/>
       <c r="P80" t="inlineStr"/>
       <c r="Q80" t="n">
-        <v>12308.8907</v>
+        <v>12308.8887</v>
       </c>
       <c r="R80" t="n">
-        <v>17.6197505158948</v>
+        <v>17.61974773367469</v>
       </c>
       <c r="S80" t="n">
         <v>4.1025</v>
       </c>
       <c r="T80" t="n">
-        <v>0.005872586592345</v>
+        <v>0.005872586619245</v>
       </c>
       <c r="U80" t="n">
         <v>2.449</v>
       </c>
       <c r="V80" t="n">
-        <v>0.00350565863855</v>
+        <v>0.003505658654609</v>
       </c>
       <c r="W80" t="n">
-        <v>11547.285</v>
+        <v>11547.283</v>
       </c>
       <c r="X80" t="n">
-        <v>16.52953834710176</v>
+        <v>16.52953555988773</v>
       </c>
       <c r="Y80" t="n">
         <v>6.1702</v>
       </c>
       <c r="Z80" t="n">
-        <v>0.008832427493501001</v>
+        <v>0.008832427533959001</v>
       </c>
       <c r="AA80" t="n">
         <v>84.389</v>
       </c>
       <c r="AB80" t="n">
-        <v>0.120799929297109</v>
+        <v>0.120799929850456</v>
       </c>
       <c r="AC80" t="n">
         <v>664.495</v>
       </c>
       <c r="AD80" t="n">
-        <v>0.95120156677153</v>
+        <v>0.951201571128689</v>
       </c>
       <c r="AE80" t="n">
-        <v>28.02294583573162</v>
+        <v>28.02294310116532</v>
       </c>
     </row>
     <row r="81">

--- a/output/zone_monthly_3_03/installed_capacity_3_03.xlsx
+++ b/output/zone_monthly_3_03/installed_capacity_3_03.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE65"/>
+  <dimension ref="A1:AE69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2162,95 +2162,101 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>台電</t>
+          <t>全國</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>01月</t>
+          <t>05月</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2025/01</t>
+          <t>2026/05</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>32516.151795</v>
+        <v>71323.981531</v>
       </c>
       <c r="E18" t="n">
         <v>2602</v>
       </c>
       <c r="F18" t="n">
-        <v>3.890402808732041</v>
+        <v>3.648141822914185</v>
       </c>
       <c r="G18" t="n">
-        <v>26145.89</v>
+        <v>44714.3656</v>
       </c>
       <c r="H18" t="n">
-        <v>39.0922536098382</v>
+        <v>62.69190900477913</v>
       </c>
       <c r="I18" t="n">
-        <v>10600</v>
+        <v>19322.757</v>
       </c>
       <c r="J18" t="n">
-        <v>15.84868169583383</v>
+        <v>27.091528803116</v>
       </c>
       <c r="K18" t="n">
-        <v>1592.488</v>
+        <v>2231.4696</v>
       </c>
       <c r="L18" t="n">
-        <v>2.381022209097644</v>
+        <v>3.128638575834584</v>
       </c>
       <c r="M18" t="n">
-        <v>13953.402</v>
+        <v>23160.139</v>
       </c>
       <c r="N18" t="n">
-        <v>20.86254970490672</v>
+        <v>32.47174162582856</v>
       </c>
       <c r="O18" t="n">
-        <v>951</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.421895876673394</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>2817.261795</v>
+        <v>24007.615931</v>
       </c>
       <c r="R18" t="n">
-        <v>4.212253343659289</v>
+        <v>33.65994917230667</v>
       </c>
       <c r="S18" t="n">
-        <v>2076.328</v>
+        <v>2124.7865</v>
       </c>
       <c r="T18" t="n">
-        <v>3.104439770579931</v>
+        <v>2.979063218836838</v>
       </c>
       <c r="U18" t="n">
-        <v>0.84</v>
+        <v>12.937</v>
       </c>
       <c r="V18" t="n">
-        <v>0.001255933266462</v>
+        <v>0.018138359247902</v>
       </c>
       <c r="W18" t="n">
-        <v>291.653795</v>
+        <v>15914.412231</v>
       </c>
       <c r="X18" t="n">
-        <v>0.436068694560092</v>
+        <v>22.31284890353887</v>
       </c>
       <c r="Y18" t="n">
-        <v>448.44</v>
+        <v>5195.9842</v>
       </c>
       <c r="Z18" t="n">
-        <v>0.670488945252804</v>
-      </c>
-      <c r="AA18" t="inlineStr"/>
-      <c r="AB18" t="inlineStr"/>
-      <c r="AC18" t="inlineStr"/>
-      <c r="AD18" t="inlineStr"/>
-      <c r="AE18" t="n">
-        <v>48.61680563890292</v>
-      </c>
+        <v>7.285045069646926</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>79.501</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.111464613014412</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>679.995</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.953389008021726</v>
+      </c>
+      <c r="AE18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2260,89 +2266,89 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>02月</t>
+          <t>01月</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2025/02</t>
+          <t>2025/01</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>32513.967795</v>
+        <v>32516.151795</v>
       </c>
       <c r="E19" t="n">
         <v>2602</v>
       </c>
       <c r="F19" t="n">
-        <v>3.887482054717989</v>
+        <v>3.890402808732041</v>
       </c>
       <c r="G19" t="n">
-        <v>26143.706</v>
+        <v>26145.89</v>
       </c>
       <c r="H19" t="n">
-        <v>39.05964178279133</v>
+        <v>39.0922536098382</v>
       </c>
       <c r="I19" t="n">
         <v>10600</v>
       </c>
       <c r="J19" t="n">
-        <v>15.83678315911249</v>
+        <v>15.84868169583383</v>
       </c>
       <c r="K19" t="n">
-        <v>1590.304</v>
+        <v>1592.488</v>
       </c>
       <c r="L19" t="n">
-        <v>2.375971660855587</v>
+        <v>2.381022209097644</v>
       </c>
       <c r="M19" t="n">
         <v>13953.402</v>
       </c>
       <c r="N19" t="n">
-        <v>20.84688696282325</v>
+        <v>20.86254970490672</v>
       </c>
       <c r="O19" t="n">
         <v>951</v>
       </c>
       <c r="P19" t="n">
-        <v>1.420828375878865</v>
+        <v>1.421895876673394</v>
       </c>
       <c r="Q19" t="n">
         <v>2817.261795</v>
       </c>
       <c r="R19" t="n">
-        <v>4.209090957534624</v>
+        <v>4.212253343659289</v>
       </c>
       <c r="S19" t="n">
         <v>2076.328</v>
       </c>
       <c r="T19" t="n">
-        <v>3.102109085206954</v>
+        <v>3.104439770579931</v>
       </c>
       <c r="U19" t="n">
         <v>0.84</v>
       </c>
       <c r="V19" t="n">
-        <v>0.001254990363552</v>
+        <v>0.001255933266462</v>
       </c>
       <c r="W19" t="n">
         <v>291.653795</v>
       </c>
       <c r="X19" t="n">
-        <v>0.435741312164834</v>
+        <v>0.436068694560092</v>
       </c>
       <c r="Y19" t="n">
         <v>448.44</v>
       </c>
       <c r="Z19" t="n">
-        <v>0.669985569799283</v>
+        <v>0.670488945252804</v>
       </c>
       <c r="AA19" t="inlineStr"/>
       <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr"/>
       <c r="AE19" t="n">
-        <v>48.57704317092281</v>
+        <v>48.61680563890292</v>
       </c>
     </row>
     <row r="20">
@@ -2353,89 +2359,89 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>03月</t>
+          <t>02月</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2025/03</t>
+          <t>2025/02</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>32515.613795</v>
+        <v>32513.967795</v>
       </c>
       <c r="E20" t="n">
         <v>2602</v>
       </c>
       <c r="F20" t="n">
-        <v>3.880977738529859</v>
+        <v>3.887482054717989</v>
       </c>
       <c r="G20" t="n">
-        <v>26145.352</v>
+        <v>26143.706</v>
       </c>
       <c r="H20" t="n">
-        <v>38.99674445735093</v>
+        <v>39.05964178279133</v>
       </c>
       <c r="I20" t="n">
         <v>10600</v>
       </c>
       <c r="J20" t="n">
-        <v>15.81028594481803</v>
+        <v>15.83678315911249</v>
       </c>
       <c r="K20" t="n">
-        <v>1591.95</v>
+        <v>1590.304</v>
       </c>
       <c r="L20" t="n">
-        <v>2.374451387721986</v>
+        <v>2.375971660855587</v>
       </c>
       <c r="M20" t="n">
         <v>13953.402</v>
       </c>
       <c r="N20" t="n">
-        <v>20.81200712481092</v>
+        <v>20.84688696282325</v>
       </c>
       <c r="O20" t="n">
         <v>951</v>
       </c>
       <c r="P20" t="n">
-        <v>1.418451125803957</v>
+        <v>1.420828375878865</v>
       </c>
       <c r="Q20" t="n">
         <v>2817.261795</v>
       </c>
       <c r="R20" t="n">
-        <v>4.202048543430312</v>
+        <v>4.209090957534624</v>
       </c>
       <c r="S20" t="n">
         <v>2076.328</v>
       </c>
       <c r="T20" t="n">
-        <v>3.096918810870955</v>
+        <v>3.102109085206954</v>
       </c>
       <c r="U20" t="n">
         <v>0.84</v>
       </c>
       <c r="V20" t="n">
-        <v>0.001252890584306</v>
+        <v>0.001254990363552</v>
       </c>
       <c r="W20" t="n">
         <v>291.653795</v>
       </c>
       <c r="X20" t="n">
-        <v>0.435012254324655</v>
+        <v>0.435741312164834</v>
       </c>
       <c r="Y20" t="n">
         <v>448.44</v>
       </c>
       <c r="Z20" t="n">
-        <v>0.668864587650396</v>
+        <v>0.669985569799283</v>
       </c>
       <c r="AA20" t="inlineStr"/>
       <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr"/>
       <c r="AE20" t="n">
-        <v>48.49822186511506</v>
+        <v>48.57704317092281</v>
       </c>
     </row>
     <row r="21">
@@ -2446,89 +2452,89 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>04月</t>
+          <t>03月</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2025/04</t>
+          <t>2025/03</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>31743.613795</v>
+        <v>32515.613795</v>
       </c>
       <c r="E21" t="n">
         <v>2602</v>
       </c>
       <c r="F21" t="n">
-        <v>3.919590556817985</v>
+        <v>3.880977738529859</v>
       </c>
       <c r="G21" t="n">
-        <v>25373.352</v>
+        <v>26145.352</v>
       </c>
       <c r="H21" t="n">
-        <v>38.22181048963056</v>
+        <v>38.99674445735093</v>
       </c>
       <c r="I21" t="n">
         <v>10600</v>
       </c>
       <c r="J21" t="n">
-        <v>15.96758643438533</v>
+        <v>15.81028594481803</v>
       </c>
       <c r="K21" t="n">
         <v>1591.95</v>
       </c>
       <c r="L21" t="n">
-        <v>2.398075398511295</v>
+        <v>2.374451387721986</v>
       </c>
       <c r="M21" t="n">
-        <v>13181.402</v>
+        <v>13953.402</v>
       </c>
       <c r="N21" t="n">
-        <v>19.85614865673393</v>
+        <v>20.81200712481092</v>
       </c>
       <c r="O21" t="n">
         <v>951</v>
       </c>
       <c r="P21" t="n">
-        <v>1.432563650858533</v>
+        <v>1.418451125803957</v>
       </c>
       <c r="Q21" t="n">
         <v>2817.261795</v>
       </c>
       <c r="R21" t="n">
-        <v>4.243855775467365</v>
+        <v>4.202048543430312</v>
       </c>
       <c r="S21" t="n">
         <v>2076.328</v>
       </c>
       <c r="T21" t="n">
-        <v>3.127730830767399</v>
+        <v>3.096918810870955</v>
       </c>
       <c r="U21" t="n">
         <v>0.84</v>
       </c>
       <c r="V21" t="n">
-        <v>0.001265355906121</v>
+        <v>0.001252890584306</v>
       </c>
       <c r="W21" t="n">
         <v>291.653795</v>
       </c>
       <c r="X21" t="n">
-        <v>0.439340300054623</v>
+        <v>0.435012254324655</v>
       </c>
       <c r="Y21" t="n">
         <v>448.44</v>
       </c>
       <c r="Z21" t="n">
-        <v>0.675519288739222</v>
+        <v>0.668864587650396</v>
       </c>
       <c r="AA21" t="inlineStr"/>
       <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr"/>
       <c r="AE21" t="n">
-        <v>47.81782047277444</v>
+        <v>48.49822186511506</v>
       </c>
     </row>
     <row r="22">
@@ -2539,12 +2545,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>05月</t>
+          <t>04月</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2025/05</t>
+          <t>2025/04</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -2554,74 +2560,74 @@
         <v>2602</v>
       </c>
       <c r="F22" t="n">
-        <v>3.8478731452884</v>
+        <v>3.919590556817985</v>
       </c>
       <c r="G22" t="n">
         <v>25373.352</v>
       </c>
       <c r="H22" t="n">
-        <v>37.52245955678313</v>
+        <v>38.22181048963056</v>
       </c>
       <c r="I22" t="n">
         <v>10600</v>
       </c>
       <c r="J22" t="n">
-        <v>15.67542480401885</v>
+        <v>15.96758643438533</v>
       </c>
       <c r="K22" t="n">
         <v>1591.95</v>
       </c>
       <c r="L22" t="n">
-        <v>2.354197407241302</v>
+        <v>2.398075398511295</v>
       </c>
       <c r="M22" t="n">
         <v>13181.402</v>
       </c>
       <c r="N22" t="n">
-        <v>19.49283734552298</v>
+        <v>19.85614865673393</v>
       </c>
       <c r="O22" t="n">
         <v>951</v>
       </c>
       <c r="P22" t="n">
-        <v>1.406351791379426</v>
+        <v>1.432563650858533</v>
       </c>
       <c r="Q22" t="n">
         <v>2817.261795</v>
       </c>
       <c r="R22" t="n">
-        <v>4.166205228373363</v>
+        <v>4.243855775467365</v>
       </c>
       <c r="S22" t="n">
         <v>2076.328</v>
       </c>
       <c r="T22" t="n">
-        <v>3.070502210611212</v>
+        <v>3.127730830767399</v>
       </c>
       <c r="U22" t="n">
         <v>0.84</v>
       </c>
       <c r="V22" t="n">
-        <v>0.001242203475035</v>
+        <v>0.001265355906121</v>
       </c>
       <c r="W22" t="n">
         <v>291.653795</v>
       </c>
       <c r="X22" t="n">
-        <v>0.431301616257474</v>
+        <v>0.439340300054623</v>
       </c>
       <c r="Y22" t="n">
         <v>448.44</v>
       </c>
       <c r="Z22" t="n">
-        <v>0.663159198029642</v>
+        <v>0.675519288739222</v>
       </c>
       <c r="AA22" t="inlineStr"/>
       <c r="AB22" t="inlineStr"/>
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr"/>
       <c r="AE22" t="n">
-        <v>46.94288972182432</v>
+        <v>47.81782047277444</v>
       </c>
     </row>
     <row r="23">
@@ -2632,89 +2638,89 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>06月</t>
+          <t>05月</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2025/06</t>
+          <t>2025/05</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>30791.113795</v>
+        <v>31743.613795</v>
       </c>
       <c r="E23" t="n">
         <v>2602</v>
       </c>
       <c r="F23" t="n">
-        <v>3.896027607475386</v>
+        <v>3.8478731452884</v>
       </c>
       <c r="G23" t="n">
         <v>25373.352</v>
       </c>
       <c r="H23" t="n">
-        <v>37.99203685095726</v>
+        <v>37.52245955678313</v>
       </c>
       <c r="I23" t="n">
         <v>10600</v>
       </c>
       <c r="J23" t="n">
-        <v>15.87159594129096</v>
+        <v>15.67542480401885</v>
       </c>
       <c r="K23" t="n">
         <v>1591.95</v>
       </c>
       <c r="L23" t="n">
-        <v>2.383659165918693</v>
+        <v>2.354197407241302</v>
       </c>
       <c r="M23" t="n">
         <v>13181.402</v>
       </c>
       <c r="N23" t="n">
-        <v>19.73678174374761</v>
+        <v>19.49283734552298</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>951</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.406351791379426</v>
       </c>
       <c r="Q23" t="n">
-        <v>2815.761795</v>
+        <v>2817.261795</v>
       </c>
       <c r="R23" t="n">
-        <v>4.216097497845676</v>
+        <v>4.166205228373363</v>
       </c>
       <c r="S23" t="n">
         <v>2076.328</v>
       </c>
       <c r="T23" t="n">
-        <v>3.108928212980074</v>
+        <v>3.070502210611212</v>
       </c>
       <c r="U23" t="n">
         <v>0.84</v>
       </c>
       <c r="V23" t="n">
-        <v>0.001257749112329</v>
+        <v>0.001242203475035</v>
       </c>
       <c r="W23" t="n">
         <v>291.653795</v>
       </c>
       <c r="X23" t="n">
-        <v>0.436699168772086</v>
+        <v>0.431301616257474</v>
       </c>
       <c r="Y23" t="n">
-        <v>446.94</v>
+        <v>448.44</v>
       </c>
       <c r="Z23" t="n">
-        <v>0.669212366981187</v>
+        <v>0.663159198029642</v>
       </c>
       <c r="AA23" t="inlineStr"/>
       <c r="AB23" t="inlineStr"/>
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr"/>
       <c r="AE23" t="n">
-        <v>46.10416195627833</v>
+        <v>46.94288972182432</v>
       </c>
     </row>
     <row r="24">
@@ -2725,46 +2731,46 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>07月</t>
+          <t>06月</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2025/07</t>
+          <t>2025/06</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>31916.742795</v>
+        <v>30791.113795</v>
       </c>
       <c r="E24" t="n">
         <v>2602</v>
       </c>
       <c r="F24" t="n">
-        <v>3.821189848227349</v>
+        <v>3.896027607475386</v>
       </c>
       <c r="G24" t="n">
-        <v>26498.981</v>
+        <v>25373.352</v>
       </c>
       <c r="H24" t="n">
-        <v>38.91531021735948</v>
+        <v>37.99203685095726</v>
       </c>
       <c r="I24" t="n">
         <v>10600</v>
       </c>
       <c r="J24" t="n">
-        <v>15.56672267148728</v>
+        <v>15.87159594129096</v>
       </c>
       <c r="K24" t="n">
-        <v>1593.95</v>
+        <v>1591.95</v>
       </c>
       <c r="L24" t="n">
-        <v>2.340809207756334</v>
+        <v>2.383659165918693</v>
       </c>
       <c r="M24" t="n">
-        <v>14305.031</v>
+        <v>13181.402</v>
       </c>
       <c r="N24" t="n">
-        <v>21.00777833811588</v>
+        <v>19.73678174374761</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -2776,38 +2782,38 @@
         <v>2815.761795</v>
       </c>
       <c r="R24" t="n">
-        <v>4.135111601107001</v>
+        <v>4.216097497845676</v>
       </c>
       <c r="S24" t="n">
         <v>2076.328</v>
       </c>
       <c r="T24" t="n">
-        <v>3.049209636890927</v>
+        <v>3.108928212980074</v>
       </c>
       <c r="U24" t="n">
         <v>0.84</v>
       </c>
       <c r="V24" t="n">
-        <v>0.001233589343778</v>
+        <v>0.001257749112329</v>
       </c>
       <c r="W24" t="n">
         <v>291.653795</v>
       </c>
       <c r="X24" t="n">
-        <v>0.428310730457717</v>
+        <v>0.436699168772086</v>
       </c>
       <c r="Y24" t="n">
         <v>446.94</v>
       </c>
       <c r="Z24" t="n">
-        <v>0.656357644414578</v>
+        <v>0.669212366981187</v>
       </c>
       <c r="AA24" t="inlineStr"/>
       <c r="AB24" t="inlineStr"/>
       <c r="AC24" t="inlineStr"/>
       <c r="AD24" t="inlineStr"/>
       <c r="AE24" t="n">
-        <v>46.87161166669384</v>
+        <v>46.10416195627833</v>
       </c>
     </row>
     <row r="25">
@@ -2818,46 +2824,46 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>08月</t>
+          <t>07月</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2025/08</t>
+          <t>2025/07</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>31914.927995</v>
+        <v>31916.742795</v>
       </c>
       <c r="E25" t="n">
         <v>2602</v>
       </c>
       <c r="F25" t="n">
-        <v>3.812952053206708</v>
+        <v>3.821189848227349</v>
       </c>
       <c r="G25" t="n">
         <v>26498.981</v>
       </c>
       <c r="H25" t="n">
-        <v>38.8314158385225</v>
+        <v>38.91531021735948</v>
       </c>
       <c r="I25" t="n">
         <v>10600</v>
       </c>
       <c r="J25" t="n">
-        <v>15.53316362951234</v>
+        <v>15.56672267148728</v>
       </c>
       <c r="K25" t="n">
         <v>1593.95</v>
       </c>
       <c r="L25" t="n">
-        <v>2.335762845968037</v>
+        <v>2.340809207756334</v>
       </c>
       <c r="M25" t="n">
         <v>14305.031</v>
       </c>
       <c r="N25" t="n">
-        <v>20.96248936304213</v>
+        <v>21.00777833811588</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -2866,41 +2872,41 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>2813.946995</v>
+        <v>2815.761795</v>
       </c>
       <c r="R25" t="n">
-        <v>4.123537652651843</v>
+        <v>4.135111601107001</v>
       </c>
       <c r="S25" t="n">
         <v>2076.328</v>
       </c>
       <c r="T25" t="n">
-        <v>3.042636091748878</v>
+        <v>3.049209636890927</v>
       </c>
       <c r="U25" t="n">
         <v>0.84</v>
       </c>
       <c r="V25" t="n">
-        <v>0.001230929947999</v>
+        <v>0.001233589343778</v>
       </c>
       <c r="W25" t="n">
-        <v>292.238995</v>
+        <v>291.653795</v>
       </c>
       <c r="X25" t="n">
-        <v>0.428244917760306</v>
+        <v>0.428310730457717</v>
       </c>
       <c r="Y25" t="n">
-        <v>444.54</v>
+        <v>446.94</v>
       </c>
       <c r="Z25" t="n">
-        <v>0.651425713194662</v>
+        <v>0.656357644414578</v>
       </c>
       <c r="AA25" t="inlineStr"/>
       <c r="AB25" t="inlineStr"/>
       <c r="AC25" t="inlineStr"/>
       <c r="AD25" t="inlineStr"/>
       <c r="AE25" t="n">
-        <v>46.76790554438106</v>
+        <v>46.87161166669384</v>
       </c>
     </row>
     <row r="26">
@@ -2911,46 +2917,46 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>09月</t>
+          <t>08月</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2025/09</t>
+          <t>2025/08</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>31913.927995</v>
+        <v>31914.927995</v>
       </c>
       <c r="E26" t="n">
         <v>2602</v>
       </c>
       <c r="F26" t="n">
-        <v>3.804023640454263</v>
+        <v>3.812952053206708</v>
       </c>
       <c r="G26" t="n">
-        <v>26497.981</v>
+        <v>26498.981</v>
       </c>
       <c r="H26" t="n">
-        <v>38.73902619074092</v>
+        <v>38.8314158385225</v>
       </c>
       <c r="I26" t="n">
         <v>10600</v>
       </c>
       <c r="J26" t="n">
-        <v>15.49679115634711</v>
+        <v>15.53316362951234</v>
       </c>
       <c r="K26" t="n">
-        <v>1592.95</v>
+        <v>1593.95</v>
       </c>
       <c r="L26" t="n">
-        <v>2.328831459670107</v>
+        <v>2.335762845968037</v>
       </c>
       <c r="M26" t="n">
         <v>14305.031</v>
       </c>
       <c r="N26" t="n">
-        <v>20.91340357472371</v>
+        <v>20.96248936304213</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -2962,38 +2968,38 @@
         <v>2813.946995</v>
       </c>
       <c r="R26" t="n">
-        <v>4.113881972315617</v>
+        <v>4.123537652651843</v>
       </c>
       <c r="S26" t="n">
         <v>2076.328</v>
       </c>
       <c r="T26" t="n">
-        <v>3.035511451705273</v>
+        <v>3.042636091748878</v>
       </c>
       <c r="U26" t="n">
         <v>0.84</v>
       </c>
       <c r="V26" t="n">
-        <v>0.001228047601069</v>
+        <v>0.001230929947999</v>
       </c>
       <c r="W26" t="n">
         <v>292.238995</v>
       </c>
       <c r="X26" t="n">
-        <v>0.427242138986393</v>
+        <v>0.428244917760306</v>
       </c>
       <c r="Y26" t="n">
         <v>444.54</v>
       </c>
       <c r="Z26" t="n">
-        <v>0.6499003340228821</v>
+        <v>0.651425713194662</v>
       </c>
       <c r="AA26" t="inlineStr"/>
       <c r="AB26" t="inlineStr"/>
       <c r="AC26" t="inlineStr"/>
       <c r="AD26" t="inlineStr"/>
       <c r="AE26" t="n">
-        <v>46.65693180351081</v>
+        <v>46.76790554438106</v>
       </c>
     </row>
     <row r="27">
@@ -3004,46 +3010,46 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>10月</t>
+          <t>09月</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2025/10</t>
+          <t>2025/09</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>31911.527995</v>
+        <v>31913.927995</v>
       </c>
       <c r="E27" t="n">
         <v>2602</v>
       </c>
       <c r="F27" t="n">
-        <v>3.794054502310996</v>
+        <v>3.804023640454263</v>
       </c>
       <c r="G27" t="n">
         <v>26497.981</v>
       </c>
       <c r="H27" t="n">
-        <v>38.63750350315189</v>
+        <v>38.73902619074092</v>
       </c>
       <c r="I27" t="n">
         <v>10600</v>
       </c>
       <c r="J27" t="n">
-        <v>15.45617898712396</v>
+        <v>15.49679115634711</v>
       </c>
       <c r="K27" t="n">
         <v>1592.95</v>
       </c>
       <c r="L27" t="n">
-        <v>2.322728331843313</v>
+        <v>2.328831459670107</v>
       </c>
       <c r="M27" t="n">
         <v>14305.031</v>
       </c>
       <c r="N27" t="n">
-        <v>20.85859618418461</v>
+        <v>20.91340357472371</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3052,41 +3058,41 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>2811.546995</v>
+        <v>2813.946995</v>
       </c>
       <c r="R27" t="n">
-        <v>4.09960128164439</v>
+        <v>4.113881972315617</v>
       </c>
       <c r="S27" t="n">
         <v>2076.328</v>
       </c>
       <c r="T27" t="n">
-        <v>3.027556339997842</v>
+        <v>3.035511451705273</v>
       </c>
       <c r="U27" t="n">
         <v>0.84</v>
       </c>
       <c r="V27" t="n">
-        <v>0.001224829278225</v>
+        <v>0.001228047601069</v>
       </c>
       <c r="W27" t="n">
         <v>292.238995</v>
       </c>
       <c r="X27" t="n">
-        <v>0.426122472994078</v>
+        <v>0.427242138986393</v>
       </c>
       <c r="Y27" t="n">
-        <v>442.14</v>
+        <v>444.54</v>
       </c>
       <c r="Z27" t="n">
-        <v>0.644697639374244</v>
+        <v>0.6499003340228821</v>
       </c>
       <c r="AA27" t="inlineStr"/>
       <c r="AB27" t="inlineStr"/>
       <c r="AC27" t="inlineStr"/>
       <c r="AD27" t="inlineStr"/>
       <c r="AE27" t="n">
-        <v>46.53115928710728</v>
+        <v>46.65693180351081</v>
       </c>
     </row>
     <row r="28">
@@ -3097,12 +3103,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>11月</t>
+          <t>10月</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2025/11</t>
+          <t>2025/10</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -3112,31 +3118,31 @@
         <v>2602</v>
       </c>
       <c r="F28" t="n">
-        <v>3.787301722280359</v>
+        <v>3.794054502310996</v>
       </c>
       <c r="G28" t="n">
         <v>26497.981</v>
       </c>
       <c r="H28" t="n">
-        <v>38.56873523376334</v>
+        <v>38.63750350315189</v>
       </c>
       <c r="I28" t="n">
         <v>10600</v>
       </c>
       <c r="J28" t="n">
-        <v>15.42866958346342</v>
+        <v>15.45617898712396</v>
       </c>
       <c r="K28" t="n">
         <v>1592.95</v>
       </c>
       <c r="L28" t="n">
-        <v>2.318594265375287</v>
+        <v>2.322728331843313</v>
       </c>
       <c r="M28" t="n">
         <v>14305.031</v>
       </c>
       <c r="N28" t="n">
-        <v>20.82147138492464</v>
+        <v>20.85859618418461</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3148,38 +3154,38 @@
         <v>2811.546995</v>
       </c>
       <c r="R28" t="n">
-        <v>4.09230467964476</v>
+        <v>4.09960128164439</v>
       </c>
       <c r="S28" t="n">
         <v>2076.328</v>
       </c>
       <c r="T28" t="n">
-        <v>3.022167798008813</v>
+        <v>3.027556339997842</v>
       </c>
       <c r="U28" t="n">
         <v>0.84</v>
       </c>
       <c r="V28" t="n">
-        <v>0.001222649287746</v>
+        <v>0.001224829278225</v>
       </c>
       <c r="W28" t="n">
         <v>292.238995</v>
       </c>
       <c r="X28" t="n">
-        <v>0.425364046533813</v>
+        <v>0.426122472994078</v>
       </c>
       <c r="Y28" t="n">
         <v>442.14</v>
       </c>
       <c r="Z28" t="n">
-        <v>0.6435501858143881</v>
+        <v>0.644697639374244</v>
       </c>
       <c r="AA28" t="inlineStr"/>
       <c r="AB28" t="inlineStr"/>
       <c r="AC28" t="inlineStr"/>
       <c r="AD28" t="inlineStr"/>
       <c r="AE28" t="n">
-        <v>46.44834163568846</v>
+        <v>46.53115928710728</v>
       </c>
     </row>
     <row r="29">
@@ -3190,46 +3196,46 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>12月</t>
+          <t>11月</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2025/12</t>
+          <t>2025/11</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>32661.527995</v>
+        <v>31911.527995</v>
       </c>
       <c r="E29" t="n">
         <v>2602</v>
       </c>
       <c r="F29" t="n">
-        <v>3.724672853936972</v>
+        <v>3.787301722280359</v>
       </c>
       <c r="G29" t="n">
-        <v>27247.981</v>
+        <v>26497.981</v>
       </c>
       <c r="H29" t="n">
-        <v>39.00454079757509</v>
+        <v>38.56873523376334</v>
       </c>
       <c r="I29" t="n">
-        <v>10050</v>
+        <v>10600</v>
       </c>
       <c r="J29" t="n">
-        <v>14.38622681862666</v>
+        <v>15.42866958346342</v>
       </c>
       <c r="K29" t="n">
         <v>1592.95</v>
       </c>
       <c r="L29" t="n">
-        <v>2.280252737386203</v>
+        <v>2.318594265375287</v>
       </c>
       <c r="M29" t="n">
-        <v>15605.031</v>
+        <v>14305.031</v>
       </c>
       <c r="N29" t="n">
-        <v>22.33806124156223</v>
+        <v>20.82147138492464</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3241,38 +3247,38 @@
         <v>2811.546995</v>
       </c>
       <c r="R29" t="n">
-        <v>4.024632117542109</v>
+        <v>4.09230467964476</v>
       </c>
       <c r="S29" t="n">
         <v>2076.328</v>
       </c>
       <c r="T29" t="n">
-        <v>2.972191597797557</v>
+        <v>3.022167798008813</v>
       </c>
       <c r="U29" t="n">
         <v>0.84</v>
       </c>
       <c r="V29" t="n">
-        <v>0.001202430898273</v>
+        <v>0.001222649287746</v>
       </c>
       <c r="W29" t="n">
         <v>292.238995</v>
       </c>
       <c r="X29" t="n">
-        <v>0.41832999674801</v>
+        <v>0.425364046533813</v>
       </c>
       <c r="Y29" t="n">
         <v>442.14</v>
       </c>
       <c r="Z29" t="n">
-        <v>0.632908092098268</v>
+        <v>0.6435501858143881</v>
       </c>
       <c r="AA29" t="inlineStr"/>
       <c r="AB29" t="inlineStr"/>
       <c r="AC29" t="inlineStr"/>
       <c r="AD29" t="inlineStr"/>
       <c r="AE29" t="n">
-        <v>46.75384576905417</v>
+        <v>46.44834163568846</v>
       </c>
     </row>
     <row r="30">
@@ -3283,46 +3289,46 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>01月</t>
+          <t>12月</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026/01</t>
+          <t>2025/12</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>32977.669995</v>
+        <v>32661.527995</v>
       </c>
       <c r="E30" t="n">
         <v>2602</v>
       </c>
       <c r="F30" t="n">
-        <v>3.701131377042136</v>
+        <v>3.724672853936972</v>
       </c>
       <c r="G30" t="n">
-        <v>27564.123</v>
+        <v>27247.981</v>
       </c>
       <c r="H30" t="n">
-        <v>39.2077019661602</v>
+        <v>39.00454079757509</v>
       </c>
       <c r="I30" t="n">
         <v>10050</v>
       </c>
       <c r="J30" t="n">
-        <v>14.29529989979764</v>
+        <v>14.38622681862666</v>
       </c>
       <c r="K30" t="n">
-        <v>1595.95</v>
+        <v>1592.95</v>
       </c>
       <c r="L30" t="n">
-        <v>2.270107848266871</v>
+        <v>2.280252737386203</v>
       </c>
       <c r="M30" t="n">
-        <v>15918.173</v>
+        <v>15605.031</v>
       </c>
       <c r="N30" t="n">
-        <v>22.64229421809568</v>
+        <v>22.33806124156223</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -3334,38 +3340,38 @@
         <v>2811.546995</v>
       </c>
       <c r="R30" t="n">
-        <v>3.999194773721381</v>
+        <v>4.024632117542109</v>
       </c>
       <c r="S30" t="n">
         <v>2076.328</v>
       </c>
       <c r="T30" t="n">
-        <v>2.953406114462392</v>
+        <v>2.972191597797557</v>
       </c>
       <c r="U30" t="n">
         <v>0.84</v>
       </c>
       <c r="V30" t="n">
-        <v>0.001194831036401</v>
+        <v>0.001202430898273</v>
       </c>
       <c r="W30" t="n">
         <v>292.238995</v>
       </c>
       <c r="X30" t="n">
-        <v>0.415685977705519</v>
+        <v>0.41832999674801</v>
       </c>
       <c r="Y30" t="n">
         <v>442.14</v>
       </c>
       <c r="Z30" t="n">
-        <v>0.628907850517068</v>
+        <v>0.632908092098268</v>
       </c>
       <c r="AA30" t="inlineStr"/>
       <c r="AB30" t="inlineStr"/>
       <c r="AC30" t="inlineStr"/>
       <c r="AD30" t="inlineStr"/>
       <c r="AE30" t="n">
-        <v>46.90802811692372</v>
+        <v>46.75384576905417</v>
       </c>
     </row>
     <row r="31">
@@ -3376,46 +3382,46 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>02月</t>
+          <t>01月</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026/02</t>
+          <t>2026/01</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>32993.752995</v>
+        <v>32977.669995</v>
       </c>
       <c r="E31" t="n">
         <v>2602</v>
       </c>
       <c r="F31" t="n">
-        <v>3.693554303106413</v>
+        <v>3.701131377042136</v>
       </c>
       <c r="G31" t="n">
         <v>27564.123</v>
       </c>
       <c r="H31" t="n">
-        <v>39.12743471099326</v>
+        <v>39.2077019661602</v>
       </c>
       <c r="I31" t="n">
         <v>10050</v>
       </c>
       <c r="J31" t="n">
-        <v>14.26603410692523</v>
+        <v>14.29529989979764</v>
       </c>
       <c r="K31" t="n">
         <v>1595.95</v>
       </c>
       <c r="L31" t="n">
-        <v>2.26546041123854</v>
+        <v>2.270107848266871</v>
       </c>
       <c r="M31" t="n">
         <v>15918.173</v>
       </c>
       <c r="N31" t="n">
-        <v>22.59594019282949</v>
+        <v>22.64229421809568</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -3424,41 +3430,41 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>2827.629995</v>
+        <v>2811.546995</v>
       </c>
       <c r="R31" t="n">
-        <v>4.013837408003464</v>
+        <v>3.999194773721381</v>
       </c>
       <c r="S31" t="n">
         <v>2076.328</v>
       </c>
       <c r="T31" t="n">
-        <v>2.94735980747899</v>
+        <v>2.953406114462392</v>
       </c>
       <c r="U31" t="n">
         <v>0.84</v>
       </c>
       <c r="V31" t="n">
-        <v>0.00119238494028</v>
+        <v>0.001194831036401</v>
       </c>
       <c r="W31" t="n">
-        <v>308.321995</v>
+        <v>292.238995</v>
       </c>
       <c r="X31" t="n">
-        <v>0.437664885232361</v>
+        <v>0.415685977705519</v>
       </c>
       <c r="Y31" t="n">
         <v>442.14</v>
       </c>
       <c r="Z31" t="n">
-        <v>0.627620330351833</v>
+        <v>0.628907850517068</v>
       </c>
       <c r="AA31" t="inlineStr"/>
       <c r="AB31" t="inlineStr"/>
       <c r="AC31" t="inlineStr"/>
       <c r="AD31" t="inlineStr"/>
       <c r="AE31" t="n">
-        <v>46.83482642210313</v>
+        <v>46.90802811692372</v>
       </c>
     </row>
     <row r="32">
@@ -3469,12 +3475,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>03月</t>
+          <t>02月</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026/03</t>
+          <t>2026/02</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -3484,31 +3490,31 @@
         <v>2602</v>
       </c>
       <c r="F32" t="n">
-        <v>3.676246830763415</v>
+        <v>3.693554303106413</v>
       </c>
       <c r="G32" t="n">
         <v>27564.123</v>
       </c>
       <c r="H32" t="n">
-        <v>38.94408909359069</v>
+        <v>39.12743471099326</v>
       </c>
       <c r="I32" t="n">
         <v>10050</v>
       </c>
       <c r="J32" t="n">
-        <v>14.19918549161119</v>
+        <v>14.26603410692523</v>
       </c>
       <c r="K32" t="n">
         <v>1595.95</v>
       </c>
       <c r="L32" t="n">
-        <v>2.254844784610635</v>
+        <v>2.26546041123854</v>
       </c>
       <c r="M32" t="n">
         <v>15918.173</v>
       </c>
       <c r="N32" t="n">
-        <v>22.49005881736885</v>
+        <v>22.59594019282949</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -3520,38 +3526,38 @@
         <v>2827.629995</v>
       </c>
       <c r="R32" t="n">
-        <v>3.995029134392898</v>
+        <v>4.013837408003464</v>
       </c>
       <c r="S32" t="n">
         <v>2076.328</v>
       </c>
       <c r="T32" t="n">
-        <v>2.933548896858317</v>
+        <v>2.94735980747899</v>
       </c>
       <c r="U32" t="n">
         <v>0.84</v>
       </c>
       <c r="V32" t="n">
-        <v>0.001186797593329</v>
+        <v>0.00119238494028</v>
       </c>
       <c r="W32" t="n">
         <v>308.321995</v>
       </c>
       <c r="X32" t="n">
-        <v>0.435614049567027</v>
+        <v>0.437664885232361</v>
       </c>
       <c r="Y32" t="n">
         <v>442.14</v>
       </c>
       <c r="Z32" t="n">
-        <v>0.624679390374226</v>
+        <v>0.627620330351833</v>
       </c>
       <c r="AA32" t="inlineStr"/>
       <c r="AB32" t="inlineStr"/>
       <c r="AC32" t="inlineStr"/>
       <c r="AD32" t="inlineStr"/>
       <c r="AE32" t="n">
-        <v>46.615365058747</v>
+        <v>46.83482642210313</v>
       </c>
     </row>
     <row r="33">
@@ -3562,12 +3568,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>04月</t>
+          <t>03月</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026/04</t>
+          <t>2026/03</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -3577,31 +3583,31 @@
         <v>2602</v>
       </c>
       <c r="F33" t="n">
-        <v>3.66460910172093</v>
+        <v>3.676246830763415</v>
       </c>
       <c r="G33" t="n">
         <v>27564.123</v>
       </c>
       <c r="H33" t="n">
-        <v>38.82080554448702</v>
+        <v>38.94408909359069</v>
       </c>
       <c r="I33" t="n">
         <v>10050</v>
       </c>
       <c r="J33" t="n">
-        <v>14.15423576952166</v>
+        <v>14.19918549161119</v>
       </c>
       <c r="K33" t="n">
         <v>1595.95</v>
       </c>
       <c r="L33" t="n">
-        <v>2.247706724016725</v>
+        <v>2.254844784610635</v>
       </c>
       <c r="M33" t="n">
         <v>15918.173</v>
       </c>
       <c r="N33" t="n">
-        <v>22.41886305094864</v>
+        <v>22.49005881736885</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -3613,200 +3619,224 @@
         <v>2827.629995</v>
       </c>
       <c r="R33" t="n">
-        <v>3.982382250567297</v>
+        <v>3.995029134392898</v>
       </c>
       <c r="S33" t="n">
         <v>2076.328</v>
       </c>
       <c r="T33" t="n">
-        <v>2.924262293219837</v>
+        <v>2.933548896858317</v>
       </c>
       <c r="U33" t="n">
         <v>0.84</v>
       </c>
       <c r="V33" t="n">
-        <v>0.001183040601632</v>
+        <v>0.001186797593329</v>
       </c>
       <c r="W33" t="n">
         <v>308.321995</v>
       </c>
       <c r="X33" t="n">
-        <v>0.434235045786993</v>
+        <v>0.435614049567027</v>
       </c>
       <c r="Y33" t="n">
         <v>442.14</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.622701870958836</v>
+        <v>0.624679390374226</v>
       </c>
       <c r="AA33" t="inlineStr"/>
       <c r="AB33" t="inlineStr"/>
       <c r="AC33" t="inlineStr"/>
       <c r="AD33" t="inlineStr"/>
       <c r="AE33" t="n">
-        <v>46.46779689677525</v>
+        <v>46.615365058747</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>民營電廠</t>
+          <t>台電</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>01月</t>
+          <t>04月</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2025/01</t>
+          <t>2026/04</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>15498.083886</v>
-      </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
+        <v>32993.752995</v>
+      </c>
+      <c r="E34" t="n">
+        <v>2602</v>
+      </c>
+      <c r="F34" t="n">
+        <v>3.66460910172093</v>
+      </c>
       <c r="G34" t="n">
-        <v>8763.280000000001</v>
+        <v>27564.123</v>
       </c>
       <c r="H34" t="n">
-        <v>13.10249389919497</v>
+        <v>38.82080554448702</v>
       </c>
       <c r="I34" t="n">
-        <v>3120.3</v>
+        <v>10050</v>
       </c>
       <c r="J34" t="n">
-        <v>4.665343537312293</v>
-      </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
+        <v>14.15423576952166</v>
+      </c>
+      <c r="K34" t="n">
+        <v>1595.95</v>
+      </c>
+      <c r="L34" t="n">
+        <v>2.247706724016725</v>
+      </c>
       <c r="M34" t="n">
-        <v>5642.98</v>
+        <v>15918.173</v>
       </c>
       <c r="N34" t="n">
-        <v>8.437150361882679</v>
-      </c>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
+        <v>22.41886305094864</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
       <c r="Q34" t="n">
-        <v>6734.803886</v>
+        <v>2827.629995</v>
       </c>
       <c r="R34" t="n">
-        <v>10.06960028991309</v>
+        <v>3.982382250567297</v>
       </c>
       <c r="S34" t="n">
-        <v>42.335</v>
+        <v>2076.328</v>
       </c>
       <c r="T34" t="n">
-        <v>0.06329754147105</v>
+        <v>2.924262293219837</v>
       </c>
       <c r="U34" t="n">
-        <v>4.2</v>
+        <v>0.84</v>
       </c>
       <c r="V34" t="n">
-        <v>0.006279666332312</v>
+        <v>0.001183040601632</v>
       </c>
       <c r="W34" t="n">
-        <v>3179.475886</v>
+        <v>308.321995</v>
       </c>
       <c r="X34" t="n">
-        <v>4.753820875169175</v>
+        <v>0.434235045786993</v>
       </c>
       <c r="Y34" t="n">
-        <v>3508.793</v>
+        <v>442.14</v>
       </c>
       <c r="Z34" t="n">
-        <v>5.246202206940555</v>
+        <v>0.622701870958836</v>
       </c>
       <c r="AA34" t="inlineStr"/>
       <c r="AB34" t="inlineStr"/>
       <c r="AC34" t="inlineStr"/>
       <c r="AD34" t="inlineStr"/>
       <c r="AE34" t="n">
-        <v>23.17209418910807</v>
+        <v>46.46779689677525</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>民營電廠</t>
+          <t>台電</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>02月</t>
+          <t>05月</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2025/02</t>
+          <t>2026/05</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>15543.445261</v>
-      </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
+        <v>32993.752995</v>
+      </c>
+      <c r="E35" t="n">
+        <v>2602</v>
+      </c>
+      <c r="F35" t="n">
+        <v>3.648141822914185</v>
+      </c>
       <c r="G35" t="n">
-        <v>8763.280000000001</v>
+        <v>27564.123</v>
       </c>
       <c r="H35" t="n">
-        <v>13.09265708703653</v>
+        <v>38.64636046435466</v>
       </c>
       <c r="I35" t="n">
-        <v>3120.3</v>
+        <v>10050</v>
       </c>
       <c r="J35" t="n">
-        <v>4.661840989752706</v>
-      </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
+        <v>14.09063232908822</v>
+      </c>
+      <c r="K35" t="n">
+        <v>1595.95</v>
+      </c>
+      <c r="L35" t="n">
+        <v>2.23760643438889</v>
+      </c>
       <c r="M35" t="n">
-        <v>5642.98</v>
+        <v>15918.173</v>
       </c>
       <c r="N35" t="n">
-        <v>8.430816097283827</v>
-      </c>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr"/>
+        <v>22.31812170087754</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
       <c r="Q35" t="n">
-        <v>6780.165261</v>
+        <v>2827.629995</v>
       </c>
       <c r="R35" t="n">
-        <v>10.12981198315135</v>
+        <v>3.964487027089211</v>
       </c>
       <c r="S35" t="n">
-        <v>42.335</v>
+        <v>2076.328</v>
       </c>
       <c r="T35" t="n">
-        <v>0.063250020286889</v>
+        <v>2.911121835083691</v>
       </c>
       <c r="U35" t="n">
-        <v>4.2</v>
+        <v>0.84</v>
       </c>
       <c r="V35" t="n">
-        <v>0.006274951817762</v>
+        <v>0.001177724493178</v>
       </c>
       <c r="W35" t="n">
-        <v>3208.837261</v>
+        <v>308.321995</v>
       </c>
       <c r="X35" t="n">
-        <v>4.794118858050701</v>
+        <v>0.432283768210545</v>
       </c>
       <c r="Y35" t="n">
-        <v>3524.793</v>
+        <v>442.14</v>
       </c>
       <c r="Z35" t="n">
-        <v>5.266168152995998</v>
+        <v>0.619903699301798</v>
       </c>
       <c r="AA35" t="inlineStr"/>
       <c r="AB35" t="inlineStr"/>
       <c r="AC35" t="inlineStr"/>
       <c r="AD35" t="inlineStr"/>
       <c r="AE35" t="n">
-        <v>23.22246907018788</v>
+        <v>46.25898931435805</v>
       </c>
     </row>
     <row r="36">
@@ -3817,16 +3847,16 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>03月</t>
+          <t>01月</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2025/03</t>
+          <t>2025/01</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>15548.263016</v>
+        <v>15498.083886</v>
       </c>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr"/>
@@ -3834,13 +3864,13 @@
         <v>8763.280000000001</v>
       </c>
       <c r="H36" t="n">
-        <v>13.07075119004763</v>
+        <v>13.10249389919497</v>
       </c>
       <c r="I36" t="n">
         <v>3120.3</v>
       </c>
       <c r="J36" t="n">
-        <v>4.654041059775064</v>
+        <v>4.665343537312293</v>
       </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
@@ -3848,46 +3878,46 @@
         <v>5642.98</v>
       </c>
       <c r="N36" t="n">
-        <v>8.41671013027257</v>
+        <v>8.437150361882679</v>
       </c>
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr"/>
       <c r="Q36" t="n">
-        <v>6784.983016</v>
+        <v>6734.803886</v>
       </c>
       <c r="R36" t="n">
-        <v>10.12004920883904</v>
+        <v>10.06960028991309</v>
       </c>
       <c r="S36" t="n">
         <v>42.335</v>
       </c>
       <c r="T36" t="n">
-        <v>0.063144193912629</v>
+        <v>0.06329754147105</v>
       </c>
       <c r="U36" t="n">
         <v>4.2</v>
       </c>
       <c r="V36" t="n">
-        <v>0.006264452921532</v>
+        <v>0.006279666332312</v>
       </c>
       <c r="W36" t="n">
-        <v>3213.655016</v>
+        <v>3179.475886</v>
       </c>
       <c r="X36" t="n">
-        <v>4.793283465184788</v>
+        <v>4.753820875169175</v>
       </c>
       <c r="Y36" t="n">
-        <v>3524.793</v>
+        <v>3508.793</v>
       </c>
       <c r="Z36" t="n">
-        <v>5.257357096820091</v>
+        <v>5.246202206940555</v>
       </c>
       <c r="AA36" t="inlineStr"/>
       <c r="AB36" t="inlineStr"/>
       <c r="AC36" t="inlineStr"/>
       <c r="AD36" t="inlineStr"/>
       <c r="AE36" t="n">
-        <v>23.19080039888668</v>
+        <v>23.17209418910807</v>
       </c>
     </row>
     <row r="37">
@@ -3898,16 +3928,16 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>04月</t>
+          <t>02月</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2025/04</t>
+          <t>2025/02</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>15561.527171</v>
+        <v>15543.445261</v>
       </c>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
@@ -3915,13 +3945,13 @@
         <v>8763.280000000001</v>
       </c>
       <c r="H37" t="n">
-        <v>13.20079536308682</v>
+        <v>13.09265708703653</v>
       </c>
       <c r="I37" t="n">
         <v>3120.3</v>
       </c>
       <c r="J37" t="n">
-        <v>4.700345278416278</v>
+        <v>4.661840989752706</v>
       </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
@@ -3929,46 +3959,46 @@
         <v>5642.98</v>
       </c>
       <c r="N37" t="n">
-        <v>8.500450084670542</v>
+        <v>8.430816097283827</v>
       </c>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr"/>
       <c r="Q37" t="n">
-        <v>6798.247171</v>
+        <v>6780.165261</v>
       </c>
       <c r="R37" t="n">
-        <v>10.24071691559038</v>
+        <v>10.12981198315135</v>
       </c>
       <c r="S37" t="n">
         <v>42.335</v>
       </c>
       <c r="T37" t="n">
-        <v>0.06377243129242501</v>
+        <v>0.063250020286889</v>
       </c>
       <c r="U37" t="n">
         <v>4.2</v>
       </c>
       <c r="V37" t="n">
-        <v>0.006326779530606</v>
+        <v>0.006274951817762</v>
       </c>
       <c r="W37" t="n">
-        <v>3226.919171</v>
+        <v>3208.837261</v>
       </c>
       <c r="X37" t="n">
-        <v>4.860953847143167</v>
+        <v>4.794118858050701</v>
       </c>
       <c r="Y37" t="n">
         <v>3524.793</v>
       </c>
       <c r="Z37" t="n">
-        <v>5.309663857624186</v>
+        <v>5.266168152995998</v>
       </c>
       <c r="AA37" t="inlineStr"/>
       <c r="AB37" t="inlineStr"/>
       <c r="AC37" t="inlineStr"/>
       <c r="AD37" t="inlineStr"/>
       <c r="AE37" t="n">
-        <v>23.44151227867721</v>
+        <v>23.22246907018788</v>
       </c>
     </row>
     <row r="38">
@@ -3979,77 +4009,77 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>05月</t>
+          <t>03月</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2025/05</t>
+          <t>2025/03</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>16668.881171</v>
+        <v>15548.263016</v>
       </c>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="n">
-        <v>9868.977999999999</v>
+        <v>8763.280000000001</v>
       </c>
       <c r="H38" t="n">
-        <v>14.59437948410531</v>
+        <v>13.07075119004763</v>
       </c>
       <c r="I38" t="n">
         <v>3120.3</v>
       </c>
       <c r="J38" t="n">
-        <v>4.61434226565849</v>
+        <v>4.654041059775064</v>
       </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="n">
-        <v>6748.678</v>
+        <v>5642.98</v>
       </c>
       <c r="N38" t="n">
-        <v>9.980037218446821</v>
+        <v>8.41671013027257</v>
       </c>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr"/>
       <c r="Q38" t="n">
-        <v>6799.903171</v>
+        <v>6784.983016</v>
       </c>
       <c r="R38" t="n">
-        <v>10.05578970109621</v>
+        <v>10.12004920883904</v>
       </c>
       <c r="S38" t="n">
-        <v>43.991</v>
+        <v>42.335</v>
       </c>
       <c r="T38" t="n">
-        <v>0.06505449175033901</v>
+        <v>0.063144193912629</v>
       </c>
       <c r="U38" t="n">
         <v>4.2</v>
       </c>
       <c r="V38" t="n">
-        <v>0.006211017375177</v>
+        <v>0.006264452921532</v>
       </c>
       <c r="W38" t="n">
-        <v>3226.919171</v>
+        <v>3213.655016</v>
       </c>
       <c r="X38" t="n">
-        <v>4.772012152231824</v>
+        <v>4.793283465184788</v>
       </c>
       <c r="Y38" t="n">
         <v>3524.793</v>
       </c>
       <c r="Z38" t="n">
-        <v>5.212512039738867</v>
+        <v>5.257357096820091</v>
       </c>
       <c r="AA38" t="inlineStr"/>
       <c r="AB38" t="inlineStr"/>
       <c r="AC38" t="inlineStr"/>
       <c r="AD38" t="inlineStr"/>
       <c r="AE38" t="n">
-        <v>24.65016918520152</v>
+        <v>23.19080039888668</v>
       </c>
     </row>
     <row r="39">
@@ -4060,77 +4090,77 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>06月</t>
+          <t>04月</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2025/06</t>
+          <t>2025/04</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>16679.366291</v>
+        <v>15561.527171</v>
       </c>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="n">
-        <v>9868.977999999999</v>
+        <v>8763.280000000001</v>
       </c>
       <c r="H39" t="n">
-        <v>14.77702180844244</v>
+        <v>13.20079536308682</v>
       </c>
       <c r="I39" t="n">
         <v>3120.3</v>
       </c>
       <c r="J39" t="n">
-        <v>4.672088756189641</v>
+        <v>4.700345278416278</v>
       </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="n">
-        <v>6748.678</v>
+        <v>5642.98</v>
       </c>
       <c r="N39" t="n">
-        <v>10.1049330522528</v>
+        <v>8.500450084670542</v>
       </c>
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr"/>
       <c r="Q39" t="n">
-        <v>6810.388291</v>
+        <v>6798.247171</v>
       </c>
       <c r="R39" t="n">
-        <v>10.19733312811803</v>
+        <v>10.24071691559038</v>
       </c>
       <c r="S39" t="n">
-        <v>43.991</v>
+        <v>42.335</v>
       </c>
       <c r="T39" t="n">
-        <v>0.06586862047672901</v>
+        <v>0.06377243129242501</v>
       </c>
       <c r="U39" t="n">
         <v>4.2</v>
       </c>
       <c r="V39" t="n">
-        <v>0.006288745561644</v>
+        <v>0.006326779530606</v>
       </c>
       <c r="W39" t="n">
-        <v>3237.404291</v>
+        <v>3226.919171</v>
       </c>
       <c r="X39" t="n">
-        <v>4.847431396731468</v>
+        <v>4.860953847143167</v>
       </c>
       <c r="Y39" t="n">
         <v>3524.793</v>
       </c>
       <c r="Z39" t="n">
-        <v>5.277744365348189</v>
+        <v>5.309663857624186</v>
       </c>
       <c r="AA39" t="inlineStr"/>
       <c r="AB39" t="inlineStr"/>
       <c r="AC39" t="inlineStr"/>
       <c r="AD39" t="inlineStr"/>
       <c r="AE39" t="n">
-        <v>24.97435493656047</v>
+        <v>23.44151227867721</v>
       </c>
     </row>
     <row r="40">
@@ -4141,16 +4171,16 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>07月</t>
+          <t>05月</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2025/07</t>
+          <t>2025/05</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>17006.324336</v>
+        <v>16668.881171</v>
       </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
@@ -4158,13 +4188,13 @@
         <v>9868.977999999999</v>
       </c>
       <c r="H40" t="n">
-        <v>14.49317392235936</v>
+        <v>14.59437948410531</v>
       </c>
       <c r="I40" t="n">
         <v>3120.3</v>
       </c>
       <c r="J40" t="n">
-        <v>4.582343844513372</v>
+        <v>4.61434226565849</v>
       </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
@@ -4172,46 +4202,46 @@
         <v>6748.678</v>
       </c>
       <c r="N40" t="n">
-        <v>9.910830077845983</v>
+        <v>9.980037218446821</v>
       </c>
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr"/>
       <c r="Q40" t="n">
-        <v>7137.346336</v>
+        <v>6799.903171</v>
       </c>
       <c r="R40" t="n">
-        <v>10.48161236064791</v>
+        <v>10.05578970109621</v>
       </c>
       <c r="S40" t="n">
         <v>43.991</v>
       </c>
       <c r="T40" t="n">
-        <v>0.06460336764541499</v>
+        <v>0.06505449175033901</v>
       </c>
       <c r="U40" t="n">
         <v>4.2</v>
       </c>
       <c r="V40" t="n">
-        <v>0.006167946718891</v>
+        <v>0.006211017375177</v>
       </c>
       <c r="W40" t="n">
-        <v>3480.317336</v>
+        <v>3226.919171</v>
       </c>
       <c r="X40" t="n">
-        <v>5.111050450781263</v>
+        <v>4.772012152231824</v>
       </c>
       <c r="Y40" t="n">
-        <v>3608.838</v>
+        <v>3524.793</v>
       </c>
       <c r="Z40" t="n">
-        <v>5.29979059550234</v>
+        <v>5.212512039738867</v>
       </c>
       <c r="AA40" t="inlineStr"/>
       <c r="AB40" t="inlineStr"/>
       <c r="AC40" t="inlineStr"/>
       <c r="AD40" t="inlineStr"/>
       <c r="AE40" t="n">
-        <v>24.97478628300726</v>
+        <v>24.65016918520152</v>
       </c>
     </row>
     <row r="41">
@@ -4222,16 +4252,16 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>08月</t>
+          <t>06月</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2025/08</t>
+          <t>2025/06</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>17079.284596</v>
+        <v>16679.366291</v>
       </c>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
@@ -4239,13 +4269,13 @@
         <v>9868.977999999999</v>
       </c>
       <c r="H41" t="n">
-        <v>14.46192925755259</v>
+        <v>14.77702180844244</v>
       </c>
       <c r="I41" t="n">
         <v>3120.3</v>
       </c>
       <c r="J41" t="n">
-        <v>4.572465138978053</v>
+        <v>4.672088756189641</v>
       </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
@@ -4253,46 +4283,46 @@
         <v>6748.678</v>
       </c>
       <c r="N41" t="n">
-        <v>9.889464118574539</v>
+        <v>10.1049330522528</v>
       </c>
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr"/>
       <c r="Q41" t="n">
-        <v>7210.306596</v>
+        <v>6810.388291</v>
       </c>
       <c r="R41" t="n">
-        <v>10.56593133722832</v>
+        <v>10.19733312811803</v>
       </c>
       <c r="S41" t="n">
         <v>43.991</v>
       </c>
       <c r="T41" t="n">
-        <v>0.064464094455271</v>
+        <v>0.06586862047672901</v>
       </c>
       <c r="U41" t="n">
         <v>4.2</v>
       </c>
       <c r="V41" t="n">
-        <v>0.006154649739995</v>
+        <v>0.006288745561644</v>
       </c>
       <c r="W41" t="n">
-        <v>3483.277596</v>
+        <v>3237.404291</v>
       </c>
       <c r="X41" t="n">
-        <v>5.104369892988904</v>
+        <v>4.847431396731468</v>
       </c>
       <c r="Y41" t="n">
-        <v>3678.838</v>
+        <v>3524.793</v>
       </c>
       <c r="Z41" t="n">
-        <v>5.390942700044143</v>
+        <v>5.277744365348189</v>
       </c>
       <c r="AA41" t="inlineStr"/>
       <c r="AB41" t="inlineStr"/>
       <c r="AC41" t="inlineStr"/>
       <c r="AD41" t="inlineStr"/>
       <c r="AE41" t="n">
-        <v>25.0278605947809</v>
+        <v>24.97435493656047</v>
       </c>
     </row>
     <row r="42">
@@ -4303,16 +4333,16 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>09月</t>
+          <t>07月</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2025/09</t>
+          <t>2025/07</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>17177.101056</v>
+        <v>17006.324336</v>
       </c>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr"/>
@@ -4320,13 +4350,13 @@
         <v>9868.977999999999</v>
       </c>
       <c r="H42" t="n">
-        <v>14.42806518797965</v>
+        <v>14.49317392235936</v>
       </c>
       <c r="I42" t="n">
         <v>3120.3</v>
       </c>
       <c r="J42" t="n">
-        <v>4.561758249542443</v>
+        <v>4.582343844513372</v>
       </c>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
@@ -4334,46 +4364,46 @@
         <v>6748.678</v>
       </c>
       <c r="N42" t="n">
-        <v>9.866306938437203</v>
+        <v>9.910830077845983</v>
       </c>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr"/>
       <c r="Q42" t="n">
-        <v>7308.123056</v>
+        <v>7137.346336</v>
       </c>
       <c r="R42" t="n">
-        <v>10.68419403242616</v>
+        <v>10.48161236064791</v>
       </c>
       <c r="S42" t="n">
         <v>43.991</v>
       </c>
       <c r="T42" t="n">
-        <v>0.06431314526027</v>
+        <v>0.06460336764541499</v>
       </c>
       <c r="U42" t="n">
         <v>4.2</v>
       </c>
       <c r="V42" t="n">
-        <v>0.006140238005345</v>
+        <v>0.006167946718891</v>
       </c>
       <c r="W42" t="n">
-        <v>3497.582056</v>
+        <v>3480.317336</v>
       </c>
       <c r="X42" t="n">
-        <v>5.113330063586713</v>
+        <v>5.111050450781263</v>
       </c>
       <c r="Y42" t="n">
-        <v>3762.35</v>
+        <v>3608.838</v>
       </c>
       <c r="Z42" t="n">
-        <v>5.500410585573827</v>
+        <v>5.29979059550234</v>
       </c>
       <c r="AA42" t="inlineStr"/>
       <c r="AB42" t="inlineStr"/>
       <c r="AC42" t="inlineStr"/>
       <c r="AD42" t="inlineStr"/>
       <c r="AE42" t="n">
-        <v>25.1122592204058</v>
+        <v>24.97478628300726</v>
       </c>
     </row>
     <row r="43">
@@ -4384,16 +4414,16 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>10月</t>
+          <t>08月</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2025/10</t>
+          <t>2025/08</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>17269.224046</v>
+        <v>17079.284596</v>
       </c>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr"/>
@@ -4401,13 +4431,13 @@
         <v>9868.977999999999</v>
       </c>
       <c r="H43" t="n">
-        <v>14.39025381018761</v>
+        <v>14.46192925755259</v>
       </c>
       <c r="I43" t="n">
         <v>3120.3</v>
       </c>
       <c r="J43" t="n">
-        <v>4.549803329577632</v>
+        <v>4.572465138978053</v>
       </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
@@ -4415,46 +4445,46 @@
         <v>6748.678</v>
       </c>
       <c r="N43" t="n">
-        <v>9.840450480609981</v>
+        <v>9.889464118574539</v>
       </c>
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr"/>
       <c r="Q43" t="n">
-        <v>7400.246046</v>
+        <v>7210.306596</v>
       </c>
       <c r="R43" t="n">
-        <v>10.79052145620117</v>
+        <v>10.56593133722832</v>
       </c>
       <c r="S43" t="n">
         <v>43.991</v>
       </c>
       <c r="T43" t="n">
-        <v>0.064144600926658</v>
+        <v>0.064464094455271</v>
       </c>
       <c r="U43" t="n">
         <v>4.2</v>
       </c>
       <c r="V43" t="n">
-        <v>0.006124146391125</v>
+        <v>0.006154649739995</v>
       </c>
       <c r="W43" t="n">
-        <v>3519.705046</v>
+        <v>3483.277596</v>
       </c>
       <c r="X43" t="n">
-        <v>5.132187846496169</v>
+        <v>5.104369892988904</v>
       </c>
       <c r="Y43" t="n">
-        <v>3832.35</v>
+        <v>3678.838</v>
       </c>
       <c r="Z43" t="n">
-        <v>5.588064862387221</v>
+        <v>5.390942700044143</v>
       </c>
       <c r="AA43" t="inlineStr"/>
       <c r="AB43" t="inlineStr"/>
       <c r="AC43" t="inlineStr"/>
       <c r="AD43" t="inlineStr"/>
       <c r="AE43" t="n">
-        <v>25.18077526638878</v>
+        <v>25.0278605947809</v>
       </c>
     </row>
     <row r="44">
@@ -4465,16 +4495,16 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>11月</t>
+          <t>09月</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2025/11</t>
+          <t>2025/09</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>17354.431326</v>
+        <v>17177.101056</v>
       </c>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr"/>
@@ -4482,13 +4512,13 @@
         <v>9868.977999999999</v>
       </c>
       <c r="H44" t="n">
-        <v>14.36464157438393</v>
+        <v>14.42806518797965</v>
       </c>
       <c r="I44" t="n">
         <v>3120.3</v>
       </c>
       <c r="J44" t="n">
-        <v>4.541705443517065</v>
+        <v>4.561758249542443</v>
       </c>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
@@ -4496,46 +4526,46 @@
         <v>6748.678</v>
       </c>
       <c r="N44" t="n">
-        <v>9.822936130866861</v>
+        <v>9.866306938437203</v>
       </c>
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr"/>
       <c r="Q44" t="n">
-        <v>7485.453326</v>
+        <v>7308.123056</v>
       </c>
       <c r="R44" t="n">
-        <v>10.89533830653691</v>
+        <v>10.68419403242616</v>
       </c>
       <c r="S44" t="n">
         <v>43.991</v>
       </c>
       <c r="T44" t="n">
-        <v>0.06403043430624</v>
+        <v>0.06431314526027</v>
       </c>
       <c r="U44" t="n">
         <v>4.2</v>
       </c>
       <c r="V44" t="n">
-        <v>0.006113246438731</v>
+        <v>0.006140238005345</v>
       </c>
       <c r="W44" t="n">
-        <v>3563.156326</v>
+        <v>3497.582056</v>
       </c>
       <c r="X44" t="n">
-        <v>5.186298266800137</v>
+        <v>5.113330063586713</v>
       </c>
       <c r="Y44" t="n">
-        <v>3874.106</v>
+        <v>3762.35</v>
       </c>
       <c r="Z44" t="n">
-        <v>5.638896358991804</v>
+        <v>5.500410585573827</v>
       </c>
       <c r="AA44" t="inlineStr"/>
       <c r="AB44" t="inlineStr"/>
       <c r="AC44" t="inlineStr"/>
       <c r="AD44" t="inlineStr"/>
       <c r="AE44" t="n">
-        <v>25.25997988092083</v>
+        <v>25.1122592204058</v>
       </c>
     </row>
     <row r="45">
@@ -4546,16 +4576,16 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>12月</t>
+          <t>10月</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2025/12</t>
+          <t>2025/10</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>17620.552981</v>
+        <v>17269.224046</v>
       </c>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr"/>
@@ -4563,13 +4593,13 @@
         <v>9868.977999999999</v>
       </c>
       <c r="H45" t="n">
-        <v>14.12710009711806</v>
+        <v>14.39025381018761</v>
       </c>
       <c r="I45" t="n">
         <v>3120.3</v>
       </c>
       <c r="J45" t="n">
-        <v>4.466601347478683</v>
+        <v>4.549803329577632</v>
       </c>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
@@ -4577,46 +4607,46 @@
         <v>6748.678</v>
       </c>
       <c r="N45" t="n">
-        <v>9.660498749639377</v>
+        <v>9.840450480609981</v>
       </c>
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr"/>
       <c r="Q45" t="n">
-        <v>7751.574981</v>
+        <v>7400.246046</v>
       </c>
       <c r="R45" t="n">
-        <v>11.09611103266245</v>
+        <v>10.79052145620117</v>
       </c>
       <c r="S45" t="n">
         <v>43.991</v>
       </c>
       <c r="T45" t="n">
-        <v>0.062971592435642</v>
+        <v>0.064144600926658</v>
       </c>
       <c r="U45" t="n">
         <v>4.2</v>
       </c>
       <c r="V45" t="n">
-        <v>0.006012154491366</v>
+        <v>0.006124146391125</v>
       </c>
       <c r="W45" t="n">
-        <v>3634.497981</v>
+        <v>3519.705046</v>
       </c>
       <c r="X45" t="n">
-        <v>5.202657942935985</v>
+        <v>5.132187846496169</v>
       </c>
       <c r="Y45" t="n">
-        <v>4068.886</v>
+        <v>3832.35</v>
       </c>
       <c r="Z45" t="n">
-        <v>5.824469342799457</v>
+        <v>5.588064862387221</v>
       </c>
       <c r="AA45" t="inlineStr"/>
       <c r="AB45" t="inlineStr"/>
       <c r="AC45" t="inlineStr"/>
       <c r="AD45" t="inlineStr"/>
       <c r="AE45" t="n">
-        <v>25.22321112978051</v>
+        <v>25.18077526638878</v>
       </c>
     </row>
     <row r="46">
@@ -4627,16 +4657,16 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>01月</t>
+          <t>11月</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026/01</t>
+          <t>2025/11</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>17728.083001</v>
+        <v>17354.431326</v>
       </c>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr"/>
@@ -4644,13 +4674,13 @@
         <v>9868.977999999999</v>
       </c>
       <c r="H46" t="n">
-        <v>14.03781096661743</v>
+        <v>14.36464157438393</v>
       </c>
       <c r="I46" t="n">
         <v>3120.3</v>
       </c>
       <c r="J46" t="n">
-        <v>4.438370574859561</v>
+        <v>4.541705443517065</v>
       </c>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
@@ -4658,46 +4688,46 @@
         <v>6748.678</v>
       </c>
       <c r="N46" t="n">
-        <v>9.599440391757868</v>
+        <v>9.822936130866861</v>
       </c>
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr"/>
       <c r="Q46" t="n">
-        <v>7859.105001</v>
+        <v>7485.453326</v>
       </c>
       <c r="R46" t="n">
-        <v>11.17893163515368</v>
+        <v>10.89533830653691</v>
       </c>
       <c r="S46" t="n">
         <v>43.991</v>
       </c>
       <c r="T46" t="n">
-        <v>0.0625735858599</v>
+        <v>0.06403043430624</v>
       </c>
       <c r="U46" t="n">
         <v>4.2</v>
       </c>
       <c r="V46" t="n">
-        <v>0.005974155182005</v>
+        <v>0.006113246438731</v>
       </c>
       <c r="W46" t="n">
-        <v>3686.516001</v>
+        <v>3563.156326</v>
       </c>
       <c r="X46" t="n">
-        <v>5.243766350218678</v>
+        <v>5.186298266800137</v>
       </c>
       <c r="Y46" t="n">
-        <v>4124.398</v>
+        <v>3874.106</v>
       </c>
       <c r="Z46" t="n">
-        <v>5.866617543893096</v>
+        <v>5.638896358991804</v>
       </c>
       <c r="AA46" t="inlineStr"/>
       <c r="AB46" t="inlineStr"/>
       <c r="AC46" t="inlineStr"/>
       <c r="AD46" t="inlineStr"/>
       <c r="AE46" t="n">
-        <v>25.21674260177111</v>
+        <v>25.25997988092083</v>
       </c>
     </row>
     <row r="47">
@@ -4708,16 +4738,16 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>02月</t>
+          <t>12月</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026/02</t>
+          <t>2025/12</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>17771.432441</v>
+        <v>17620.552981</v>
       </c>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr"/>
@@ -4725,13 +4755,13 @@
         <v>9868.977999999999</v>
       </c>
       <c r="H47" t="n">
-        <v>14.00907231328306</v>
+        <v>14.12710009711806</v>
       </c>
       <c r="I47" t="n">
         <v>3120.3</v>
       </c>
       <c r="J47" t="n">
-        <v>4.429284201376995</v>
+        <v>4.466601347478683</v>
       </c>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
@@ -4739,46 +4769,46 @@
         <v>6748.678</v>
       </c>
       <c r="N47" t="n">
-        <v>9.579788111906067</v>
+        <v>9.660498749639377</v>
       </c>
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr"/>
       <c r="Q47" t="n">
-        <v>7902.454441</v>
+        <v>7751.574981</v>
       </c>
       <c r="R47" t="n">
-        <v>11.2175805555949</v>
+        <v>11.09611103266245</v>
       </c>
       <c r="S47" t="n">
         <v>43.991</v>
       </c>
       <c r="T47" t="n">
-        <v>0.062445483223657</v>
+        <v>0.062971592435642</v>
       </c>
       <c r="U47" t="n">
         <v>4.2</v>
       </c>
       <c r="V47" t="n">
-        <v>0.005961924701402</v>
+        <v>0.006012154491366</v>
       </c>
       <c r="W47" t="n">
-        <v>3688.231441</v>
+        <v>3634.497981</v>
       </c>
       <c r="X47" t="n">
-        <v>5.23546622204378</v>
+        <v>5.202657942935985</v>
       </c>
       <c r="Y47" t="n">
-        <v>4166.032</v>
+        <v>4068.886</v>
       </c>
       <c r="Z47" t="n">
-        <v>5.913706925626064</v>
+        <v>5.824469342799457</v>
       </c>
       <c r="AA47" t="inlineStr"/>
       <c r="AB47" t="inlineStr"/>
       <c r="AC47" t="inlineStr"/>
       <c r="AD47" t="inlineStr"/>
       <c r="AE47" t="n">
-        <v>25.22665286887796</v>
+        <v>25.22321112978051</v>
       </c>
     </row>
     <row r="48">
@@ -4789,16 +4819,16 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>03月</t>
+          <t>01月</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026/03</t>
+          <t>2026/01</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>18008.212441</v>
+        <v>17728.083001</v>
       </c>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr"/>
@@ -4806,13 +4836,13 @@
         <v>9868.977999999999</v>
       </c>
       <c r="H48" t="n">
-        <v>13.9434277845403</v>
+        <v>14.03781096661743</v>
       </c>
       <c r="I48" t="n">
         <v>3120.3</v>
       </c>
       <c r="J48" t="n">
-        <v>4.408529202932776</v>
+        <v>4.438370574859561</v>
       </c>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
@@ -4820,46 +4850,46 @@
         <v>6748.678</v>
       </c>
       <c r="N48" t="n">
-        <v>9.534898581607528</v>
+        <v>9.599440391757868</v>
       </c>
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr"/>
       <c r="Q48" t="n">
-        <v>8139.234441</v>
+        <v>7859.105001</v>
       </c>
       <c r="R48" t="n">
-        <v>11.49955219775814</v>
+        <v>11.17893163515368</v>
       </c>
       <c r="S48" t="n">
         <v>43.991</v>
       </c>
       <c r="T48" t="n">
-        <v>0.062152872533479</v>
+        <v>0.0625735858599</v>
       </c>
       <c r="U48" t="n">
         <v>4.2</v>
       </c>
       <c r="V48" t="n">
-        <v>0.005933987966643</v>
+        <v>0.005974155182005</v>
       </c>
       <c r="W48" t="n">
-        <v>3688.231441</v>
+        <v>3686.516001</v>
       </c>
       <c r="X48" t="n">
-        <v>5.210933568830989</v>
+        <v>5.243766350218678</v>
       </c>
       <c r="Y48" t="n">
-        <v>4402.812</v>
+        <v>4124.398</v>
       </c>
       <c r="Z48" t="n">
-        <v>6.22053176842703</v>
+        <v>5.866617543893096</v>
       </c>
       <c r="AA48" t="inlineStr"/>
       <c r="AB48" t="inlineStr"/>
       <c r="AC48" t="inlineStr"/>
       <c r="AD48" t="inlineStr"/>
       <c r="AE48" t="n">
-        <v>25.44297998229845</v>
+        <v>25.21674260177111</v>
       </c>
     </row>
     <row r="49">
@@ -4870,16 +4900,16 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>04月</t>
+          <t>02月</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026/04</t>
+          <t>2026/02</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>18176.879961</v>
+        <v>17771.432441</v>
       </c>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr"/>
@@ -4887,13 +4917,13 @@
         <v>9868.977999999999</v>
       </c>
       <c r="H49" t="n">
-        <v>13.8992877031067</v>
+        <v>14.00907231328306</v>
       </c>
       <c r="I49" t="n">
         <v>3120.3</v>
       </c>
       <c r="J49" t="n">
-        <v>4.394573320561037</v>
+        <v>4.429284201376995</v>
       </c>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
@@ -4901,325 +4931,289 @@
         <v>6748.678</v>
       </c>
       <c r="N49" t="n">
-        <v>9.504714382545659</v>
+        <v>9.579788111906067</v>
       </c>
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr"/>
       <c r="Q49" t="n">
-        <v>8307.901961</v>
+        <v>7902.454441</v>
       </c>
       <c r="R49" t="n">
-        <v>11.70069682647416</v>
+        <v>11.2175805555949</v>
       </c>
       <c r="S49" t="n">
         <v>43.991</v>
       </c>
       <c r="T49" t="n">
-        <v>0.061956117983784</v>
+        <v>0.062445483223657</v>
       </c>
       <c r="U49" t="n">
         <v>4.2</v>
       </c>
       <c r="V49" t="n">
-        <v>0.005915203008158</v>
+        <v>0.005961924701402</v>
       </c>
       <c r="W49" t="n">
-        <v>3703.508961</v>
+        <v>3688.231441</v>
       </c>
       <c r="X49" t="n">
-        <v>5.215954130202009</v>
+        <v>5.23546622204378</v>
       </c>
       <c r="Y49" t="n">
-        <v>4556.202</v>
+        <v>4166.032</v>
       </c>
       <c r="Z49" t="n">
-        <v>6.41687137528021</v>
+        <v>5.913706925626064</v>
       </c>
       <c r="AA49" t="inlineStr"/>
       <c r="AB49" t="inlineStr"/>
       <c r="AC49" t="inlineStr"/>
       <c r="AD49" t="inlineStr"/>
       <c r="AE49" t="n">
-        <v>25.59998452958085</v>
+        <v>25.22665286887796</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>自用發電設備</t>
+          <t>民營電廠</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>01月</t>
+          <t>03月</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2025/01</t>
+          <t>2026/03</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>18868.2988</v>
+        <v>18008.212441</v>
       </c>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="n">
-        <v>7211.8346</v>
+        <v>9868.977999999999</v>
       </c>
       <c r="H50" t="n">
-        <v>10.78283688852841</v>
+        <v>13.9434277845403</v>
       </c>
       <c r="I50" t="n">
-        <v>6151.384</v>
+        <v>3120.3</v>
       </c>
       <c r="J50" t="n">
-        <v>9.197295000457087</v>
-      </c>
-      <c r="K50" t="n">
-        <v>560.4126</v>
-      </c>
-      <c r="L50" t="n">
-        <v>0.837905746767419</v>
-      </c>
+        <v>4.408529202932776</v>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
       <c r="M50" t="n">
-        <v>500.038</v>
+        <v>6748.678</v>
       </c>
       <c r="N50" t="n">
-        <v>0.747636141303902</v>
+        <v>9.534898581607528</v>
       </c>
       <c r="O50" t="inlineStr"/>
       <c r="P50" t="inlineStr"/>
       <c r="Q50" t="n">
-        <v>11656.4642</v>
+        <v>8139.234441</v>
       </c>
       <c r="R50" t="n">
-        <v>17.4282632834606</v>
+        <v>11.49955219775814</v>
       </c>
       <c r="S50" t="n">
-        <v>3.9605</v>
+        <v>43.991</v>
       </c>
       <c r="T50" t="n">
-        <v>0.005921575835505</v>
+        <v>0.062152872533479</v>
       </c>
       <c r="U50" t="n">
-        <v>2.449</v>
+        <v>4.2</v>
       </c>
       <c r="V50" t="n">
-        <v>0.003661643535198</v>
+        <v>0.005933987966643</v>
       </c>
       <c r="W50" t="n">
-        <v>10893.378</v>
+        <v>3688.231441</v>
       </c>
       <c r="X50" t="n">
-        <v>16.287328350415</v>
+        <v>5.210933568830989</v>
       </c>
       <c r="Y50" t="n">
-        <v>6.2137</v>
+        <v>4402.812</v>
       </c>
       <c r="Z50" t="n">
-        <v>0.009290467306924999</v>
-      </c>
-      <c r="AA50" t="n">
-        <v>83.998</v>
-      </c>
-      <c r="AB50" t="n">
-        <v>0.125590336328929</v>
-      </c>
-      <c r="AC50" t="n">
-        <v>666.465</v>
-      </c>
-      <c r="AD50" t="n">
-        <v>0.996470910039047</v>
-      </c>
+        <v>6.22053176842703</v>
+      </c>
+      <c r="AA50" t="inlineStr"/>
+      <c r="AB50" t="inlineStr"/>
+      <c r="AC50" t="inlineStr"/>
+      <c r="AD50" t="inlineStr"/>
       <c r="AE50" t="n">
-        <v>28.21110017198901</v>
+        <v>25.44297998229845</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>自用發電設備</t>
+          <t>民營電廠</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>02月</t>
+          <t>04月</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2025/02</t>
+          <t>2026/04</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>18875.3718</v>
+        <v>18176.879961</v>
       </c>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="n">
-        <v>7171.8346</v>
+        <v>9868.977999999999</v>
       </c>
       <c r="H51" t="n">
-        <v>10.71498013332266</v>
+        <v>13.8992877031067</v>
       </c>
       <c r="I51" t="n">
-        <v>6111.384</v>
+        <v>3120.3</v>
       </c>
       <c r="J51" t="n">
-        <v>9.130628604723539</v>
-      </c>
-      <c r="K51" t="n">
-        <v>560.4126</v>
-      </c>
-      <c r="L51" t="n">
-        <v>0.837276681682494</v>
-      </c>
+        <v>4.394573320561037</v>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
       <c r="M51" t="n">
-        <v>500.038</v>
+        <v>6748.678</v>
       </c>
       <c r="N51" t="n">
-        <v>0.747074846916631</v>
+        <v>9.504714382545659</v>
       </c>
       <c r="O51" t="inlineStr"/>
       <c r="P51" t="inlineStr"/>
       <c r="Q51" t="n">
-        <v>11703.5372</v>
+        <v>8307.901961</v>
       </c>
       <c r="R51" t="n">
-        <v>17.48550762556665</v>
+        <v>11.70069682647416</v>
       </c>
       <c r="S51" t="n">
-        <v>4.0205</v>
+        <v>43.991</v>
       </c>
       <c r="T51" t="n">
-        <v>0.00600677232936</v>
+        <v>0.061956117983784</v>
       </c>
       <c r="U51" t="n">
-        <v>2.449</v>
+        <v>4.2</v>
       </c>
       <c r="V51" t="n">
-        <v>0.003658894524214</v>
+        <v>0.005915203008158</v>
       </c>
       <c r="W51" t="n">
-        <v>10940.391</v>
+        <v>3703.508961</v>
       </c>
       <c r="X51" t="n">
-        <v>16.34533961725527</v>
+        <v>5.215954130202009</v>
       </c>
       <c r="Y51" t="n">
-        <v>6.2137</v>
+        <v>4556.202</v>
       </c>
       <c r="Z51" t="n">
-        <v>0.009283492407148999</v>
-      </c>
-      <c r="AA51" t="n">
-        <v>83.998</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>0.125496048282937</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>666.465</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>0.995722800767727</v>
-      </c>
+        <v>6.41687137528021</v>
+      </c>
+      <c r="AA51" t="inlineStr"/>
+      <c r="AB51" t="inlineStr"/>
+      <c r="AC51" t="inlineStr"/>
+      <c r="AD51" t="inlineStr"/>
       <c r="AE51" t="n">
-        <v>28.20048775888931</v>
+        <v>25.59998452958085</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>自用發電設備</t>
+          <t>民營電廠</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>03月</t>
+          <t>05月</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2025/03</t>
+          <t>2026/05</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>18981.0839</v>
+        <v>18421.913236</v>
       </c>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="n">
-        <v>7212.6946</v>
+        <v>9868.977999999999</v>
       </c>
       <c r="H52" t="n">
-        <v>10.75799660930612</v>
+        <v>13.83682989670253</v>
       </c>
       <c r="I52" t="n">
-        <v>6111.384</v>
+        <v>3120.3</v>
       </c>
       <c r="J52" t="n">
-        <v>9.115351750809978</v>
-      </c>
-      <c r="K52" t="n">
-        <v>601.2726</v>
-      </c>
-      <c r="L52" t="n">
-        <v>0.89681997516832</v>
-      </c>
+        <v>4.374825876264078</v>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
       <c r="M52" t="n">
-        <v>500.038</v>
+        <v>6748.678</v>
       </c>
       <c r="N52" t="n">
-        <v>0.745824883327822</v>
+        <v>9.462004020438455</v>
       </c>
       <c r="O52" t="inlineStr"/>
       <c r="P52" t="inlineStr"/>
       <c r="Q52" t="n">
-        <v>11768.3893</v>
+        <v>8552.935235999999</v>
       </c>
       <c r="R52" t="n">
-        <v>17.55298112669216</v>
+        <v>11.99166823333128</v>
       </c>
       <c r="S52" t="n">
-        <v>3.5405</v>
+        <v>43.991</v>
       </c>
       <c r="T52" t="n">
-        <v>0.00528078465921</v>
+        <v>0.061677712118301</v>
       </c>
       <c r="U52" t="n">
-        <v>2.449</v>
+        <v>4.2</v>
       </c>
       <c r="V52" t="n">
-        <v>0.003652772667817</v>
+        <v>0.005888622465888</v>
       </c>
       <c r="W52" t="n">
-        <v>11005.562</v>
+        <v>3767.030236</v>
       </c>
       <c r="X52" t="n">
-        <v>16.41519643428522</v>
+        <v>5.281575923187507</v>
       </c>
       <c r="Y52" t="n">
-        <v>6.1798</v>
+        <v>4737.714</v>
       </c>
       <c r="Z52" t="n">
-        <v>0.009217396705829</v>
-      </c>
-      <c r="AA52" t="n">
-        <v>84.193</v>
-      </c>
-      <c r="AB52" t="n">
-        <v>0.125576924957742</v>
-      </c>
-      <c r="AC52" t="n">
-        <v>666.465</v>
-      </c>
-      <c r="AD52" t="n">
-        <v>0.994056813416335</v>
-      </c>
+        <v>6.642525975559591</v>
+      </c>
+      <c r="AA52" t="inlineStr"/>
+      <c r="AB52" t="inlineStr"/>
+      <c r="AC52" t="inlineStr"/>
+      <c r="AD52" t="inlineStr"/>
       <c r="AE52" t="n">
-        <v>28.31097773599827</v>
+        <v>25.82849813003382</v>
       </c>
     </row>
     <row r="53">
@@ -5230,89 +5224,89 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>04月</t>
+          <t>01月</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2025/04</t>
+          <t>2025/01</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>19079.3439</v>
+        <v>18868.2988</v>
       </c>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="n">
-        <v>7212.6946</v>
+        <v>7211.8346</v>
       </c>
       <c r="H53" t="n">
-        <v>10.86503060852116</v>
+        <v>10.78283688852841</v>
       </c>
       <c r="I53" t="n">
-        <v>6111.384</v>
+        <v>6151.384</v>
       </c>
       <c r="J53" t="n">
-        <v>9.206042665445244</v>
+        <v>9.197295000457087</v>
       </c>
       <c r="K53" t="n">
-        <v>601.2726</v>
+        <v>560.4126</v>
       </c>
       <c r="L53" t="n">
-        <v>0.905742661427132</v>
+        <v>0.837905746767419</v>
       </c>
       <c r="M53" t="n">
         <v>500.038</v>
       </c>
       <c r="N53" t="n">
-        <v>0.75324528164879</v>
+        <v>0.747636141303902</v>
       </c>
       <c r="O53" t="inlineStr"/>
       <c r="P53" t="inlineStr"/>
       <c r="Q53" t="n">
-        <v>11866.6493</v>
+        <v>11656.4642</v>
       </c>
       <c r="R53" t="n">
-        <v>17.87563664002719</v>
+        <v>17.4282632834606</v>
       </c>
       <c r="S53" t="n">
-        <v>3.5405</v>
+        <v>3.9605</v>
       </c>
       <c r="T53" t="n">
-        <v>0.005333324506693</v>
+        <v>0.005921575835505</v>
       </c>
       <c r="U53" t="n">
         <v>2.449</v>
       </c>
       <c r="V53" t="n">
-        <v>0.003689115016774</v>
+        <v>0.003661643535198</v>
       </c>
       <c r="W53" t="n">
-        <v>11103.822</v>
+        <v>10893.378</v>
       </c>
       <c r="X53" t="n">
-        <v>16.72653184311598</v>
+        <v>16.287328350415</v>
       </c>
       <c r="Y53" t="n">
-        <v>6.1798</v>
+        <v>6.2137</v>
       </c>
       <c r="Z53" t="n">
-        <v>0.009309102891246999</v>
+        <v>0.009290467306924999</v>
       </c>
       <c r="AA53" t="n">
-        <v>84.193</v>
+        <v>83.998</v>
       </c>
       <c r="AB53" t="n">
-        <v>0.126826321195302</v>
+        <v>0.125590336328929</v>
       </c>
       <c r="AC53" t="n">
         <v>666.465</v>
       </c>
       <c r="AD53" t="n">
-        <v>1.003946933301191</v>
+        <v>0.996470910039047</v>
       </c>
       <c r="AE53" t="n">
-        <v>28.74066724854835</v>
+        <v>28.21110017198901</v>
       </c>
     </row>
     <row r="54">
@@ -5323,89 +5317,89 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>05月</t>
+          <t>02月</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2025/05</t>
+          <t>2025/02</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>19209.2769</v>
+        <v>18875.3718</v>
       </c>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="n">
-        <v>7237.4036</v>
+        <v>7171.8346</v>
       </c>
       <c r="H54" t="n">
-        <v>10.70277131208823</v>
+        <v>10.71498013332266</v>
       </c>
       <c r="I54" t="n">
         <v>6111.384</v>
       </c>
       <c r="J54" t="n">
-        <v>9.037598145328669</v>
+        <v>9.130628604723539</v>
       </c>
       <c r="K54" t="n">
-        <v>632.7316</v>
+        <v>560.4126</v>
       </c>
       <c r="L54" t="n">
-        <v>0.935692133672314</v>
+        <v>0.837276681682494</v>
       </c>
       <c r="M54" t="n">
-        <v>493.288</v>
+        <v>500.038</v>
       </c>
       <c r="N54" t="n">
-        <v>0.72948103308725</v>
+        <v>0.747074846916631</v>
       </c>
       <c r="O54" t="inlineStr"/>
       <c r="P54" t="inlineStr"/>
       <c r="Q54" t="n">
-        <v>11971.8733</v>
+        <v>11703.5372</v>
       </c>
       <c r="R54" t="n">
-        <v>17.70416978088594</v>
+        <v>17.48550762556665</v>
       </c>
       <c r="S54" t="n">
-        <v>3.5405</v>
+        <v>4.0205</v>
       </c>
       <c r="T54" t="n">
-        <v>0.005235739765908</v>
+        <v>0.00600677232936</v>
       </c>
       <c r="U54" t="n">
         <v>2.449</v>
       </c>
       <c r="V54" t="n">
-        <v>0.003621614655193</v>
+        <v>0.003658894524214</v>
       </c>
       <c r="W54" t="n">
-        <v>11209.065</v>
+        <v>10940.391</v>
       </c>
       <c r="X54" t="n">
-        <v>16.5761184463075</v>
+        <v>16.34533961725527</v>
       </c>
       <c r="Y54" t="n">
-        <v>6.1798</v>
+        <v>6.2137</v>
       </c>
       <c r="Z54" t="n">
-        <v>0.009138772660743</v>
+        <v>0.009283492407148999</v>
       </c>
       <c r="AA54" t="n">
-        <v>84.17400000000001</v>
+        <v>83.998</v>
       </c>
       <c r="AB54" t="n">
-        <v>0.124477661080517</v>
+        <v>0.125496048282937</v>
       </c>
       <c r="AC54" t="n">
         <v>666.465</v>
       </c>
       <c r="AD54" t="n">
-        <v>0.985577546416077</v>
+        <v>0.995722800767727</v>
       </c>
       <c r="AE54" t="n">
-        <v>28.40694109297418</v>
+        <v>28.20048775888931</v>
       </c>
     </row>
     <row r="55">
@@ -5416,89 +5410,89 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>06月</t>
+          <t>03月</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2025/06</t>
+          <t>2025/03</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>19315.4943</v>
+        <v>18981.0839</v>
       </c>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="n">
-        <v>7237.4036</v>
+        <v>7212.6946</v>
       </c>
       <c r="H55" t="n">
-        <v>10.8367118493627</v>
+        <v>10.75799660930612</v>
       </c>
       <c r="I55" t="n">
         <v>6111.384</v>
       </c>
       <c r="J55" t="n">
-        <v>9.150699763214202</v>
+        <v>9.115351750809978</v>
       </c>
       <c r="K55" t="n">
-        <v>632.7316</v>
+        <v>601.2726</v>
       </c>
       <c r="L55" t="n">
-        <v>0.947401914574202</v>
+        <v>0.89681997516832</v>
       </c>
       <c r="M55" t="n">
-        <v>493.288</v>
+        <v>500.038</v>
       </c>
       <c r="N55" t="n">
-        <v>0.738610171574296</v>
+        <v>0.745824883327822</v>
       </c>
       <c r="O55" t="inlineStr"/>
       <c r="P55" t="inlineStr"/>
       <c r="Q55" t="n">
-        <v>12078.0907</v>
+        <v>11768.3893</v>
       </c>
       <c r="R55" t="n">
-        <v>18.08477125779851</v>
+        <v>17.55298112669216</v>
       </c>
       <c r="S55" t="n">
         <v>3.5405</v>
       </c>
       <c r="T55" t="n">
-        <v>0.005301262776428</v>
+        <v>0.00528078465921</v>
       </c>
       <c r="U55" t="n">
         <v>2.449</v>
       </c>
       <c r="V55" t="n">
-        <v>0.003666937590587</v>
+        <v>0.003652772667817</v>
       </c>
       <c r="W55" t="n">
-        <v>11315.292</v>
+        <v>11005.562</v>
       </c>
       <c r="X55" t="n">
-        <v>16.94261722469077</v>
+        <v>16.41519643428522</v>
       </c>
       <c r="Y55" t="n">
-        <v>6.1702</v>
+        <v>6.1798</v>
       </c>
       <c r="Z55" t="n">
-        <v>0.009238766158203</v>
+        <v>0.009217396705829</v>
       </c>
       <c r="AA55" t="n">
-        <v>84.17400000000001</v>
+        <v>84.193</v>
       </c>
       <c r="AB55" t="n">
-        <v>0.126035444977568</v>
+        <v>0.125576924957742</v>
       </c>
       <c r="AC55" t="n">
         <v>666.465</v>
       </c>
       <c r="AD55" t="n">
-        <v>0.9979116216049509</v>
+        <v>0.994056813416335</v>
       </c>
       <c r="AE55" t="n">
-        <v>28.9214831071612</v>
+        <v>28.31097773599827</v>
       </c>
     </row>
     <row r="56">
@@ -5509,89 +5503,89 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>07月</t>
+          <t>04月</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2025/07</t>
+          <t>2025/04</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>19170.9063</v>
+        <v>19079.3439</v>
       </c>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="n">
-        <v>7237.4036</v>
+        <v>7212.6946</v>
       </c>
       <c r="H56" t="n">
-        <v>10.62855233045506</v>
+        <v>10.86503060852116</v>
       </c>
       <c r="I56" t="n">
         <v>6111.384</v>
       </c>
       <c r="J56" t="n">
-        <v>8.974926402543829</v>
+        <v>9.206042665445244</v>
       </c>
       <c r="K56" t="n">
-        <v>632.7316</v>
+        <v>601.2726</v>
       </c>
       <c r="L56" t="n">
-        <v>0.929203522894945</v>
+        <v>0.905742661427132</v>
       </c>
       <c r="M56" t="n">
-        <v>493.288</v>
+        <v>500.038</v>
       </c>
       <c r="N56" t="n">
-        <v>0.724422405016285</v>
+        <v>0.75324528164879</v>
       </c>
       <c r="O56" t="inlineStr"/>
       <c r="P56" t="inlineStr"/>
       <c r="Q56" t="n">
-        <v>11933.5027</v>
+        <v>11866.6493</v>
       </c>
       <c r="R56" t="n">
-        <v>17.52504971984383</v>
+        <v>17.87563664002719</v>
       </c>
       <c r="S56" t="n">
         <v>3.5405</v>
       </c>
       <c r="T56" t="n">
-        <v>0.005199432228151</v>
+        <v>0.005333324506693</v>
       </c>
       <c r="U56" t="n">
         <v>2.449</v>
       </c>
       <c r="V56" t="n">
-        <v>0.003596500360611</v>
+        <v>0.003689115016774</v>
       </c>
       <c r="W56" t="n">
-        <v>11170.654</v>
+        <v>11103.822</v>
       </c>
       <c r="X56" t="n">
-        <v>16.40476159218302</v>
+        <v>16.72653184311598</v>
       </c>
       <c r="Y56" t="n">
-        <v>6.1702</v>
+        <v>6.1798</v>
       </c>
       <c r="Z56" t="n">
-        <v>0.009061301153548</v>
+        <v>0.009309102891246999</v>
       </c>
       <c r="AA56" t="n">
-        <v>84.224</v>
+        <v>84.193</v>
       </c>
       <c r="AB56" t="n">
-        <v>0.123687891536165</v>
+        <v>0.126826321195302</v>
       </c>
       <c r="AC56" t="n">
         <v>666.465</v>
       </c>
       <c r="AD56" t="n">
-        <v>0.978743002382337</v>
+        <v>1.003946933301191</v>
       </c>
       <c r="AE56" t="n">
-        <v>28.15360205029889</v>
+        <v>28.74066724854835</v>
       </c>
     </row>
     <row r="57">
@@ -5602,89 +5596,89 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>08月</t>
+          <t>05月</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2025/08</t>
+          <t>2025/05</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>19246.8763</v>
+        <v>19209.2769</v>
       </c>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="n">
-        <v>7240.1916</v>
+        <v>7237.4036</v>
       </c>
       <c r="H57" t="n">
-        <v>10.60972460677555</v>
+        <v>10.70277131208823</v>
       </c>
       <c r="I57" t="n">
         <v>6111.384</v>
       </c>
       <c r="J57" t="n">
-        <v>8.95557808252676</v>
+        <v>9.037598145328669</v>
       </c>
       <c r="K57" t="n">
-        <v>635.5196</v>
+        <v>632.7316</v>
       </c>
       <c r="L57" t="n">
-        <v>0.931285843071909</v>
+        <v>0.935692133672314</v>
       </c>
       <c r="M57" t="n">
         <v>493.288</v>
       </c>
       <c r="N57" t="n">
-        <v>0.722860681176876</v>
+        <v>0.72948103308725</v>
       </c>
       <c r="O57" t="inlineStr"/>
       <c r="P57" t="inlineStr"/>
       <c r="Q57" t="n">
-        <v>12006.6847</v>
+        <v>11971.8733</v>
       </c>
       <c r="R57" t="n">
-        <v>17.59450925406248</v>
+        <v>17.70416978088594</v>
       </c>
       <c r="S57" t="n">
         <v>3.5405</v>
       </c>
       <c r="T57" t="n">
-        <v>0.005188223191537</v>
+        <v>0.005235739765908</v>
       </c>
       <c r="U57" t="n">
         <v>2.449</v>
       </c>
       <c r="V57" t="n">
-        <v>0.003588746955535</v>
+        <v>0.003621614655193</v>
       </c>
       <c r="W57" t="n">
-        <v>11243.576</v>
+        <v>11209.065</v>
       </c>
       <c r="X57" t="n">
-        <v>16.4762552630998</v>
+        <v>16.5761184463075</v>
       </c>
       <c r="Y57" t="n">
-        <v>6.1702</v>
+        <v>6.1798</v>
       </c>
       <c r="Z57" t="n">
-        <v>0.009041766625171</v>
+        <v>0.009138772660743</v>
       </c>
       <c r="AA57" t="n">
-        <v>84.48399999999999</v>
+        <v>84.17400000000001</v>
       </c>
       <c r="AB57" t="n">
-        <v>0.123802244912804</v>
+        <v>0.124477661080517</v>
       </c>
       <c r="AC57" t="n">
         <v>666.465</v>
       </c>
       <c r="AD57" t="n">
-        <v>0.976633009277636</v>
+        <v>0.985577546416077</v>
       </c>
       <c r="AE57" t="n">
-        <v>28.20423386083803</v>
+        <v>28.40694109297418</v>
       </c>
     </row>
     <row r="58">
@@ -5695,89 +5689,89 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>09月</t>
+          <t>06月</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2025/09</t>
+          <t>2025/06</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>19310.2283</v>
+        <v>19315.4943</v>
       </c>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="n">
-        <v>7240.1916</v>
+        <v>7237.4036</v>
       </c>
       <c r="H58" t="n">
-        <v>10.58488086388101</v>
+        <v>10.8367118493627</v>
       </c>
       <c r="I58" t="n">
         <v>6111.384</v>
       </c>
       <c r="J58" t="n">
-        <v>8.934607690966155</v>
+        <v>9.150699763214202</v>
       </c>
       <c r="K58" t="n">
-        <v>635.5196</v>
+        <v>632.7316</v>
       </c>
       <c r="L58" t="n">
-        <v>0.92910514310993</v>
+        <v>0.947401914574202</v>
       </c>
       <c r="M58" t="n">
         <v>493.288</v>
       </c>
       <c r="N58" t="n">
-        <v>0.72116802980492</v>
+        <v>0.738610171574296</v>
       </c>
       <c r="O58" t="inlineStr"/>
       <c r="P58" t="inlineStr"/>
       <c r="Q58" t="n">
-        <v>12070.0367</v>
+        <v>12078.0907</v>
       </c>
       <c r="R58" t="n">
-        <v>17.64592811220237</v>
+        <v>18.08477125779851</v>
       </c>
       <c r="S58" t="n">
         <v>3.5405</v>
       </c>
       <c r="T58" t="n">
-        <v>0.005176074442363</v>
+        <v>0.005301262776428</v>
       </c>
       <c r="U58" t="n">
         <v>2.449</v>
       </c>
       <c r="V58" t="n">
-        <v>0.003580343541688</v>
+        <v>0.003666937590587</v>
       </c>
       <c r="W58" t="n">
-        <v>11308.948</v>
+        <v>11315.292</v>
       </c>
       <c r="X58" t="n">
-        <v>16.53324578811221</v>
+        <v>16.94261722469077</v>
       </c>
       <c r="Y58" t="n">
         <v>6.1702</v>
       </c>
       <c r="Z58" t="n">
-        <v>0.009020594414424</v>
+        <v>0.009238766158203</v>
       </c>
       <c r="AA58" t="n">
-        <v>84.434</v>
+        <v>84.17400000000001</v>
       </c>
       <c r="AB58" t="n">
-        <v>0.123439251367454</v>
+        <v>0.126035444977568</v>
       </c>
       <c r="AC58" t="n">
-        <v>664.495</v>
+        <v>666.465</v>
       </c>
       <c r="AD58" t="n">
-        <v>0.971466060324234</v>
+        <v>0.9979116216049509</v>
       </c>
       <c r="AE58" t="n">
-        <v>28.23080897608337</v>
+        <v>28.9214831071612</v>
       </c>
     </row>
     <row r="59">
@@ -5788,89 +5782,89 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>10月</t>
+          <t>07月</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2025/10</t>
+          <t>2025/07</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>19400.2343</v>
+        <v>19170.9063</v>
       </c>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="n">
-        <v>7267.5146</v>
+        <v>7237.4036</v>
       </c>
       <c r="H59" t="n">
-        <v>10.59698174048459</v>
+        <v>10.62855233045506</v>
       </c>
       <c r="I59" t="n">
-        <v>6138.707</v>
+        <v>6111.384</v>
       </c>
       <c r="J59" t="n">
-        <v>8.951033409576489</v>
+        <v>8.974926402543829</v>
       </c>
       <c r="K59" t="n">
-        <v>635.5196</v>
+        <v>632.7316</v>
       </c>
       <c r="L59" t="n">
-        <v>0.926670253530701</v>
+        <v>0.929203522894945</v>
       </c>
       <c r="M59" t="n">
         <v>493.288</v>
       </c>
       <c r="N59" t="n">
-        <v>0.719278077377397</v>
+        <v>0.724422405016285</v>
       </c>
       <c r="O59" t="inlineStr"/>
       <c r="P59" t="inlineStr"/>
       <c r="Q59" t="n">
-        <v>12132.7197</v>
+        <v>11933.5027</v>
       </c>
       <c r="R59" t="n">
-        <v>17.69108370601933</v>
+        <v>17.52504971984383</v>
       </c>
       <c r="S59" t="n">
         <v>3.5405</v>
       </c>
       <c r="T59" t="n">
-        <v>0.005162509594709</v>
+        <v>0.005199432228151</v>
       </c>
       <c r="U59" t="n">
         <v>2.449</v>
       </c>
       <c r="V59" t="n">
-        <v>0.003570960598063</v>
+        <v>0.003596500360611</v>
       </c>
       <c r="W59" t="n">
-        <v>11371.631</v>
+        <v>11170.654</v>
       </c>
       <c r="X59" t="n">
-        <v>16.58131736901203</v>
+        <v>16.40476159218302</v>
       </c>
       <c r="Y59" t="n">
         <v>6.1702</v>
       </c>
       <c r="Z59" t="n">
-        <v>0.008996954300599</v>
+        <v>0.009061301153548</v>
       </c>
       <c r="AA59" t="n">
-        <v>84.434</v>
+        <v>84.224</v>
       </c>
       <c r="AB59" t="n">
-        <v>0.123115756282908</v>
+        <v>0.123687891536165</v>
       </c>
       <c r="AC59" t="n">
-        <v>664.495</v>
+        <v>666.465</v>
       </c>
       <c r="AD59" t="n">
-        <v>0.968920156231032</v>
+        <v>0.978743002382337</v>
       </c>
       <c r="AE59" t="n">
-        <v>28.28806544650392</v>
+        <v>28.15360205029889</v>
       </c>
     </row>
     <row r="60">
@@ -5881,89 +5875,89 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>11月</t>
+          <t>08月</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2025/11</t>
+          <t>2025/08</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>19437.3073</v>
+        <v>19246.8763</v>
       </c>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="n">
-        <v>7267.5146</v>
+        <v>7240.1916</v>
       </c>
       <c r="H60" t="n">
-        <v>10.57812089211286</v>
+        <v>10.60972460677555</v>
       </c>
       <c r="I60" t="n">
-        <v>6138.707</v>
+        <v>6111.384</v>
       </c>
       <c r="J60" t="n">
-        <v>8.935102072895655</v>
+        <v>8.95557808252676</v>
       </c>
       <c r="K60" t="n">
         <v>635.5196</v>
       </c>
       <c r="L60" t="n">
-        <v>0.925020936058003</v>
+        <v>0.931285843071909</v>
       </c>
       <c r="M60" t="n">
         <v>493.288</v>
       </c>
       <c r="N60" t="n">
-        <v>0.717997883159198</v>
+        <v>0.722860681176876</v>
       </c>
       <c r="O60" t="inlineStr"/>
       <c r="P60" t="inlineStr"/>
       <c r="Q60" t="n">
-        <v>12169.7927</v>
+        <v>12006.6847</v>
       </c>
       <c r="R60" t="n">
-        <v>17.71355759127784</v>
+        <v>17.59450925406248</v>
       </c>
       <c r="S60" t="n">
-        <v>4.1025</v>
+        <v>3.5405</v>
       </c>
       <c r="T60" t="n">
-        <v>0.00597133178926</v>
+        <v>0.005188223191537</v>
       </c>
       <c r="U60" t="n">
         <v>2.449</v>
       </c>
       <c r="V60" t="n">
-        <v>0.003564604887727</v>
+        <v>0.003588746955535</v>
       </c>
       <c r="W60" t="n">
-        <v>11408.142</v>
+        <v>11243.576</v>
       </c>
       <c r="X60" t="n">
-        <v>16.60494844143693</v>
+        <v>16.4762552630998</v>
       </c>
       <c r="Y60" t="n">
         <v>6.1702</v>
       </c>
       <c r="Z60" t="n">
-        <v>0.008980941232442001</v>
+        <v>0.009041766625171</v>
       </c>
       <c r="AA60" t="n">
-        <v>84.434</v>
+        <v>84.48399999999999</v>
       </c>
       <c r="AB60" t="n">
-        <v>0.122896630906618</v>
+        <v>0.123802244912804</v>
       </c>
       <c r="AC60" t="n">
-        <v>664.495</v>
+        <v>666.465</v>
       </c>
       <c r="AD60" t="n">
-        <v>0.967195641024861</v>
+        <v>0.976633009277636</v>
       </c>
       <c r="AE60" t="n">
-        <v>28.29167848339069</v>
+        <v>28.20423386083803</v>
       </c>
     </row>
     <row r="61">
@@ -5974,89 +5968,89 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>12月</t>
+          <t>09月</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2025/12</t>
+          <t>2025/09</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>19576.4033</v>
+        <v>19310.2283</v>
       </c>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="n">
-        <v>7267.5146</v>
+        <v>7240.1916</v>
       </c>
       <c r="H61" t="n">
-        <v>10.40319536749063</v>
+        <v>10.58488086388101</v>
       </c>
       <c r="I61" t="n">
-        <v>6138.707</v>
+        <v>6111.384</v>
       </c>
       <c r="J61" t="n">
-        <v>8.787346395531461</v>
+        <v>8.934607690966155</v>
       </c>
       <c r="K61" t="n">
         <v>635.5196</v>
       </c>
       <c r="L61" t="n">
-        <v>0.909724289878894</v>
+        <v>0.92910514310993</v>
       </c>
       <c r="M61" t="n">
         <v>493.288</v>
       </c>
       <c r="N61" t="n">
-        <v>0.706124682080269</v>
+        <v>0.72116802980492</v>
       </c>
       <c r="O61" t="inlineStr"/>
       <c r="P61" t="inlineStr"/>
       <c r="Q61" t="n">
-        <v>12308.8887</v>
+        <v>12070.0367</v>
       </c>
       <c r="R61" t="n">
-        <v>17.61974773367469</v>
+        <v>17.64592811220237</v>
       </c>
       <c r="S61" t="n">
-        <v>4.1025</v>
+        <v>3.5405</v>
       </c>
       <c r="T61" t="n">
-        <v>0.005872586619245</v>
+        <v>0.005176074442363</v>
       </c>
       <c r="U61" t="n">
         <v>2.449</v>
       </c>
       <c r="V61" t="n">
-        <v>0.003505658654609</v>
+        <v>0.003580343541688</v>
       </c>
       <c r="W61" t="n">
-        <v>11547.283</v>
+        <v>11308.948</v>
       </c>
       <c r="X61" t="n">
-        <v>16.52953555988773</v>
+        <v>16.53324578811221</v>
       </c>
       <c r="Y61" t="n">
         <v>6.1702</v>
       </c>
       <c r="Z61" t="n">
-        <v>0.008832427533959001</v>
+        <v>0.009020594414424</v>
       </c>
       <c r="AA61" t="n">
-        <v>84.389</v>
+        <v>84.434</v>
       </c>
       <c r="AB61" t="n">
-        <v>0.120799929850456</v>
+        <v>0.123439251367454</v>
       </c>
       <c r="AC61" t="n">
         <v>664.495</v>
       </c>
       <c r="AD61" t="n">
-        <v>0.951201571128689</v>
+        <v>0.971466060324234</v>
       </c>
       <c r="AE61" t="n">
-        <v>28.02294310116532</v>
+        <v>28.23080897608337</v>
       </c>
     </row>
     <row r="62">
@@ -6067,89 +6061,89 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>01月</t>
+          <t>10月</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2026/01</t>
+          <t>2025/10</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>19597.0743</v>
+        <v>19400.2343</v>
       </c>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="n">
-        <v>7229.1146</v>
+        <v>7267.5146</v>
       </c>
       <c r="H62" t="n">
-        <v>10.28282201164236</v>
+        <v>10.59698174048459</v>
       </c>
       <c r="I62" t="n">
-        <v>6100.307</v>
+        <v>6138.707</v>
       </c>
       <c r="J62" t="n">
-        <v>8.677185875207451</v>
+        <v>8.951033409576489</v>
       </c>
       <c r="K62" t="n">
         <v>635.5196</v>
       </c>
       <c r="L62" t="n">
-        <v>0.903974455144223</v>
+        <v>0.926670253530701</v>
       </c>
       <c r="M62" t="n">
         <v>493.288</v>
       </c>
       <c r="N62" t="n">
-        <v>0.701661681290685</v>
+        <v>0.719278077377397</v>
       </c>
       <c r="O62" t="inlineStr"/>
       <c r="P62" t="inlineStr"/>
       <c r="Q62" t="n">
-        <v>12367.9597</v>
+        <v>12132.7197</v>
       </c>
       <c r="R62" t="n">
-        <v>17.59240726966282</v>
+        <v>17.69108370601933</v>
       </c>
       <c r="S62" t="n">
-        <v>4.1025</v>
+        <v>3.5405</v>
       </c>
       <c r="T62" t="n">
-        <v>0.005835469436708</v>
+        <v>0.005162509594709</v>
       </c>
       <c r="U62" t="n">
-        <v>7.897</v>
+        <v>2.449</v>
       </c>
       <c r="V62" t="n">
-        <v>0.01123283416007</v>
+        <v>0.003570960598063</v>
       </c>
       <c r="W62" t="n">
-        <v>11600.906</v>
+        <v>11371.631</v>
       </c>
       <c r="X62" t="n">
-        <v>16.50133635615541</v>
+        <v>16.58131736901203</v>
       </c>
       <c r="Y62" t="n">
         <v>6.1702</v>
       </c>
       <c r="Z62" t="n">
-        <v>0.008776602929525999</v>
+        <v>0.008996954300599</v>
       </c>
       <c r="AA62" t="n">
-        <v>84.389</v>
+        <v>84.434</v>
       </c>
       <c r="AB62" t="n">
-        <v>0.120036424203385</v>
+        <v>0.123115756282908</v>
       </c>
       <c r="AC62" t="n">
         <v>664.495</v>
       </c>
       <c r="AD62" t="n">
-        <v>0.945189582777715</v>
+        <v>0.968920156231032</v>
       </c>
       <c r="AE62" t="n">
-        <v>27.87522928130518</v>
+        <v>28.28806544650392</v>
       </c>
     </row>
     <row r="63">
@@ -6160,89 +6154,89 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>02月</t>
+          <t>11月</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2026/02</t>
+          <t>2025/11</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>19681.8633</v>
+        <v>19437.3073</v>
       </c>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="n">
-        <v>7229.1146</v>
+        <v>7267.5146</v>
       </c>
       <c r="H63" t="n">
-        <v>10.26177069119116</v>
+        <v>10.57812089211286</v>
       </c>
       <c r="I63" t="n">
-        <v>6100.307</v>
+        <v>6138.707</v>
       </c>
       <c r="J63" t="n">
-        <v>8.65942166415072</v>
+        <v>8.935102072895655</v>
       </c>
       <c r="K63" t="n">
         <v>635.5196</v>
       </c>
       <c r="L63" t="n">
-        <v>0.902123809872585</v>
+        <v>0.925020936058003</v>
       </c>
       <c r="M63" t="n">
         <v>493.288</v>
       </c>
       <c r="N63" t="n">
-        <v>0.700225217167854</v>
+        <v>0.717997883159198</v>
       </c>
       <c r="O63" t="inlineStr"/>
       <c r="P63" t="inlineStr"/>
       <c r="Q63" t="n">
-        <v>12452.7487</v>
+        <v>12169.7927</v>
       </c>
       <c r="R63" t="n">
-        <v>17.67675001782774</v>
+        <v>17.71355759127784</v>
       </c>
       <c r="S63" t="n">
         <v>4.1025</v>
       </c>
       <c r="T63" t="n">
-        <v>0.005823522877976</v>
+        <v>0.00597133178926</v>
       </c>
       <c r="U63" t="n">
-        <v>7.897</v>
+        <v>2.449</v>
       </c>
       <c r="V63" t="n">
-        <v>0.011209837944516</v>
+        <v>0.003564604887727</v>
       </c>
       <c r="W63" t="n">
-        <v>11679.818</v>
+        <v>11408.142</v>
       </c>
       <c r="X63" t="n">
-        <v>16.57957034335117</v>
+        <v>16.60494844143693</v>
       </c>
       <c r="Y63" t="n">
-        <v>16.1302</v>
+        <v>6.1702</v>
       </c>
       <c r="Z63" t="n">
-        <v>0.022896913766321</v>
+        <v>0.008980941232442001</v>
       </c>
       <c r="AA63" t="n">
-        <v>80.306</v>
+        <v>84.434</v>
       </c>
       <c r="AB63" t="n">
-        <v>0.113994839302561</v>
+        <v>0.122896630906618</v>
       </c>
       <c r="AC63" t="n">
         <v>664.495</v>
       </c>
       <c r="AD63" t="n">
-        <v>0.943254560585202</v>
+        <v>0.967195641024861</v>
       </c>
       <c r="AE63" t="n">
-        <v>27.9385207090189</v>
+        <v>28.29167848339069</v>
       </c>
     </row>
     <row r="64">
@@ -6253,89 +6247,89 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>03月</t>
+          <t>12月</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2026/03</t>
+          <t>2025/12</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>19776.7423</v>
+        <v>19576.4033</v>
       </c>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="n">
-        <v>7235.2646</v>
+        <v>7267.5146</v>
       </c>
       <c r="H64" t="n">
-        <v>10.22237454092418</v>
+        <v>10.40319536749063</v>
       </c>
       <c r="I64" t="n">
-        <v>6106.457</v>
+        <v>6138.707</v>
       </c>
       <c r="J64" t="n">
-        <v>8.627533894482349</v>
+        <v>8.787346395531461</v>
       </c>
       <c r="K64" t="n">
         <v>635.5196</v>
       </c>
       <c r="L64" t="n">
-        <v>0.897896585468114</v>
+        <v>0.909724289878894</v>
       </c>
       <c r="M64" t="n">
         <v>493.288</v>
       </c>
       <c r="N64" t="n">
-        <v>0.696944060973722</v>
+        <v>0.706124682080269</v>
       </c>
       <c r="O64" t="inlineStr"/>
       <c r="P64" t="inlineStr"/>
       <c r="Q64" t="n">
-        <v>12541.4777</v>
+        <v>12308.8887</v>
       </c>
       <c r="R64" t="n">
-        <v>17.71928041803038</v>
+        <v>17.61974773367469</v>
       </c>
       <c r="S64" t="n">
         <v>4.1025</v>
       </c>
       <c r="T64" t="n">
-        <v>0.005796234674561</v>
+        <v>0.005872586619245</v>
       </c>
       <c r="U64" t="n">
-        <v>7.897</v>
+        <v>2.449</v>
       </c>
       <c r="V64" t="n">
-        <v>0.011157310231568</v>
+        <v>0.003505658654609</v>
       </c>
       <c r="W64" t="n">
-        <v>11768.547</v>
+        <v>11547.283</v>
       </c>
       <c r="X64" t="n">
-        <v>16.62724197211388</v>
+        <v>16.52953555988773</v>
       </c>
       <c r="Y64" t="n">
-        <v>16.1302</v>
+        <v>6.1702</v>
       </c>
       <c r="Z64" t="n">
-        <v>0.022789622071322</v>
+        <v>0.008832427533959001</v>
       </c>
       <c r="AA64" t="n">
-        <v>80.306</v>
+        <v>84.389</v>
       </c>
       <c r="AB64" t="n">
-        <v>0.113460675630779</v>
+        <v>0.120799929850456</v>
       </c>
       <c r="AC64" t="n">
         <v>664.495</v>
       </c>
       <c r="AD64" t="n">
-        <v>0.938834603308276</v>
+        <v>0.951201571128689</v>
       </c>
       <c r="AE64" t="n">
-        <v>27.94165495895456</v>
+        <v>28.02294310116532</v>
       </c>
     </row>
     <row r="65">
@@ -6346,89 +6340,461 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>04月</t>
+          <t>01月</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2026/04</t>
+          <t>2026/01</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>19832.8473</v>
+        <v>19597.0743</v>
       </c>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="n">
-        <v>7235.2646</v>
+        <v>7229.1146</v>
       </c>
       <c r="H65" t="n">
-        <v>10.1900140301765</v>
+        <v>10.28282201164236</v>
       </c>
       <c r="I65" t="n">
-        <v>6106.457</v>
+        <v>6100.307</v>
       </c>
       <c r="J65" t="n">
-        <v>8.600222098949843</v>
+        <v>8.677185875207451</v>
       </c>
       <c r="K65" t="n">
         <v>635.5196</v>
       </c>
       <c r="L65" t="n">
-        <v>0.8950541546818001</v>
+        <v>0.903974455144223</v>
       </c>
       <c r="M65" t="n">
         <v>493.288</v>
       </c>
       <c r="N65" t="n">
-        <v>0.694737776544856</v>
+        <v>0.701661681290685</v>
       </c>
       <c r="O65" t="inlineStr"/>
       <c r="P65" t="inlineStr"/>
       <c r="Q65" t="n">
-        <v>12597.5827</v>
+        <v>12367.9597</v>
       </c>
       <c r="R65" t="n">
-        <v>17.74220454346738</v>
+        <v>17.59240726966282</v>
       </c>
       <c r="S65" t="n">
-        <v>4.4675</v>
+        <v>4.1025</v>
       </c>
       <c r="T65" t="n">
-        <v>0.006291945104511</v>
+        <v>0.005835469436708</v>
       </c>
       <c r="U65" t="n">
         <v>7.897</v>
       </c>
       <c r="V65" t="n">
-        <v>0.011121990037006</v>
+        <v>0.01123283416007</v>
       </c>
       <c r="W65" t="n">
-        <v>11824.862</v>
+        <v>11600.906</v>
       </c>
       <c r="X65" t="n">
-        <v>16.65391887463258</v>
+        <v>16.50133635615541</v>
       </c>
       <c r="Y65" t="n">
-        <v>16.1302</v>
+        <v>6.1702</v>
       </c>
       <c r="Z65" t="n">
-        <v>0.022717477990999</v>
+        <v>0.008776602929525999</v>
       </c>
       <c r="AA65" t="n">
-        <v>79.73099999999999</v>
+        <v>84.389</v>
       </c>
       <c r="AB65" t="n">
-        <v>0.112291678819874</v>
+        <v>0.120036424203385</v>
       </c>
       <c r="AC65" t="n">
         <v>664.495</v>
       </c>
       <c r="AD65" t="n">
+        <v>0.945189582777715</v>
+      </c>
+      <c r="AE65" t="n">
+        <v>27.87522928130518</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>自用發電設備</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>02月</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>2026/02</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>19681.8633</v>
+      </c>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="n">
+        <v>7229.1146</v>
+      </c>
+      <c r="H66" t="n">
+        <v>10.26177069119116</v>
+      </c>
+      <c r="I66" t="n">
+        <v>6100.307</v>
+      </c>
+      <c r="J66" t="n">
+        <v>8.65942166415072</v>
+      </c>
+      <c r="K66" t="n">
+        <v>635.5196</v>
+      </c>
+      <c r="L66" t="n">
+        <v>0.902123809872585</v>
+      </c>
+      <c r="M66" t="n">
+        <v>493.288</v>
+      </c>
+      <c r="N66" t="n">
+        <v>0.700225217167854</v>
+      </c>
+      <c r="O66" t="inlineStr"/>
+      <c r="P66" t="inlineStr"/>
+      <c r="Q66" t="n">
+        <v>12452.7487</v>
+      </c>
+      <c r="R66" t="n">
+        <v>17.67675001782774</v>
+      </c>
+      <c r="S66" t="n">
+        <v>4.1025</v>
+      </c>
+      <c r="T66" t="n">
+        <v>0.005823522877976</v>
+      </c>
+      <c r="U66" t="n">
+        <v>7.897</v>
+      </c>
+      <c r="V66" t="n">
+        <v>0.011209837944516</v>
+      </c>
+      <c r="W66" t="n">
+        <v>11679.818</v>
+      </c>
+      <c r="X66" t="n">
+        <v>16.57957034335117</v>
+      </c>
+      <c r="Y66" t="n">
+        <v>16.1302</v>
+      </c>
+      <c r="Z66" t="n">
+        <v>0.022896913766321</v>
+      </c>
+      <c r="AA66" t="n">
+        <v>80.306</v>
+      </c>
+      <c r="AB66" t="n">
+        <v>0.113994839302561</v>
+      </c>
+      <c r="AC66" t="n">
+        <v>664.495</v>
+      </c>
+      <c r="AD66" t="n">
+        <v>0.943254560585202</v>
+      </c>
+      <c r="AE66" t="n">
+        <v>27.9385207090189</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>自用發電設備</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>03月</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>2026/03</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>19776.7423</v>
+      </c>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="n">
+        <v>7235.2646</v>
+      </c>
+      <c r="H67" t="n">
+        <v>10.22237454092418</v>
+      </c>
+      <c r="I67" t="n">
+        <v>6106.457</v>
+      </c>
+      <c r="J67" t="n">
+        <v>8.627533894482349</v>
+      </c>
+      <c r="K67" t="n">
+        <v>635.5196</v>
+      </c>
+      <c r="L67" t="n">
+        <v>0.897896585468114</v>
+      </c>
+      <c r="M67" t="n">
+        <v>493.288</v>
+      </c>
+      <c r="N67" t="n">
+        <v>0.696944060973722</v>
+      </c>
+      <c r="O67" t="inlineStr"/>
+      <c r="P67" t="inlineStr"/>
+      <c r="Q67" t="n">
+        <v>12541.4777</v>
+      </c>
+      <c r="R67" t="n">
+        <v>17.71928041803038</v>
+      </c>
+      <c r="S67" t="n">
+        <v>4.1025</v>
+      </c>
+      <c r="T67" t="n">
+        <v>0.005796234674561</v>
+      </c>
+      <c r="U67" t="n">
+        <v>7.897</v>
+      </c>
+      <c r="V67" t="n">
+        <v>0.011157310231568</v>
+      </c>
+      <c r="W67" t="n">
+        <v>11768.547</v>
+      </c>
+      <c r="X67" t="n">
+        <v>16.62724197211388</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>16.1302</v>
+      </c>
+      <c r="Z67" t="n">
+        <v>0.022789622071322</v>
+      </c>
+      <c r="AA67" t="n">
+        <v>80.306</v>
+      </c>
+      <c r="AB67" t="n">
+        <v>0.113460675630779</v>
+      </c>
+      <c r="AC67" t="n">
+        <v>664.495</v>
+      </c>
+      <c r="AD67" t="n">
+        <v>0.938834603308276</v>
+      </c>
+      <c r="AE67" t="n">
+        <v>27.94165495895456</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>自用發電設備</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>04月</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>2026/04</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>19832.8473</v>
+      </c>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="n">
+        <v>7235.2646</v>
+      </c>
+      <c r="H68" t="n">
+        <v>10.1900140301765</v>
+      </c>
+      <c r="I68" t="n">
+        <v>6106.457</v>
+      </c>
+      <c r="J68" t="n">
+        <v>8.600222098949843</v>
+      </c>
+      <c r="K68" t="n">
+        <v>635.5196</v>
+      </c>
+      <c r="L68" t="n">
+        <v>0.8950541546818001</v>
+      </c>
+      <c r="M68" t="n">
+        <v>493.288</v>
+      </c>
+      <c r="N68" t="n">
+        <v>0.694737776544856</v>
+      </c>
+      <c r="O68" t="inlineStr"/>
+      <c r="P68" t="inlineStr"/>
+      <c r="Q68" t="n">
+        <v>12597.5827</v>
+      </c>
+      <c r="R68" t="n">
+        <v>17.74220454346738</v>
+      </c>
+      <c r="S68" t="n">
+        <v>4.4675</v>
+      </c>
+      <c r="T68" t="n">
+        <v>0.006291945104511</v>
+      </c>
+      <c r="U68" t="n">
+        <v>7.897</v>
+      </c>
+      <c r="V68" t="n">
+        <v>0.011121990037006</v>
+      </c>
+      <c r="W68" t="n">
+        <v>11824.862</v>
+      </c>
+      <c r="X68" t="n">
+        <v>16.65391887463258</v>
+      </c>
+      <c r="Y68" t="n">
+        <v>16.1302</v>
+      </c>
+      <c r="Z68" t="n">
+        <v>0.022717477990999</v>
+      </c>
+      <c r="AA68" t="n">
+        <v>79.73099999999999</v>
+      </c>
+      <c r="AB68" t="n">
+        <v>0.112291678819874</v>
+      </c>
+      <c r="AC68" t="n">
+        <v>664.495</v>
+      </c>
+      <c r="AD68" t="n">
         <v>0.935862576882417</v>
       </c>
-      <c r="AE65" t="n">
+      <c r="AE68" t="n">
         <v>27.93221857364388</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>自用發電設備</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>05月</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>2026/05</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>19908.3153</v>
+      </c>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="n">
+        <v>7281.2646</v>
+      </c>
+      <c r="H69" t="n">
+        <v>10.20871864372196</v>
+      </c>
+      <c r="I69" t="n">
+        <v>6152.457</v>
+      </c>
+      <c r="J69" t="n">
+        <v>8.626070597763695</v>
+      </c>
+      <c r="K69" t="n">
+        <v>635.5196</v>
+      </c>
+      <c r="L69" t="n">
+        <v>0.891032141445693</v>
+      </c>
+      <c r="M69" t="n">
+        <v>493.288</v>
+      </c>
+      <c r="N69" t="n">
+        <v>0.6916159045125641</v>
+      </c>
+      <c r="O69" t="inlineStr"/>
+      <c r="P69" t="inlineStr"/>
+      <c r="Q69" t="n">
+        <v>12627.0507</v>
+      </c>
+      <c r="R69" t="n">
+        <v>17.70379391188618</v>
+      </c>
+      <c r="S69" t="n">
+        <v>4.4675</v>
+      </c>
+      <c r="T69" t="n">
+        <v>0.006263671634846</v>
+      </c>
+      <c r="U69" t="n">
+        <v>7.897</v>
+      </c>
+      <c r="V69" t="n">
+        <v>0.011072012288837</v>
+      </c>
+      <c r="W69" t="n">
+        <v>11839.06</v>
+      </c>
+      <c r="X69" t="n">
+        <v>16.59898921214082</v>
+      </c>
+      <c r="Y69" t="n">
+        <v>16.1302</v>
+      </c>
+      <c r="Z69" t="n">
+        <v>0.022615394785538</v>
+      </c>
+      <c r="AA69" t="n">
+        <v>79.501</v>
+      </c>
+      <c r="AB69" t="n">
+        <v>0.111464613014412</v>
+      </c>
+      <c r="AC69" t="n">
+        <v>679.995</v>
+      </c>
+      <c r="AD69" t="n">
+        <v>0.953389008021726</v>
+      </c>
+      <c r="AE69" t="n">
+        <v>27.91251255560813</v>
       </c>
     </row>
   </sheetData>
